--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3A5BF7-D764-4BA4-969C-CF0737F83F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2745DA-8307-42B7-AED9-476ECB37E6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="3105" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7237,7 +7237,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7258,6 +7258,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7456,7 +7462,7 @@
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7578,6 +7584,53 @@
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -17383,75 +17436,75 @@
         <v>429</v>
       </c>
     </row>
-    <row r="265" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="42" t="s">
+    <row r="265" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="52" t="s">
         <v>513</v>
       </c>
-      <c r="B265" s="25" t="s">
+      <c r="B265" s="53" t="s">
         <v>514</v>
       </c>
-      <c r="C265" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D265" s="4">
+      <c r="C265" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D265" s="55">
         <v>6</v>
       </c>
-      <c r="E265" s="4">
+      <c r="E265" s="55">
         <v>1825</v>
       </c>
-      <c r="F265" s="15">
+      <c r="F265" s="56">
         <f t="shared" si="4"/>
         <v>10950</v>
       </c>
-      <c r="G265" s="8">
+      <c r="G265" s="54">
         <v>696</v>
       </c>
-      <c r="H265" s="5">
+      <c r="H265" s="57">
         <v>46236</v>
       </c>
-      <c r="I265" s="8" t="s">
+      <c r="I265" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="J265" s="8">
+      <c r="J265" s="54">
         <v>6170</v>
       </c>
-      <c r="K265" s="5" t="s">
+      <c r="K265" s="57" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="266" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="42" t="s">
+    <row r="266" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="52" t="s">
         <v>515</v>
       </c>
-      <c r="B266" s="25" t="s">
+      <c r="B266" s="53" t="s">
         <v>516</v>
       </c>
-      <c r="C266" s="8" t="s">
+      <c r="C266" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="D266" s="4">
+      <c r="D266" s="55">
         <v>900</v>
       </c>
-      <c r="E266" s="4">
-        <v>148.94</v>
-      </c>
-      <c r="F266" s="15">
+      <c r="E266" s="55">
+        <v>128.94</v>
+      </c>
+      <c r="F266" s="56">
         <f t="shared" si="4"/>
-        <v>134046</v>
-      </c>
-      <c r="G266" s="8">
+        <v>116046</v>
+      </c>
+      <c r="G266" s="54">
         <v>696</v>
       </c>
-      <c r="H266" s="5">
+      <c r="H266" s="57">
         <v>46236</v>
       </c>
-      <c r="I266" s="8" t="s">
+      <c r="I266" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="J266" s="8">
+      <c r="J266" s="54">
         <v>6170</v>
       </c>
-      <c r="K266" s="5" t="s">
+      <c r="K266" s="57" t="s">
         <v>429</v>
       </c>
     </row>
@@ -18607,39 +18660,39 @@
         <v>429</v>
       </c>
     </row>
-    <row r="299" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="42" t="s">
+    <row r="299" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="52" t="s">
         <v>562</v>
       </c>
-      <c r="B299" s="25" t="s">
+      <c r="B299" s="53" t="s">
         <v>563</v>
       </c>
-      <c r="C299" s="8" t="s">
+      <c r="C299" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="D299" s="4">
+      <c r="D299" s="55">
         <v>527</v>
       </c>
-      <c r="E299" s="4">
-        <v>13</v>
-      </c>
-      <c r="F299" s="15">
+      <c r="E299" s="55">
+        <v>130</v>
+      </c>
+      <c r="F299" s="56">
         <f t="shared" si="4"/>
-        <v>6851</v>
-      </c>
-      <c r="G299" s="8">
+        <v>68510</v>
+      </c>
+      <c r="G299" s="54">
         <v>695</v>
       </c>
-      <c r="H299" s="5" t="s">
+      <c r="H299" s="57" t="s">
         <v>564</v>
       </c>
-      <c r="I299" s="8" t="s">
+      <c r="I299" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="J299" s="8">
+      <c r="J299" s="54">
         <v>6177</v>
       </c>
-      <c r="K299" s="5" t="s">
+      <c r="K299" s="57" t="s">
         <v>429</v>
       </c>
     </row>
@@ -19579,7 +19632,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="326" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:11" s="19" customFormat="1" ht="24.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="42" t="s">
         <v>615</v>
       </c>
@@ -19687,111 +19740,111 @@
         <v>617</v>
       </c>
     </row>
-    <row r="329" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A329" s="42" t="s">
+    <row r="329" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A329" s="44" t="s">
         <v>621</v>
       </c>
-      <c r="B329" s="25" t="s">
+      <c r="B329" s="45" t="s">
         <v>622</v>
       </c>
-      <c r="C329" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D329" s="4">
+      <c r="C329" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D329" s="47">
         <v>20</v>
       </c>
-      <c r="E329" s="4">
+      <c r="E329" s="47">
         <v>133</v>
       </c>
-      <c r="F329" s="15">
+      <c r="F329" s="49">
         <f t="shared" si="5"/>
         <v>2660</v>
       </c>
-      <c r="G329" s="8">
+      <c r="G329" s="46">
         <v>694</v>
       </c>
-      <c r="H329" s="5" t="s">
+      <c r="H329" s="50" t="s">
         <v>338</v>
       </c>
-      <c r="I329" s="8" t="s">
+      <c r="I329" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J329" s="8">
+      <c r="J329" s="46">
         <v>6183</v>
       </c>
-      <c r="K329" s="5" t="s">
+      <c r="K329" s="50" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="330" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A330" s="42" t="s">
+    <row r="330" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A330" s="44" t="s">
         <v>623</v>
       </c>
-      <c r="B330" s="25" t="s">
+      <c r="B330" s="45" t="s">
         <v>624</v>
       </c>
-      <c r="C330" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D330" s="4">
+      <c r="C330" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D330" s="47">
         <v>15</v>
       </c>
-      <c r="E330" s="4">
+      <c r="E330" s="47">
         <v>133</v>
       </c>
-      <c r="F330" s="15">
+      <c r="F330" s="49">
         <f t="shared" si="5"/>
         <v>1995</v>
       </c>
-      <c r="G330" s="8">
+      <c r="G330" s="46">
         <v>694</v>
       </c>
-      <c r="H330" s="5" t="s">
+      <c r="H330" s="50" t="s">
         <v>338</v>
       </c>
-      <c r="I330" s="8" t="s">
+      <c r="I330" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J330" s="8">
+      <c r="J330" s="46">
         <v>6183</v>
       </c>
-      <c r="K330" s="5" t="s">
+      <c r="K330" s="50" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="331" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A331" s="42" t="s">
+    <row r="331" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A331" s="44" t="s">
         <v>515</v>
       </c>
-      <c r="B331" s="25" t="s">
+      <c r="B331" s="45" t="s">
         <v>625</v>
       </c>
-      <c r="C331" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D331" s="4">
+      <c r="C331" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D331" s="47">
         <v>20</v>
       </c>
-      <c r="E331" s="4">
+      <c r="E331" s="47">
         <v>133</v>
       </c>
-      <c r="F331" s="15">
+      <c r="F331" s="49">
         <f t="shared" si="5"/>
         <v>2660</v>
       </c>
-      <c r="G331" s="8">
+      <c r="G331" s="46">
         <v>694</v>
       </c>
-      <c r="H331" s="5" t="s">
+      <c r="H331" s="50" t="s">
         <v>338</v>
       </c>
-      <c r="I331" s="8" t="s">
+      <c r="I331" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J331" s="8">
+      <c r="J331" s="46">
         <v>6183</v>
       </c>
-      <c r="K331" s="5" t="s">
+      <c r="K331" s="50" t="s">
         <v>617</v>
       </c>
     </row>
@@ -20820,7 +20873,7 @@
         <v>10965</v>
       </c>
       <c r="F360" s="15">
-        <f t="shared" si="5"/>
+        <f>E360*D360</f>
         <v>21930</v>
       </c>
       <c r="G360" s="8">
@@ -20875,183 +20928,183 @@
         <v>46298</v>
       </c>
     </row>
-    <row r="362" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A362" s="42" t="s">
+    <row r="362" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A362" s="44" t="s">
         <v>680</v>
       </c>
-      <c r="B362" s="25" t="s">
+      <c r="B362" s="45" t="s">
         <v>681</v>
       </c>
-      <c r="C362" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D362" s="4">
+      <c r="C362" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D362" s="47">
         <v>20</v>
       </c>
-      <c r="E362" s="4">
+      <c r="E362" s="47">
         <v>4068.1280000000002</v>
       </c>
-      <c r="F362" s="15">
+      <c r="F362" s="49">
         <f t="shared" si="5"/>
         <v>81362.559999999998</v>
       </c>
-      <c r="G362" s="8">
+      <c r="G362" s="46">
         <v>701</v>
       </c>
-      <c r="H362" s="5" t="s">
+      <c r="H362" s="50" t="s">
         <v>671</v>
       </c>
-      <c r="I362" s="8" t="s">
+      <c r="I362" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J362" s="8">
+      <c r="J362" s="46">
         <v>6190</v>
       </c>
-      <c r="K362" s="5">
+      <c r="K362" s="50">
         <v>46298</v>
       </c>
     </row>
-    <row r="363" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="42" t="s">
+    <row r="363" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A363" s="44" t="s">
         <v>682</v>
       </c>
-      <c r="B363" s="25" t="s">
+      <c r="B363" s="45" t="s">
         <v>683</v>
       </c>
-      <c r="C363" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D363" s="4">
+      <c r="C363" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D363" s="47">
         <v>55</v>
       </c>
-      <c r="E363" s="4">
+      <c r="E363" s="47">
         <v>4068.1280000000002</v>
       </c>
-      <c r="F363" s="15">
+      <c r="F363" s="49">
         <f t="shared" si="5"/>
         <v>223747.04</v>
       </c>
-      <c r="G363" s="8">
+      <c r="G363" s="46">
         <v>701</v>
       </c>
-      <c r="H363" s="5" t="s">
+      <c r="H363" s="50" t="s">
         <v>671</v>
       </c>
-      <c r="I363" s="8" t="s">
+      <c r="I363" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J363" s="8">
+      <c r="J363" s="46">
         <v>6190</v>
       </c>
-      <c r="K363" s="5">
+      <c r="K363" s="50">
         <v>46298</v>
       </c>
     </row>
-    <row r="364" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A364" s="42" t="s">
+    <row r="364" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A364" s="44" t="s">
         <v>684</v>
       </c>
-      <c r="B364" s="25" t="s">
+      <c r="B364" s="45" t="s">
         <v>685</v>
       </c>
-      <c r="C364" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D364" s="4">
+      <c r="C364" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D364" s="47">
         <v>40</v>
       </c>
-      <c r="E364" s="4">
+      <c r="E364" s="47">
         <v>4068.1280000000002</v>
       </c>
-      <c r="F364" s="15">
+      <c r="F364" s="49">
         <f t="shared" si="5"/>
         <v>162725.12</v>
       </c>
-      <c r="G364" s="8">
+      <c r="G364" s="46">
         <v>701</v>
       </c>
-      <c r="H364" s="5" t="s">
+      <c r="H364" s="50" t="s">
         <v>671</v>
       </c>
-      <c r="I364" s="8" t="s">
+      <c r="I364" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J364" s="8">
+      <c r="J364" s="46">
         <v>6190</v>
       </c>
-      <c r="K364" s="5">
+      <c r="K364" s="50">
         <v>46298</v>
       </c>
     </row>
-    <row r="365" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A365" s="42" t="s">
+    <row r="365" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A365" s="44" t="s">
         <v>621</v>
       </c>
-      <c r="B365" s="25" t="s">
+      <c r="B365" s="45" t="s">
         <v>686</v>
       </c>
-      <c r="C365" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D365" s="4">
+      <c r="C365" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D365" s="47">
         <v>55</v>
       </c>
-      <c r="E365" s="4">
+      <c r="E365" s="47">
         <v>4068.1280000000002</v>
       </c>
-      <c r="F365" s="15">
+      <c r="F365" s="49">
         <f t="shared" si="5"/>
         <v>223747.04</v>
       </c>
-      <c r="G365" s="8">
+      <c r="G365" s="46">
         <v>701</v>
       </c>
-      <c r="H365" s="5" t="s">
+      <c r="H365" s="50" t="s">
         <v>671</v>
       </c>
-      <c r="I365" s="8" t="s">
+      <c r="I365" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J365" s="8">
+      <c r="J365" s="46">
         <v>6190</v>
       </c>
-      <c r="K365" s="5">
+      <c r="K365" s="50">
         <v>46298</v>
       </c>
     </row>
-    <row r="366" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A366" s="42" t="s">
+    <row r="366" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A366" s="44" t="s">
         <v>562</v>
       </c>
-      <c r="B366" s="25" t="s">
+      <c r="B366" s="45" t="s">
         <v>687</v>
       </c>
-      <c r="C366" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D366" s="4">
+      <c r="C366" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D366" s="47">
         <v>24</v>
       </c>
-      <c r="E366" s="4">
+      <c r="E366" s="47">
         <v>4068.1280000000002</v>
       </c>
-      <c r="F366" s="15">
+      <c r="F366" s="49">
         <f t="shared" si="5"/>
         <v>97635.072</v>
       </c>
-      <c r="G366" s="8">
+      <c r="G366" s="46">
         <v>701</v>
       </c>
-      <c r="H366" s="5" t="s">
+      <c r="H366" s="50" t="s">
         <v>671</v>
       </c>
-      <c r="I366" s="8" t="s">
+      <c r="I366" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="J366" s="8">
+      <c r="J366" s="46">
         <v>6190</v>
       </c>
-      <c r="K366" s="5">
+      <c r="K366" s="50">
         <v>46298</v>
       </c>
     </row>
@@ -41955,111 +42008,111 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="948" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A948" s="42" t="s">
+    <row r="948" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A948" s="52" t="s">
         <v>1520</v>
       </c>
-      <c r="B948" s="25" t="s">
+      <c r="B948" s="53" t="s">
         <v>1521</v>
       </c>
-      <c r="C948" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D948" s="4">
+      <c r="C948" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D948" s="55">
         <v>4</v>
       </c>
-      <c r="E948" s="4">
+      <c r="E948" s="55">
         <v>400</v>
       </c>
-      <c r="F948" s="15">
+      <c r="F948" s="56">
         <f t="shared" si="14"/>
         <v>1600</v>
       </c>
-      <c r="G948" s="8">
+      <c r="G948" s="54">
         <v>12324</v>
       </c>
-      <c r="H948" s="5">
+      <c r="H948" s="57">
         <v>46360</v>
       </c>
-      <c r="I948" s="8" t="s">
+      <c r="I948" s="54" t="s">
         <v>488</v>
       </c>
-      <c r="J948" s="8">
+      <c r="J948" s="54">
         <v>6311</v>
       </c>
-      <c r="K948" s="5" t="s">
+      <c r="K948" s="57" t="s">
         <v>1465</v>
       </c>
     </row>
-    <row r="949" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A949" s="42" t="s">
+    <row r="949" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A949" s="52" t="s">
         <v>1522</v>
       </c>
-      <c r="B949" s="25" t="s">
+      <c r="B949" s="53" t="s">
         <v>1523</v>
       </c>
-      <c r="C949" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D949" s="4">
+      <c r="C949" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D949" s="55">
         <v>18</v>
       </c>
-      <c r="E949" s="4">
+      <c r="E949" s="55">
         <v>10</v>
       </c>
-      <c r="F949" s="15">
+      <c r="F949" s="56">
         <f t="shared" si="14"/>
         <v>180</v>
       </c>
-      <c r="G949" s="8">
+      <c r="G949" s="54">
         <v>12324</v>
       </c>
-      <c r="H949" s="5">
+      <c r="H949" s="57">
         <v>46360</v>
       </c>
-      <c r="I949" s="8" t="s">
+      <c r="I949" s="54" t="s">
         <v>488</v>
       </c>
-      <c r="J949" s="8">
+      <c r="J949" s="54">
         <v>6311</v>
       </c>
-      <c r="K949" s="5" t="s">
+      <c r="K949" s="57" t="s">
         <v>1465</v>
       </c>
     </row>
-    <row r="950" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A950" s="42" t="s">
+    <row r="950" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A950" s="52" t="s">
         <v>1524</v>
       </c>
-      <c r="B950" s="25" t="s">
+      <c r="B950" s="53" t="s">
         <v>1525</v>
       </c>
-      <c r="C950" s="8" t="s">
+      <c r="C950" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="D950" s="4">
-        <v>188</v>
-      </c>
-      <c r="E950" s="4">
+      <c r="D950" s="55">
+        <v>1.88</v>
+      </c>
+      <c r="E950" s="55">
         <v>260</v>
       </c>
-      <c r="F950" s="15">
+      <c r="F950" s="56">
         <f t="shared" si="14"/>
-        <v>48880</v>
-      </c>
-      <c r="G950" s="8">
+        <v>488.79999999999995</v>
+      </c>
+      <c r="G950" s="54">
         <v>12324</v>
       </c>
-      <c r="H950" s="5">
+      <c r="H950" s="57">
         <v>46360</v>
       </c>
-      <c r="I950" s="8" t="s">
+      <c r="I950" s="54" t="s">
         <v>488</v>
       </c>
-      <c r="J950" s="8">
+      <c r="J950" s="54">
         <v>6311</v>
       </c>
-      <c r="K950" s="5" t="s">
+      <c r="K950" s="57" t="s">
         <v>1465</v>
       </c>
     </row>
@@ -45119,507 +45172,507 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="1036" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1036" s="42" t="s">
+    <row r="1036" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1036" s="44" t="s">
         <v>1617</v>
       </c>
-      <c r="B1036" s="40" t="s">
+      <c r="B1036" s="59" t="s">
         <v>1618</v>
       </c>
-      <c r="C1036" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1036" s="4">
+      <c r="C1036" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1036" s="47">
         <v>10</v>
       </c>
-      <c r="E1036" s="4">
+      <c r="E1036" s="47">
         <v>550</v>
       </c>
-      <c r="F1036" s="15">
+      <c r="F1036" s="49">
         <f t="shared" si="16"/>
         <v>5500</v>
       </c>
-      <c r="G1036" s="8" t="s">
+      <c r="G1036" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1036" s="5" t="s">
+      <c r="H1036" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1036" s="8" t="s">
+      <c r="I1036" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1036" s="8">
+      <c r="J1036" s="46">
         <v>6333</v>
       </c>
-      <c r="K1036" s="5">
+      <c r="K1036" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1037" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1037" s="42" t="s">
+    <row r="1037" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1037" s="44" t="s">
         <v>1172</v>
       </c>
-      <c r="B1037" s="25" t="s">
+      <c r="B1037" s="45" t="s">
         <v>1619</v>
       </c>
-      <c r="C1037" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1037" s="4">
+      <c r="C1037" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1037" s="47">
         <v>24</v>
       </c>
-      <c r="E1037" s="4">
+      <c r="E1037" s="47">
         <v>1000</v>
       </c>
-      <c r="F1037" s="15">
+      <c r="F1037" s="49">
         <f t="shared" si="16"/>
         <v>24000</v>
       </c>
-      <c r="G1037" s="8" t="s">
+      <c r="G1037" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1037" s="5" t="s">
+      <c r="H1037" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1037" s="8" t="s">
+      <c r="I1037" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1037" s="8">
+      <c r="J1037" s="46">
         <v>6333</v>
       </c>
-      <c r="K1037" s="5">
+      <c r="K1037" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1038" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1038" s="42" t="s">
+    <row r="1038" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1038" s="44" t="s">
         <v>1620</v>
       </c>
-      <c r="B1038" s="25" t="s">
+      <c r="B1038" s="45" t="s">
         <v>1621</v>
       </c>
-      <c r="C1038" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1038" s="4">
+      <c r="C1038" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1038" s="47">
         <v>50</v>
       </c>
-      <c r="E1038" s="4">
+      <c r="E1038" s="47">
         <v>60</v>
       </c>
-      <c r="F1038" s="15">
+      <c r="F1038" s="49">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
-      <c r="G1038" s="8" t="s">
+      <c r="G1038" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1038" s="5" t="s">
+      <c r="H1038" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1038" s="8" t="s">
+      <c r="I1038" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1038" s="8">
+      <c r="J1038" s="46">
         <v>6333</v>
       </c>
-      <c r="K1038" s="5">
+      <c r="K1038" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1039" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1039" s="42" t="s">
+    <row r="1039" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1039" s="44" t="s">
         <v>1241</v>
       </c>
-      <c r="B1039" s="25" t="s">
+      <c r="B1039" s="45" t="s">
         <v>1249</v>
       </c>
-      <c r="C1039" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1039" s="4">
+      <c r="C1039" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1039" s="47">
         <v>1</v>
       </c>
-      <c r="E1039" s="4">
+      <c r="E1039" s="47">
         <v>2300</v>
       </c>
-      <c r="F1039" s="15">
+      <c r="F1039" s="49">
         <f t="shared" si="16"/>
         <v>2300</v>
       </c>
-      <c r="G1039" s="8" t="s">
+      <c r="G1039" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1039" s="5" t="s">
+      <c r="H1039" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1039" s="8" t="s">
+      <c r="I1039" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1039" s="8">
+      <c r="J1039" s="46">
         <v>6333</v>
       </c>
-      <c r="K1039" s="5">
+      <c r="K1039" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1040" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1040" s="42" t="s">
+    <row r="1040" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1040" s="44" t="s">
         <v>1174</v>
       </c>
-      <c r="B1040" s="25" t="s">
+      <c r="B1040" s="45" t="s">
         <v>1175</v>
       </c>
-      <c r="C1040" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1040" s="4">
+      <c r="C1040" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1040" s="47">
         <v>2</v>
       </c>
-      <c r="E1040" s="4">
+      <c r="E1040" s="47">
         <v>5500</v>
       </c>
-      <c r="F1040" s="15">
+      <c r="F1040" s="49">
         <f t="shared" si="16"/>
         <v>11000</v>
       </c>
-      <c r="G1040" s="8" t="s">
+      <c r="G1040" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1040" s="5" t="s">
+      <c r="H1040" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1040" s="8" t="s">
+      <c r="I1040" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1040" s="8">
+      <c r="J1040" s="46">
         <v>6333</v>
       </c>
-      <c r="K1040" s="5">
+      <c r="K1040" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1041" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1041" s="42" t="s">
+    <row r="1041" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1041" s="44" t="s">
         <v>1176</v>
       </c>
-      <c r="B1041" s="25" t="s">
+      <c r="B1041" s="45" t="s">
         <v>1247</v>
       </c>
-      <c r="C1041" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1041" s="4">
+      <c r="C1041" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1041" s="47">
         <v>2</v>
       </c>
-      <c r="E1041" s="4">
+      <c r="E1041" s="47">
         <v>2500</v>
       </c>
-      <c r="F1041" s="15">
+      <c r="F1041" s="49">
         <f t="shared" si="16"/>
         <v>5000</v>
       </c>
-      <c r="G1041" s="8" t="s">
+      <c r="G1041" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1041" s="5" t="s">
+      <c r="H1041" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1041" s="8" t="s">
+      <c r="I1041" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1041" s="8">
+      <c r="J1041" s="46">
         <v>6333</v>
       </c>
-      <c r="K1041" s="5">
+      <c r="K1041" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1042" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1042" s="42" t="s">
+    <row r="1042" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1042" s="44" t="s">
         <v>1178</v>
       </c>
-      <c r="B1042" s="25" t="s">
+      <c r="B1042" s="45" t="s">
         <v>1179</v>
       </c>
-      <c r="C1042" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1042" s="4">
+      <c r="C1042" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1042" s="47">
         <v>2</v>
       </c>
-      <c r="E1042" s="4">
+      <c r="E1042" s="47">
         <v>1500</v>
       </c>
-      <c r="F1042" s="15">
+      <c r="F1042" s="49">
         <f t="shared" si="16"/>
         <v>3000</v>
       </c>
-      <c r="G1042" s="8" t="s">
+      <c r="G1042" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1042" s="5" t="s">
+      <c r="H1042" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1042" s="8" t="s">
+      <c r="I1042" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1042" s="8">
+      <c r="J1042" s="46">
         <v>6333</v>
       </c>
-      <c r="K1042" s="5">
+      <c r="K1042" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1043" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1043" s="42" t="s">
+    <row r="1043" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1043" s="44" t="s">
         <v>1622</v>
       </c>
-      <c r="B1043" s="25" t="s">
+      <c r="B1043" s="45" t="s">
         <v>1623</v>
       </c>
-      <c r="C1043" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1043" s="4">
+      <c r="C1043" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1043" s="47">
         <v>1</v>
       </c>
-      <c r="E1043" s="4">
+      <c r="E1043" s="47">
         <v>1500</v>
       </c>
-      <c r="F1043" s="15">
+      <c r="F1043" s="49">
         <f t="shared" si="16"/>
         <v>1500</v>
       </c>
-      <c r="G1043" s="8" t="s">
+      <c r="G1043" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1043" s="5" t="s">
+      <c r="H1043" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1043" s="8" t="s">
+      <c r="I1043" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1043" s="8">
+      <c r="J1043" s="46">
         <v>6333</v>
       </c>
-      <c r="K1043" s="5">
+      <c r="K1043" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1044" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1044" s="42" t="s">
+    <row r="1044" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1044" s="44" t="s">
         <v>1236</v>
       </c>
-      <c r="B1044" s="25" t="s">
+      <c r="B1044" s="45" t="s">
         <v>1624</v>
       </c>
-      <c r="C1044" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1044" s="4">
+      <c r="C1044" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1044" s="47">
         <v>3300</v>
       </c>
-      <c r="E1044" s="4">
+      <c r="E1044" s="47">
         <v>10</v>
       </c>
-      <c r="F1044" s="15">
+      <c r="F1044" s="49">
         <f t="shared" si="16"/>
         <v>33000</v>
       </c>
-      <c r="G1044" s="8" t="s">
+      <c r="G1044" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1044" s="5" t="s">
+      <c r="H1044" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1044" s="8" t="s">
+      <c r="I1044" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1044" s="8">
+      <c r="J1044" s="46">
         <v>6333</v>
       </c>
-      <c r="K1044" s="5">
+      <c r="K1044" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1045" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1045" s="42" t="s">
+    <row r="1045" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1045" s="44" t="s">
         <v>1224</v>
       </c>
-      <c r="B1045" s="25" t="s">
+      <c r="B1045" s="45" t="s">
         <v>1625</v>
       </c>
-      <c r="C1045" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1045" s="4">
+      <c r="C1045" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1045" s="47">
         <v>5</v>
       </c>
-      <c r="E1045" s="4">
+      <c r="E1045" s="47">
         <v>350</v>
       </c>
-      <c r="F1045" s="15">
+      <c r="F1045" s="49">
         <f t="shared" si="16"/>
         <v>1750</v>
       </c>
-      <c r="G1045" s="8" t="s">
+      <c r="G1045" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1045" s="5" t="s">
+      <c r="H1045" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1045" s="8" t="s">
+      <c r="I1045" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1045" s="8">
+      <c r="J1045" s="46">
         <v>6333</v>
       </c>
-      <c r="K1045" s="5">
+      <c r="K1045" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1046" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1046" s="42" t="s">
+    <row r="1046" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1046" s="44" t="s">
         <v>1234</v>
       </c>
-      <c r="B1046" s="25" t="s">
+      <c r="B1046" s="45" t="s">
         <v>1235</v>
       </c>
-      <c r="C1046" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1046" s="4">
+      <c r="C1046" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1046" s="47">
         <v>5</v>
       </c>
-      <c r="E1046" s="4">
+      <c r="E1046" s="47">
         <v>100</v>
       </c>
-      <c r="F1046" s="15">
+      <c r="F1046" s="49">
         <f t="shared" si="16"/>
         <v>500</v>
       </c>
-      <c r="G1046" s="8" t="s">
+      <c r="G1046" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1046" s="5" t="s">
+      <c r="H1046" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1046" s="8" t="s">
+      <c r="I1046" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1046" s="8">
+      <c r="J1046" s="46">
         <v>6333</v>
       </c>
-      <c r="K1046" s="5">
+      <c r="K1046" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1047" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1047" s="42" t="s">
+    <row r="1047" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1047" s="44" t="s">
         <v>1220</v>
       </c>
-      <c r="B1047" s="25" t="s">
+      <c r="B1047" s="45" t="s">
         <v>1221</v>
       </c>
-      <c r="C1047" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1047" s="4">
+      <c r="C1047" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1047" s="47">
         <v>5</v>
       </c>
-      <c r="E1047" s="4">
+      <c r="E1047" s="47">
         <v>100</v>
       </c>
-      <c r="F1047" s="15">
+      <c r="F1047" s="49">
         <f t="shared" si="16"/>
         <v>500</v>
       </c>
-      <c r="G1047" s="8" t="s">
+      <c r="G1047" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1047" s="5" t="s">
+      <c r="H1047" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1047" s="8" t="s">
+      <c r="I1047" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1047" s="8">
+      <c r="J1047" s="46">
         <v>6333</v>
       </c>
-      <c r="K1047" s="5">
+      <c r="K1047" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1048" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1048" s="42" t="s">
+    <row r="1048" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1048" s="44" t="s">
         <v>1626</v>
       </c>
-      <c r="B1048" s="25" t="s">
+      <c r="B1048" s="45" t="s">
         <v>1627</v>
       </c>
-      <c r="C1048" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1048" s="4">
+      <c r="C1048" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1048" s="47">
         <v>1</v>
       </c>
-      <c r="E1048" s="29">
+      <c r="E1048" s="48">
         <v>25100</v>
       </c>
-      <c r="F1048" s="15">
+      <c r="F1048" s="49">
         <f t="shared" si="16"/>
         <v>25100</v>
       </c>
-      <c r="G1048" s="8" t="s">
+      <c r="G1048" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1048" s="5" t="s">
+      <c r="H1048" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1048" s="8" t="s">
+      <c r="I1048" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1048" s="8">
+      <c r="J1048" s="46">
         <v>6333</v>
       </c>
-      <c r="K1048" s="5">
+      <c r="K1048" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1049" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1049" s="42" t="s">
+    <row r="1049" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1049" s="44" t="s">
         <v>1628</v>
       </c>
-      <c r="B1049" s="25" t="s">
+      <c r="B1049" s="45" t="s">
         <v>1629</v>
       </c>
-      <c r="C1049" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1049" s="4">
+      <c r="C1049" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1049" s="47">
         <v>10</v>
       </c>
-      <c r="E1049" s="4">
+      <c r="E1049" s="47">
         <v>150</v>
       </c>
-      <c r="F1049" s="15">
+      <c r="F1049" s="49">
         <f t="shared" si="16"/>
         <v>1500</v>
       </c>
-      <c r="G1049" s="8" t="s">
+      <c r="G1049" s="46" t="s">
         <v>2304</v>
       </c>
-      <c r="H1049" s="5" t="s">
+      <c r="H1049" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1049" s="8" t="s">
+      <c r="I1049" s="46" t="s">
         <v>2349</v>
       </c>
-      <c r="J1049" s="8">
+      <c r="J1049" s="46">
         <v>6333</v>
       </c>
-      <c r="K1049" s="5">
+      <c r="K1049" s="50">
         <v>46117</v>
       </c>
     </row>
@@ -46235,147 +46288,147 @@
         <v>46117</v>
       </c>
     </row>
-    <row r="1067" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1067" s="42" t="s">
+    <row r="1067" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1067" s="44" t="s">
         <v>1648</v>
       </c>
-      <c r="B1067" s="25" t="s">
+      <c r="B1067" s="45" t="s">
         <v>1649</v>
       </c>
-      <c r="C1067" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1067" s="4">
+      <c r="C1067" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1067" s="47">
         <v>1</v>
       </c>
-      <c r="E1067" s="4">
+      <c r="E1067" s="47">
         <v>1429</v>
       </c>
-      <c r="F1067" s="15">
+      <c r="F1067" s="49">
         <f t="shared" si="16"/>
         <v>1429</v>
       </c>
-      <c r="G1067" s="8" t="s">
+      <c r="G1067" s="46" t="s">
         <v>2328</v>
       </c>
-      <c r="H1067" s="5" t="s">
+      <c r="H1067" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1067" s="8" t="s">
+      <c r="I1067" s="46" t="s">
         <v>1650</v>
       </c>
-      <c r="J1067" s="8">
+      <c r="J1067" s="46">
         <v>6337</v>
       </c>
-      <c r="K1067" s="5">
+      <c r="K1067" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1068" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1068" s="42" t="s">
+    <row r="1068" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1068" s="44" t="s">
         <v>1651</v>
       </c>
-      <c r="B1068" s="25" t="s">
+      <c r="B1068" s="45" t="s">
         <v>1652</v>
       </c>
-      <c r="C1068" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1068" s="4">
+      <c r="C1068" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1068" s="47">
         <v>1</v>
       </c>
-      <c r="E1068" s="4">
+      <c r="E1068" s="47">
         <v>3591</v>
       </c>
-      <c r="F1068" s="15">
+      <c r="F1068" s="49">
         <f t="shared" si="16"/>
         <v>3591</v>
       </c>
-      <c r="G1068" s="8" t="s">
+      <c r="G1068" s="46" t="s">
         <v>2328</v>
       </c>
-      <c r="H1068" s="5" t="s">
+      <c r="H1068" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1068" s="8" t="s">
+      <c r="I1068" s="46" t="s">
         <v>1650</v>
       </c>
-      <c r="J1068" s="8">
+      <c r="J1068" s="46">
         <v>6337</v>
       </c>
-      <c r="K1068" s="5">
+      <c r="K1068" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1069" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1069" s="42" t="s">
+    <row r="1069" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1069" s="44" t="s">
         <v>1653</v>
       </c>
-      <c r="B1069" s="25" t="s">
+      <c r="B1069" s="45" t="s">
         <v>1654</v>
       </c>
-      <c r="C1069" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1069" s="4">
+      <c r="C1069" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1069" s="47">
         <v>2</v>
       </c>
-      <c r="E1069" s="29">
+      <c r="E1069" s="48">
         <v>12373</v>
       </c>
-      <c r="F1069" s="15">
+      <c r="F1069" s="49">
         <f t="shared" si="16"/>
         <v>24746</v>
       </c>
-      <c r="G1069" s="8" t="s">
+      <c r="G1069" s="46" t="s">
         <v>2328</v>
       </c>
-      <c r="H1069" s="5" t="s">
+      <c r="H1069" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1069" s="8" t="s">
+      <c r="I1069" s="46" t="s">
         <v>1650</v>
       </c>
-      <c r="J1069" s="8">
+      <c r="J1069" s="46">
         <v>6337</v>
       </c>
-      <c r="K1069" s="5">
+      <c r="K1069" s="50">
         <v>46117</v>
       </c>
     </row>
-    <row r="1070" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1070" s="42" t="s">
+    <row r="1070" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1070" s="44" t="s">
         <v>1655</v>
       </c>
-      <c r="B1070" s="25" t="s">
+      <c r="B1070" s="45" t="s">
         <v>1656</v>
       </c>
-      <c r="C1070" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1070" s="4">
+      <c r="C1070" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1070" s="47">
         <v>1</v>
       </c>
-      <c r="E1070" s="4">
+      <c r="E1070" s="47">
         <v>856</v>
       </c>
-      <c r="F1070" s="15">
+      <c r="F1070" s="49">
         <f t="shared" si="16"/>
         <v>856</v>
       </c>
-      <c r="G1070" s="8" t="s">
+      <c r="G1070" s="46" t="s">
         <v>2328</v>
       </c>
-      <c r="H1070" s="5" t="s">
+      <c r="H1070" s="50" t="s">
         <v>1612</v>
       </c>
-      <c r="I1070" s="8" t="s">
+      <c r="I1070" s="46" t="s">
         <v>1650</v>
       </c>
-      <c r="J1070" s="8">
+      <c r="J1070" s="46">
         <v>6337</v>
       </c>
-      <c r="K1070" s="5">
+      <c r="K1070" s="50">
         <v>46117</v>
       </c>
     </row>
@@ -47745,183 +47798,183 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="1109" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1109" s="42" t="s">
+    <row r="1109" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1109" s="52" t="s">
         <v>211</v>
       </c>
-      <c r="B1109" s="25" t="s">
+      <c r="B1109" s="53" t="s">
         <v>1717</v>
       </c>
-      <c r="C1109" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1109" s="4">
+      <c r="C1109" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1109" s="55">
         <v>10</v>
       </c>
-      <c r="E1109" s="4">
+      <c r="E1109" s="55">
         <v>134.55000000000001</v>
       </c>
-      <c r="F1109" s="15">
-        <f t="shared" si="17"/>
+      <c r="F1109" s="56">
+        <f>E1109*D1109</f>
         <v>1345.5</v>
       </c>
-      <c r="G1109" s="8">
+      <c r="G1109" s="54">
         <v>93</v>
       </c>
-      <c r="H1109" s="5" t="s">
+      <c r="H1109" s="57" t="s">
         <v>1718</v>
       </c>
-      <c r="I1109" s="8" t="s">
+      <c r="I1109" s="54" t="s">
         <v>339</v>
       </c>
-      <c r="J1109" s="8">
+      <c r="J1109" s="54">
         <v>6348</v>
       </c>
-      <c r="K1109" s="5">
+      <c r="K1109" s="57">
         <v>46147</v>
       </c>
     </row>
-    <row r="1110" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1110" s="42" t="s">
+    <row r="1110" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1110" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="B1110" s="25" t="s">
+      <c r="B1110" s="53" t="s">
         <v>1147</v>
       </c>
-      <c r="C1110" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1110" s="4">
+      <c r="C1110" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1110" s="55">
         <v>10</v>
       </c>
-      <c r="E1110" s="4">
+      <c r="E1110" s="55">
         <v>526.5</v>
       </c>
-      <c r="F1110" s="15">
+      <c r="F1110" s="56">
         <f t="shared" si="17"/>
         <v>5265</v>
       </c>
-      <c r="G1110" s="8">
+      <c r="G1110" s="54">
         <v>93</v>
       </c>
-      <c r="H1110" s="5" t="s">
+      <c r="H1110" s="57" t="s">
         <v>1718</v>
       </c>
-      <c r="I1110" s="8" t="s">
+      <c r="I1110" s="54" t="s">
         <v>339</v>
       </c>
-      <c r="J1110" s="8">
+      <c r="J1110" s="54">
         <v>6348</v>
       </c>
-      <c r="K1110" s="5">
+      <c r="K1110" s="57">
         <v>46147</v>
       </c>
     </row>
-    <row r="1111" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1111" s="42" t="s">
+    <row r="1111" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1111" s="52" t="s">
         <v>434</v>
       </c>
-      <c r="B1111" s="25" t="s">
+      <c r="B1111" s="53" t="s">
         <v>1719</v>
       </c>
-      <c r="C1111" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1111" s="4">
+      <c r="C1111" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1111" s="55">
         <v>2</v>
       </c>
-      <c r="E1111" s="4">
+      <c r="E1111" s="55">
         <v>234</v>
       </c>
-      <c r="F1111" s="15">
+      <c r="F1111" s="56">
         <f t="shared" si="17"/>
         <v>468</v>
       </c>
-      <c r="G1111" s="8">
+      <c r="G1111" s="54">
         <v>93</v>
       </c>
-      <c r="H1111" s="5" t="s">
+      <c r="H1111" s="57" t="s">
         <v>1718</v>
       </c>
-      <c r="I1111" s="8" t="s">
+      <c r="I1111" s="54" t="s">
         <v>339</v>
       </c>
-      <c r="J1111" s="8">
+      <c r="J1111" s="54">
         <v>6348</v>
       </c>
-      <c r="K1111" s="5">
+      <c r="K1111" s="57">
         <v>46147</v>
       </c>
     </row>
-    <row r="1112" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1112" s="42" t="s">
+    <row r="1112" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1112" s="52" t="s">
         <v>333</v>
       </c>
-      <c r="B1112" s="25" t="s">
+      <c r="B1112" s="53" t="s">
         <v>1720</v>
       </c>
-      <c r="C1112" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1112" s="4">
+      <c r="C1112" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1112" s="55">
         <v>1</v>
       </c>
-      <c r="E1112" s="4">
+      <c r="E1112" s="55">
         <v>82</v>
       </c>
-      <c r="F1112" s="15">
+      <c r="F1112" s="56">
         <f t="shared" si="17"/>
         <v>82</v>
       </c>
-      <c r="G1112" s="8">
+      <c r="G1112" s="54">
         <v>93</v>
       </c>
-      <c r="H1112" s="5" t="s">
+      <c r="H1112" s="57" t="s">
         <v>1721</v>
       </c>
-      <c r="I1112" s="8" t="s">
+      <c r="I1112" s="54" t="s">
         <v>339</v>
       </c>
-      <c r="J1112" s="8">
+      <c r="J1112" s="54">
         <v>6348</v>
       </c>
-      <c r="K1112" s="5">
+      <c r="K1112" s="57">
         <v>46147</v>
       </c>
     </row>
-    <row r="1113" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1113" s="42" t="s">
+    <row r="1113" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1113" s="52" t="s">
         <v>1722</v>
       </c>
-      <c r="B1113" s="25" t="s">
+      <c r="B1113" s="53" t="s">
         <v>1723</v>
       </c>
-      <c r="C1113" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1113" s="4">
+      <c r="C1113" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1113" s="55">
         <v>5</v>
       </c>
-      <c r="E1113" s="4">
+      <c r="E1113" s="55">
+        <v>1755</v>
+      </c>
+      <c r="F1113" s="56">
+        <f t="shared" si="17"/>
         <v>8775</v>
       </c>
-      <c r="F1113" s="15">
-        <f t="shared" si="17"/>
-        <v>43875</v>
-      </c>
-      <c r="G1113" s="8">
+      <c r="G1113" s="54">
         <v>93</v>
       </c>
-      <c r="H1113" s="5" t="s">
+      <c r="H1113" s="57" t="s">
         <v>1721</v>
       </c>
-      <c r="I1113" s="8" t="s">
+      <c r="I1113" s="54" t="s">
         <v>339</v>
       </c>
-      <c r="J1113" s="8">
+      <c r="J1113" s="54">
         <v>6348</v>
       </c>
-      <c r="K1113" s="5">
+      <c r="K1113" s="57">
         <v>46147</v>
       </c>
     </row>
@@ -50694,327 +50747,327 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="1191" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1191" s="42" t="s">
+    <row r="1191" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1191" s="52" t="s">
         <v>204</v>
       </c>
-      <c r="B1191" s="25" t="s">
+      <c r="B1191" s="53" t="s">
         <v>1795</v>
       </c>
-      <c r="C1191" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1191" s="4">
+      <c r="C1191" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1191" s="55">
         <v>5</v>
       </c>
-      <c r="E1191" s="4">
+      <c r="E1191" s="55">
         <v>250</v>
       </c>
-      <c r="F1191" s="15">
+      <c r="F1191" s="56">
         <f t="shared" si="19"/>
         <v>1250</v>
       </c>
-      <c r="G1191" s="8">
+      <c r="G1191" s="54">
         <v>5024</v>
       </c>
-      <c r="H1191" s="5" t="s">
+      <c r="H1191" s="57" t="s">
         <v>1796</v>
       </c>
-      <c r="I1191" s="8" t="s">
+      <c r="I1191" s="54" t="s">
         <v>2345</v>
       </c>
-      <c r="J1191" s="8">
+      <c r="J1191" s="54">
         <v>6372</v>
       </c>
-      <c r="K1191" s="5">
+      <c r="K1191" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1192" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1192" s="42" t="s">
+    <row r="1192" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1192" s="52" t="s">
         <v>1797</v>
       </c>
-      <c r="B1192" s="25" t="s">
+      <c r="B1192" s="53" t="s">
         <v>1798</v>
       </c>
-      <c r="C1192" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1192" s="4">
+      <c r="C1192" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1192" s="55">
         <v>30</v>
       </c>
-      <c r="E1192" s="4">
+      <c r="E1192" s="55">
         <v>50</v>
       </c>
-      <c r="F1192" s="15">
+      <c r="F1192" s="56">
         <f t="shared" si="19"/>
         <v>1500</v>
       </c>
-      <c r="G1192" s="8">
+      <c r="G1192" s="54">
         <v>5024</v>
       </c>
-      <c r="H1192" s="5" t="s">
+      <c r="H1192" s="57" t="s">
         <v>1796</v>
       </c>
-      <c r="I1192" s="8" t="s">
+      <c r="I1192" s="54" t="s">
         <v>2345</v>
       </c>
-      <c r="J1192" s="8">
+      <c r="J1192" s="54">
         <v>6372</v>
       </c>
-      <c r="K1192" s="5">
+      <c r="K1192" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1193" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1193" s="42" t="s">
+    <row r="1193" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1193" s="52" t="s">
         <v>331</v>
       </c>
-      <c r="B1193" s="25" t="s">
+      <c r="B1193" s="53" t="s">
         <v>171</v>
       </c>
-      <c r="C1193" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1193" s="4">
+      <c r="C1193" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1193" s="55">
         <v>1</v>
       </c>
-      <c r="E1193" s="4">
+      <c r="E1193" s="55">
         <v>850</v>
       </c>
-      <c r="F1193" s="15">
+      <c r="F1193" s="56">
         <f t="shared" si="19"/>
         <v>850</v>
       </c>
-      <c r="G1193" s="8">
+      <c r="G1193" s="54">
         <v>5024</v>
       </c>
-      <c r="H1193" s="5" t="s">
+      <c r="H1193" s="57" t="s">
         <v>1796</v>
       </c>
-      <c r="I1193" s="8" t="s">
+      <c r="I1193" s="54" t="s">
         <v>2345</v>
       </c>
-      <c r="J1193" s="8">
+      <c r="J1193" s="54">
         <v>6372</v>
       </c>
-      <c r="K1193" s="5">
+      <c r="K1193" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1194" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1194" s="42" t="s">
+    <row r="1194" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1194" s="52" t="s">
         <v>774</v>
       </c>
-      <c r="B1194" s="25" t="s">
+      <c r="B1194" s="53" t="s">
         <v>775</v>
       </c>
-      <c r="C1194" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1194" s="4">
+      <c r="C1194" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1194" s="55">
         <v>90</v>
       </c>
-      <c r="E1194" s="4">
-        <v>530</v>
-      </c>
-      <c r="F1194" s="15">
+      <c r="E1194" s="55">
+        <v>30</v>
+      </c>
+      <c r="F1194" s="56">
         <f t="shared" si="19"/>
-        <v>47700</v>
-      </c>
-      <c r="G1194" s="8">
+        <v>2700</v>
+      </c>
+      <c r="G1194" s="54">
         <v>5024</v>
       </c>
-      <c r="H1194" s="5" t="s">
+      <c r="H1194" s="57" t="s">
         <v>1796</v>
       </c>
-      <c r="I1194" s="8" t="s">
+      <c r="I1194" s="54" t="s">
         <v>2345</v>
       </c>
-      <c r="J1194" s="8">
+      <c r="J1194" s="54">
         <v>6372</v>
       </c>
-      <c r="K1194" s="5">
+      <c r="K1194" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1195" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1195" s="42" t="s">
+    <row r="1195" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1195" s="52" t="s">
         <v>309</v>
       </c>
-      <c r="B1195" s="25" t="s">
+      <c r="B1195" s="53" t="s">
         <v>1799</v>
       </c>
-      <c r="C1195" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1195" s="4">
+      <c r="C1195" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1195" s="55">
         <v>50</v>
       </c>
-      <c r="E1195" s="4">
+      <c r="E1195" s="55">
         <v>27</v>
       </c>
-      <c r="F1195" s="15">
+      <c r="F1195" s="56">
         <f t="shared" si="19"/>
         <v>1350</v>
       </c>
-      <c r="G1195" s="8">
+      <c r="G1195" s="54">
         <v>5024</v>
       </c>
-      <c r="H1195" s="5" t="s">
+      <c r="H1195" s="57" t="s">
         <v>1796</v>
       </c>
-      <c r="I1195" s="8" t="s">
+      <c r="I1195" s="54" t="s">
         <v>2345</v>
       </c>
-      <c r="J1195" s="8">
+      <c r="J1195" s="54">
         <v>6372</v>
       </c>
-      <c r="K1195" s="5">
+      <c r="K1195" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1196" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1196" s="42" t="s">
+    <row r="1196" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1196" s="52" t="s">
         <v>1800</v>
       </c>
-      <c r="B1196" s="25" t="s">
+      <c r="B1196" s="53" t="s">
         <v>1801</v>
       </c>
-      <c r="C1196" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1196" s="4">
+      <c r="C1196" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1196" s="55">
         <v>40</v>
       </c>
-      <c r="E1196" s="4">
+      <c r="E1196" s="55">
         <v>35</v>
       </c>
-      <c r="F1196" s="15">
+      <c r="F1196" s="56">
         <f t="shared" si="19"/>
         <v>1400</v>
       </c>
-      <c r="G1196" s="8">
+      <c r="G1196" s="54">
         <v>5024</v>
       </c>
-      <c r="H1196" s="5" t="s">
+      <c r="H1196" s="57" t="s">
         <v>1796</v>
       </c>
-      <c r="I1196" s="8" t="s">
+      <c r="I1196" s="54" t="s">
         <v>2345</v>
       </c>
-      <c r="J1196" s="8">
+      <c r="J1196" s="54">
         <v>6372</v>
       </c>
-      <c r="K1196" s="5">
+      <c r="K1196" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1197" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1197" s="42" t="s">
+    <row r="1197" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1197" s="52" t="s">
         <v>1802</v>
       </c>
-      <c r="B1197" s="25" t="s">
+      <c r="B1197" s="53" t="s">
         <v>1803</v>
       </c>
-      <c r="C1197" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1197" s="4">
+      <c r="C1197" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1197" s="55">
         <v>2</v>
       </c>
-      <c r="E1197" s="4">
+      <c r="E1197" s="55">
         <v>190</v>
       </c>
-      <c r="F1197" s="15">
+      <c r="F1197" s="56">
         <f t="shared" si="19"/>
         <v>380</v>
       </c>
-      <c r="G1197" s="8">
+      <c r="G1197" s="54">
         <v>5024</v>
       </c>
-      <c r="H1197" s="5" t="s">
+      <c r="H1197" s="57" t="s">
         <v>1796</v>
       </c>
-      <c r="I1197" s="8" t="s">
+      <c r="I1197" s="54" t="s">
         <v>2345</v>
       </c>
-      <c r="J1197" s="8">
+      <c r="J1197" s="54">
         <v>6372</v>
       </c>
-      <c r="K1197" s="5">
+      <c r="K1197" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1198" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1198" s="42" t="s">
+    <row r="1198" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1198" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="B1198" s="25" t="s">
+      <c r="B1198" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="C1198" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1198" s="4">
+      <c r="C1198" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1198" s="55">
         <v>100</v>
       </c>
-      <c r="E1198" s="4">
+      <c r="E1198" s="55">
         <v>20</v>
       </c>
-      <c r="F1198" s="15">
+      <c r="F1198" s="56">
         <f t="shared" si="19"/>
         <v>2000</v>
       </c>
-      <c r="G1198" s="8">
+      <c r="G1198" s="54">
         <v>5024</v>
       </c>
-      <c r="H1198" s="5" t="s">
+      <c r="H1198" s="57" t="s">
         <v>1796</v>
       </c>
-      <c r="I1198" s="8" t="s">
+      <c r="I1198" s="54" t="s">
         <v>2345</v>
       </c>
-      <c r="J1198" s="8">
+      <c r="J1198" s="54">
         <v>6372</v>
       </c>
-      <c r="K1198" s="5">
+      <c r="K1198" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1199" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1199" s="42" t="s">
+    <row r="1199" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1199" s="52" t="s">
         <v>950</v>
       </c>
-      <c r="B1199" s="25" t="s">
+      <c r="B1199" s="53" t="s">
         <v>1804</v>
       </c>
-      <c r="C1199" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1199" s="4">
+      <c r="C1199" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1199" s="55">
         <v>2</v>
       </c>
-      <c r="E1199" s="4">
+      <c r="E1199" s="55">
         <v>1800</v>
       </c>
-      <c r="F1199" s="15">
+      <c r="F1199" s="56">
         <f t="shared" si="19"/>
         <v>3600</v>
       </c>
-      <c r="G1199" s="8">
+      <c r="G1199" s="54">
         <v>5024</v>
       </c>
-      <c r="H1199" s="5" t="s">
+      <c r="H1199" s="57" t="s">
         <v>1796</v>
       </c>
-      <c r="I1199" s="8" t="s">
+      <c r="I1199" s="54" t="s">
         <v>2345</v>
       </c>
-      <c r="J1199" s="8">
+      <c r="J1199" s="54">
         <v>6372</v>
       </c>
-      <c r="K1199" s="5">
+      <c r="K1199" s="57">
         <v>46301</v>
       </c>
     </row>
@@ -52238,147 +52291,147 @@
         <v>46301</v>
       </c>
     </row>
-    <row r="1234" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1234" s="42" t="s">
+    <row r="1234" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1234" s="52" t="s">
         <v>1250</v>
       </c>
-      <c r="B1234" s="25" t="s">
+      <c r="B1234" s="53" t="s">
         <v>1855</v>
       </c>
-      <c r="C1234" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1234" s="4">
+      <c r="C1234" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1234" s="55">
         <v>1</v>
       </c>
-      <c r="E1234" s="4">
+      <c r="E1234" s="55">
         <v>4300</v>
       </c>
-      <c r="F1234" s="15">
+      <c r="F1234" s="56">
         <f t="shared" si="20"/>
         <v>4300</v>
       </c>
-      <c r="G1234" s="8" t="s">
+      <c r="G1234" s="54" t="s">
         <v>2306</v>
       </c>
-      <c r="H1234" s="5" t="s">
+      <c r="H1234" s="57" t="s">
         <v>1856</v>
       </c>
-      <c r="I1234" s="8" t="s">
+      <c r="I1234" s="54" t="s">
         <v>2336</v>
       </c>
-      <c r="J1234" s="8">
+      <c r="J1234" s="54">
         <v>6390</v>
       </c>
-      <c r="K1234" s="5">
+      <c r="K1234" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1235" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1235" s="42" t="s">
+    <row r="1235" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1235" s="52" t="s">
         <v>191</v>
       </c>
-      <c r="B1235" s="25" t="s">
+      <c r="B1235" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="C1235" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1235" s="4">
+      <c r="C1235" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1235" s="55">
         <v>24</v>
       </c>
-      <c r="E1235" s="4">
-        <v>100</v>
-      </c>
-      <c r="F1235" s="15">
+      <c r="E1235" s="55">
+        <v>1000</v>
+      </c>
+      <c r="F1235" s="56">
         <f t="shared" si="20"/>
-        <v>2400</v>
-      </c>
-      <c r="G1235" s="8" t="s">
+        <v>24000</v>
+      </c>
+      <c r="G1235" s="54" t="s">
         <v>2306</v>
       </c>
-      <c r="H1235" s="5" t="s">
+      <c r="H1235" s="57" t="s">
         <v>1856</v>
       </c>
-      <c r="I1235" s="8" t="s">
+      <c r="I1235" s="54" t="s">
         <v>2336</v>
       </c>
-      <c r="J1235" s="8">
+      <c r="J1235" s="54">
         <v>6390</v>
       </c>
-      <c r="K1235" s="5">
+      <c r="K1235" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1236" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1236" s="42" t="s">
+    <row r="1236" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1236" s="52" t="s">
         <v>1170</v>
       </c>
-      <c r="B1236" s="25" t="s">
+      <c r="B1236" s="53" t="s">
         <v>1857</v>
       </c>
-      <c r="C1236" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1236" s="4">
+      <c r="C1236" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1236" s="55">
         <v>50</v>
       </c>
-      <c r="E1236" s="4">
+      <c r="E1236" s="55">
         <v>35</v>
       </c>
-      <c r="F1236" s="15">
+      <c r="F1236" s="56">
         <f t="shared" si="20"/>
         <v>1750</v>
       </c>
-      <c r="G1236" s="8" t="s">
+      <c r="G1236" s="54" t="s">
         <v>2306</v>
       </c>
-      <c r="H1236" s="5" t="s">
+      <c r="H1236" s="57" t="s">
         <v>1856</v>
       </c>
-      <c r="I1236" s="8" t="s">
+      <c r="I1236" s="54" t="s">
         <v>2336</v>
       </c>
-      <c r="J1236" s="8">
+      <c r="J1236" s="54">
         <v>6390</v>
       </c>
-      <c r="K1236" s="5">
+      <c r="K1236" s="57">
         <v>46301</v>
       </c>
     </row>
-    <row r="1237" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1237" s="42" t="s">
+    <row r="1237" spans="1:11" s="58" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1237" s="52" t="s">
         <v>317</v>
       </c>
-      <c r="B1237" s="25" t="s">
+      <c r="B1237" s="53" t="s">
         <v>157</v>
       </c>
-      <c r="C1237" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1237" s="4">
+      <c r="C1237" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1237" s="55">
         <v>12</v>
       </c>
-      <c r="E1237" s="4">
+      <c r="E1237" s="55">
         <v>1000</v>
       </c>
-      <c r="F1237" s="15">
+      <c r="F1237" s="56">
         <f t="shared" si="20"/>
         <v>12000</v>
       </c>
-      <c r="G1237" s="8" t="s">
+      <c r="G1237" s="54" t="s">
         <v>2306</v>
       </c>
-      <c r="H1237" s="5" t="s">
+      <c r="H1237" s="57" t="s">
         <v>1856</v>
       </c>
-      <c r="I1237" s="8" t="s">
+      <c r="I1237" s="54" t="s">
         <v>2336</v>
       </c>
-      <c r="J1237" s="8">
+      <c r="J1237" s="54">
         <v>6390</v>
       </c>
-      <c r="K1237" s="5">
+      <c r="K1237" s="57">
         <v>46301</v>
       </c>
     </row>
@@ -60994,399 +61047,399 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="1478" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1478" s="42" t="s">
+    <row r="1478" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1478" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="B1478" s="25" t="s">
+      <c r="B1478" s="45" t="s">
         <v>2160</v>
       </c>
-      <c r="C1478" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1478" s="4">
+      <c r="C1478" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1478" s="47">
         <v>263</v>
       </c>
-      <c r="E1478" s="4">
+      <c r="E1478" s="47">
         <v>263</v>
       </c>
-      <c r="F1478" s="15">
+      <c r="F1478" s="49">
         <f t="shared" si="23"/>
         <v>69169</v>
       </c>
-      <c r="G1478" s="8">
+      <c r="G1478" s="46">
         <v>131</v>
       </c>
-      <c r="H1478" s="5" t="s">
+      <c r="H1478" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1478" s="8" t="s">
+      <c r="I1478" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1478" s="8">
+      <c r="J1478" s="46">
         <v>6446</v>
       </c>
-      <c r="K1478" s="5" t="s">
+      <c r="K1478" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1479" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1479" s="42" t="s">
+    <row r="1479" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1479" s="44" t="s">
         <v>2161</v>
       </c>
-      <c r="B1479" s="25" t="s">
+      <c r="B1479" s="45" t="s">
         <v>2162</v>
       </c>
-      <c r="C1479" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1479" s="4">
+      <c r="C1479" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1479" s="47">
         <v>1</v>
       </c>
-      <c r="E1479" s="4">
+      <c r="E1479" s="47">
         <v>1170</v>
       </c>
-      <c r="F1479" s="15">
+      <c r="F1479" s="49">
         <f t="shared" ref="F1479:F1542" si="24">E1479*D1479</f>
         <v>1170</v>
       </c>
-      <c r="G1479" s="8">
+      <c r="G1479" s="46">
         <v>131</v>
       </c>
-      <c r="H1479" s="5" t="s">
+      <c r="H1479" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1479" s="8" t="s">
+      <c r="I1479" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1479" s="8">
+      <c r="J1479" s="46">
         <v>6446</v>
       </c>
-      <c r="K1479" s="5" t="s">
+      <c r="K1479" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1480" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1480" s="42" t="s">
+    <row r="1480" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1480" s="44" t="s">
         <v>2163</v>
       </c>
-      <c r="B1480" s="25" t="s">
+      <c r="B1480" s="45" t="s">
         <v>2164</v>
       </c>
-      <c r="C1480" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1480" s="4">
+      <c r="C1480" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1480" s="47">
         <v>10</v>
       </c>
-      <c r="E1480" s="4">
+      <c r="E1480" s="47">
         <v>41</v>
       </c>
-      <c r="F1480" s="15">
+      <c r="F1480" s="49">
         <f t="shared" si="24"/>
         <v>410</v>
       </c>
-      <c r="G1480" s="8">
+      <c r="G1480" s="46">
         <v>131</v>
       </c>
-      <c r="H1480" s="5" t="s">
+      <c r="H1480" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1480" s="8" t="s">
+      <c r="I1480" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1480" s="8">
+      <c r="J1480" s="46">
         <v>6446</v>
       </c>
-      <c r="K1480" s="5" t="s">
+      <c r="K1480" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1481" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1481" s="42" t="s">
+    <row r="1481" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1481" s="44" t="s">
         <v>227</v>
       </c>
-      <c r="B1481" s="25" t="s">
+      <c r="B1481" s="45" t="s">
         <v>2165</v>
       </c>
-      <c r="C1481" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1481" s="4">
+      <c r="C1481" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1481" s="47">
         <v>10</v>
       </c>
-      <c r="E1481" s="4">
+      <c r="E1481" s="47">
         <v>41</v>
       </c>
-      <c r="F1481" s="15">
+      <c r="F1481" s="49">
         <f t="shared" si="24"/>
         <v>410</v>
       </c>
-      <c r="G1481" s="8">
+      <c r="G1481" s="46">
         <v>131</v>
       </c>
-      <c r="H1481" s="5" t="s">
+      <c r="H1481" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1481" s="8" t="s">
+      <c r="I1481" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1481" s="8">
+      <c r="J1481" s="46">
         <v>6446</v>
       </c>
-      <c r="K1481" s="5" t="s">
+      <c r="K1481" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1482" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1482" s="42" t="s">
+    <row r="1482" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1482" s="44" t="s">
         <v>1355</v>
       </c>
-      <c r="B1482" s="25" t="s">
+      <c r="B1482" s="45" t="s">
         <v>2166</v>
       </c>
-      <c r="C1482" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1482" s="4">
+      <c r="C1482" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1482" s="47">
         <v>5</v>
       </c>
-      <c r="E1482" s="4">
+      <c r="E1482" s="47">
         <v>135.5</v>
       </c>
-      <c r="F1482" s="15">
+      <c r="F1482" s="49">
         <f t="shared" si="24"/>
         <v>677.5</v>
       </c>
-      <c r="G1482" s="8">
+      <c r="G1482" s="46">
         <v>131</v>
       </c>
-      <c r="H1482" s="5" t="s">
+      <c r="H1482" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1482" s="8" t="s">
+      <c r="I1482" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1482" s="8">
+      <c r="J1482" s="46">
         <v>6446</v>
       </c>
-      <c r="K1482" s="5" t="s">
+      <c r="K1482" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1483" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1483" s="42" t="s">
+    <row r="1483" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1483" s="44" t="s">
         <v>2167</v>
       </c>
-      <c r="B1483" s="25" t="s">
+      <c r="B1483" s="45" t="s">
         <v>2168</v>
       </c>
-      <c r="C1483" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1483" s="4">
+      <c r="C1483" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1483" s="47">
         <v>16</v>
       </c>
-      <c r="E1483" s="4">
+      <c r="E1483" s="47">
         <v>169</v>
       </c>
-      <c r="F1483" s="15">
+      <c r="F1483" s="49">
         <f t="shared" si="24"/>
         <v>2704</v>
       </c>
-      <c r="G1483" s="8">
+      <c r="G1483" s="46">
         <v>131</v>
       </c>
-      <c r="H1483" s="5" t="s">
+      <c r="H1483" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1483" s="8" t="s">
+      <c r="I1483" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1483" s="8">
+      <c r="J1483" s="46">
         <v>6446</v>
       </c>
-      <c r="K1483" s="5" t="s">
+      <c r="K1483" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1484" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1484" s="42" t="s">
+    <row r="1484" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1484" s="44" t="s">
         <v>2169</v>
       </c>
-      <c r="B1484" s="25" t="s">
+      <c r="B1484" s="45" t="s">
         <v>2170</v>
       </c>
-      <c r="C1484" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1484" s="4">
+      <c r="C1484" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1484" s="47">
         <v>1</v>
       </c>
-      <c r="E1484" s="4">
+      <c r="E1484" s="47">
         <v>175.5</v>
       </c>
-      <c r="F1484" s="15">
+      <c r="F1484" s="49">
         <f t="shared" si="24"/>
         <v>175.5</v>
       </c>
-      <c r="G1484" s="8">
+      <c r="G1484" s="46">
         <v>131</v>
       </c>
-      <c r="H1484" s="5" t="s">
+      <c r="H1484" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1484" s="8" t="s">
+      <c r="I1484" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1484" s="8">
+      <c r="J1484" s="46">
         <v>6446</v>
       </c>
-      <c r="K1484" s="5" t="s">
+      <c r="K1484" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1485" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1485" s="42" t="s">
+    <row r="1485" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1485" s="44" t="s">
         <v>2171</v>
       </c>
-      <c r="B1485" s="25" t="s">
+      <c r="B1485" s="45" t="s">
         <v>2172</v>
       </c>
-      <c r="C1485" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1485" s="4">
+      <c r="C1485" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1485" s="47">
         <v>1</v>
       </c>
-      <c r="E1485" s="4">
+      <c r="E1485" s="47">
         <v>2106</v>
       </c>
-      <c r="F1485" s="15">
+      <c r="F1485" s="49">
         <f t="shared" si="24"/>
         <v>2106</v>
       </c>
-      <c r="G1485" s="8">
+      <c r="G1485" s="46">
         <v>131</v>
       </c>
-      <c r="H1485" s="5" t="s">
+      <c r="H1485" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1485" s="8" t="s">
+      <c r="I1485" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1485" s="8">
+      <c r="J1485" s="46">
         <v>6446</v>
       </c>
-      <c r="K1485" s="5" t="s">
+      <c r="K1485" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1486" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1486" s="42" t="s">
+    <row r="1486" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1486" s="44" t="s">
         <v>326</v>
       </c>
-      <c r="B1486" s="25" t="s">
+      <c r="B1486" s="45" t="s">
         <v>1952</v>
       </c>
-      <c r="C1486" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1486" s="4">
+      <c r="C1486" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1486" s="47">
         <v>24</v>
       </c>
-      <c r="E1486" s="4">
+      <c r="E1486" s="47">
         <v>117</v>
       </c>
-      <c r="F1486" s="15">
+      <c r="F1486" s="49">
         <f t="shared" si="24"/>
         <v>2808</v>
       </c>
-      <c r="G1486" s="8">
+      <c r="G1486" s="46">
         <v>131</v>
       </c>
-      <c r="H1486" s="5" t="s">
+      <c r="H1486" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1486" s="8" t="s">
+      <c r="I1486" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1486" s="8">
+      <c r="J1486" s="46">
         <v>6446</v>
       </c>
-      <c r="K1486" s="5" t="s">
+      <c r="K1486" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1487" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1487" s="42" t="s">
+    <row r="1487" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1487" s="44" t="s">
         <v>296</v>
       </c>
-      <c r="B1487" s="25" t="s">
+      <c r="B1487" s="45" t="s">
         <v>1744</v>
       </c>
-      <c r="C1487" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1487" s="4">
+      <c r="C1487" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1487" s="47">
         <v>12</v>
       </c>
-      <c r="E1487" s="4">
+      <c r="E1487" s="47">
         <v>351</v>
       </c>
-      <c r="F1487" s="15">
+      <c r="F1487" s="49">
         <f t="shared" si="24"/>
         <v>4212</v>
       </c>
-      <c r="G1487" s="8">
+      <c r="G1487" s="46">
         <v>131</v>
       </c>
-      <c r="H1487" s="5" t="s">
+      <c r="H1487" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1487" s="8" t="s">
+      <c r="I1487" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1487" s="8">
+      <c r="J1487" s="46">
         <v>6446</v>
       </c>
-      <c r="K1487" s="5" t="s">
+      <c r="K1487" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1488" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1488" s="42" t="s">
+    <row r="1488" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1488" s="44" t="s">
         <v>716</v>
       </c>
-      <c r="B1488" s="25" t="s">
+      <c r="B1488" s="45" t="s">
         <v>717</v>
       </c>
-      <c r="C1488" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1488" s="4">
+      <c r="C1488" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1488" s="47">
         <v>10</v>
       </c>
-      <c r="E1488" s="4">
+      <c r="E1488" s="47">
         <v>111.35</v>
       </c>
-      <c r="F1488" s="15">
+      <c r="F1488" s="49">
         <f t="shared" si="24"/>
         <v>1113.5</v>
       </c>
-      <c r="G1488" s="8">
+      <c r="G1488" s="46">
         <v>131</v>
       </c>
-      <c r="H1488" s="5" t="s">
+      <c r="H1488" s="50" t="s">
         <v>1928</v>
       </c>
-      <c r="I1488" s="8" t="s">
+      <c r="I1488" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="J1488" s="8">
+      <c r="J1488" s="46">
         <v>6446</v>
       </c>
-      <c r="K1488" s="5" t="s">
+      <c r="K1488" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
@@ -62254,1835 +62307,1835 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="1513" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1513" s="42" t="s">
+    <row r="1513" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1513" s="44" t="s">
         <v>1172</v>
       </c>
-      <c r="B1513" s="25" t="s">
+      <c r="B1513" s="45" t="s">
         <v>1173</v>
       </c>
-      <c r="C1513" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1513" s="4">
+      <c r="C1513" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1513" s="47">
         <v>13</v>
       </c>
-      <c r="E1513" s="4">
+      <c r="E1513" s="47">
         <v>100</v>
       </c>
-      <c r="F1513" s="15">
+      <c r="F1513" s="49">
         <f t="shared" si="24"/>
         <v>1300</v>
       </c>
-      <c r="G1513" s="8" t="s">
+      <c r="G1513" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1513" s="5" t="s">
+      <c r="H1513" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1513" s="8" t="s">
+      <c r="I1513" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1513" s="8">
+      <c r="J1513" s="46">
         <v>6455</v>
       </c>
-      <c r="K1513" s="5" t="s">
+      <c r="K1513" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1514" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1514" s="42" t="s">
+    <row r="1514" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1514" s="44" t="s">
         <v>2205</v>
       </c>
-      <c r="B1514" s="25" t="s">
+      <c r="B1514" s="45" t="s">
         <v>2206</v>
       </c>
-      <c r="C1514" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1514" s="4">
+      <c r="C1514" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1514" s="47">
         <v>15</v>
       </c>
-      <c r="E1514" s="4">
+      <c r="E1514" s="47">
         <v>35</v>
       </c>
-      <c r="F1514" s="15">
+      <c r="F1514" s="49">
         <f t="shared" si="24"/>
         <v>525</v>
       </c>
-      <c r="G1514" s="8" t="s">
+      <c r="G1514" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1514" s="5" t="s">
+      <c r="H1514" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1514" s="8" t="s">
+      <c r="I1514" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1514" s="8">
+      <c r="J1514" s="46">
         <v>6455</v>
       </c>
-      <c r="K1514" s="5" t="s">
+      <c r="K1514" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1515" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1515" s="42" t="s">
+    <row r="1515" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1515" s="44" t="s">
         <v>2207</v>
       </c>
-      <c r="B1515" s="25" t="s">
+      <c r="B1515" s="45" t="s">
         <v>2208</v>
       </c>
-      <c r="C1515" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1515" s="4">
+      <c r="C1515" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1515" s="47">
         <v>300</v>
       </c>
-      <c r="E1515" s="4">
+      <c r="E1515" s="47">
         <v>15</v>
       </c>
-      <c r="F1515" s="15">
+      <c r="F1515" s="49">
         <f t="shared" si="24"/>
         <v>4500</v>
       </c>
-      <c r="G1515" s="8" t="s">
+      <c r="G1515" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1515" s="5" t="s">
+      <c r="H1515" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1515" s="8" t="s">
+      <c r="I1515" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1515" s="8">
+      <c r="J1515" s="46">
         <v>6455</v>
       </c>
-      <c r="K1515" s="5" t="s">
+      <c r="K1515" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1516" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1516" s="42" t="s">
+    <row r="1516" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1516" s="44" t="s">
         <v>2209</v>
       </c>
-      <c r="B1516" s="25" t="s">
+      <c r="B1516" s="45" t="s">
         <v>2210</v>
       </c>
-      <c r="C1516" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1516" s="4">
+      <c r="C1516" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1516" s="47">
         <v>5</v>
       </c>
-      <c r="E1516" s="4">
+      <c r="E1516" s="47">
         <v>1600</v>
       </c>
-      <c r="F1516" s="15">
+      <c r="F1516" s="49">
         <f t="shared" si="24"/>
         <v>8000</v>
       </c>
-      <c r="G1516" s="8" t="s">
+      <c r="G1516" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1516" s="5" t="s">
+      <c r="H1516" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1516" s="8" t="s">
+      <c r="I1516" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1516" s="8">
+      <c r="J1516" s="46">
         <v>6455</v>
       </c>
-      <c r="K1516" s="5" t="s">
+      <c r="K1516" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1517" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1517" s="42" t="s">
+    <row r="1517" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1517" s="44" t="s">
         <v>1579</v>
       </c>
-      <c r="B1517" s="25" t="s">
+      <c r="B1517" s="45" t="s">
         <v>1580</v>
       </c>
-      <c r="C1517" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1517" s="4">
+      <c r="C1517" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1517" s="47">
         <v>4</v>
       </c>
-      <c r="E1517" s="4">
+      <c r="E1517" s="47">
         <v>1100</v>
       </c>
-      <c r="F1517" s="15">
+      <c r="F1517" s="49">
         <f t="shared" si="24"/>
         <v>4400</v>
       </c>
-      <c r="G1517" s="8" t="s">
+      <c r="G1517" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1517" s="5" t="s">
+      <c r="H1517" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1517" s="8" t="s">
+      <c r="I1517" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1517" s="8">
+      <c r="J1517" s="46">
         <v>6455</v>
       </c>
-      <c r="K1517" s="5" t="s">
+      <c r="K1517" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1518" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1518" s="42" t="s">
+    <row r="1518" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1518" s="44" t="s">
         <v>1190</v>
       </c>
-      <c r="B1518" s="25" t="s">
+      <c r="B1518" s="45" t="s">
         <v>2211</v>
       </c>
-      <c r="C1518" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1518" s="4">
+      <c r="C1518" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1518" s="47">
         <v>15</v>
       </c>
-      <c r="E1518" s="4">
+      <c r="E1518" s="47">
         <v>150</v>
       </c>
-      <c r="F1518" s="15">
+      <c r="F1518" s="49">
         <f t="shared" si="24"/>
         <v>2250</v>
       </c>
-      <c r="G1518" s="8" t="s">
+      <c r="G1518" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1518" s="5" t="s">
+      <c r="H1518" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1518" s="8" t="s">
+      <c r="I1518" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1518" s="8">
+      <c r="J1518" s="46">
         <v>6455</v>
       </c>
-      <c r="K1518" s="5" t="s">
+      <c r="K1518" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1519" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1519" s="42" t="s">
+    <row r="1519" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1519" s="44" t="s">
         <v>1197</v>
       </c>
-      <c r="B1519" s="25" t="s">
+      <c r="B1519" s="45" t="s">
         <v>2212</v>
       </c>
-      <c r="C1519" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1519" s="4">
+      <c r="C1519" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1519" s="47">
         <v>15</v>
       </c>
-      <c r="E1519" s="4">
+      <c r="E1519" s="47">
         <v>200</v>
       </c>
-      <c r="F1519" s="15">
+      <c r="F1519" s="49">
         <f t="shared" si="24"/>
         <v>3000</v>
       </c>
-      <c r="G1519" s="8" t="s">
+      <c r="G1519" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1519" s="5" t="s">
+      <c r="H1519" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1519" s="8" t="s">
+      <c r="I1519" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1519" s="8">
+      <c r="J1519" s="46">
         <v>6455</v>
       </c>
-      <c r="K1519" s="5" t="s">
+      <c r="K1519" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1520" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1520" s="42" t="s">
+    <row r="1520" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1520" s="44" t="s">
         <v>1622</v>
       </c>
-      <c r="B1520" s="25" t="s">
+      <c r="B1520" s="45" t="s">
         <v>2213</v>
       </c>
-      <c r="C1520" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1520" s="4">
+      <c r="C1520" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1520" s="47">
         <v>37</v>
       </c>
-      <c r="E1520" s="4">
+      <c r="E1520" s="47">
         <v>1750</v>
       </c>
-      <c r="F1520" s="15">
+      <c r="F1520" s="49">
         <f t="shared" si="24"/>
         <v>64750</v>
       </c>
-      <c r="G1520" s="8" t="s">
+      <c r="G1520" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1520" s="5" t="s">
+      <c r="H1520" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1520" s="8" t="s">
+      <c r="I1520" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1520" s="8">
+      <c r="J1520" s="46">
         <v>6455</v>
       </c>
-      <c r="K1520" s="5" t="s">
+      <c r="K1520" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1521" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1521" s="42" t="s">
+    <row r="1521" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1521" s="44" t="s">
         <v>1254</v>
       </c>
-      <c r="B1521" s="25" t="s">
+      <c r="B1521" s="45" t="s">
         <v>2214</v>
       </c>
-      <c r="C1521" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1521" s="4">
+      <c r="C1521" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1521" s="47">
         <v>15</v>
       </c>
-      <c r="E1521" s="4">
+      <c r="E1521" s="47">
         <v>1600</v>
       </c>
-      <c r="F1521" s="15">
+      <c r="F1521" s="49">
         <f t="shared" si="24"/>
         <v>24000</v>
       </c>
-      <c r="G1521" s="8" t="s">
+      <c r="G1521" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1521" s="5" t="s">
+      <c r="H1521" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1521" s="8" t="s">
+      <c r="I1521" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1521" s="8">
+      <c r="J1521" s="46">
         <v>6455</v>
       </c>
-      <c r="K1521" s="5" t="s">
+      <c r="K1521" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1522" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1522" s="42" t="s">
+    <row r="1522" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1522" s="44" t="s">
         <v>2215</v>
       </c>
-      <c r="B1522" s="25" t="s">
+      <c r="B1522" s="45" t="s">
         <v>2216</v>
       </c>
-      <c r="C1522" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1522" s="4">
+      <c r="C1522" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1522" s="47">
         <v>15</v>
       </c>
-      <c r="E1522" s="4">
+      <c r="E1522" s="47">
         <v>100</v>
       </c>
-      <c r="F1522" s="15">
+      <c r="F1522" s="49">
         <f t="shared" si="24"/>
         <v>1500</v>
       </c>
-      <c r="G1522" s="8" t="s">
+      <c r="G1522" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1522" s="5" t="s">
+      <c r="H1522" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1522" s="8" t="s">
+      <c r="I1522" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1522" s="8">
+      <c r="J1522" s="46">
         <v>6455</v>
       </c>
-      <c r="K1522" s="5" t="s">
+      <c r="K1522" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1523" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1523" s="42" t="s">
+    <row r="1523" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1523" s="44" t="s">
         <v>1258</v>
       </c>
-      <c r="B1523" s="25" t="s">
+      <c r="B1523" s="45" t="s">
         <v>2217</v>
       </c>
-      <c r="C1523" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1523" s="4">
+      <c r="C1523" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1523" s="47">
         <v>15</v>
       </c>
-      <c r="E1523" s="4">
+      <c r="E1523" s="47">
         <v>2800</v>
       </c>
-      <c r="F1523" s="15">
+      <c r="F1523" s="49">
         <f t="shared" si="24"/>
         <v>42000</v>
       </c>
-      <c r="G1523" s="8" t="s">
+      <c r="G1523" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1523" s="5" t="s">
+      <c r="H1523" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1523" s="8" t="s">
+      <c r="I1523" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1523" s="8">
+      <c r="J1523" s="46">
         <v>6455</v>
       </c>
-      <c r="K1523" s="5" t="s">
+      <c r="K1523" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1524" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1524" s="42" t="s">
+    <row r="1524" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1524" s="44" t="s">
         <v>2218</v>
       </c>
-      <c r="B1524" s="25" t="s">
+      <c r="B1524" s="45" t="s">
         <v>2219</v>
       </c>
-      <c r="C1524" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1524" s="4">
+      <c r="C1524" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1524" s="47">
         <v>15</v>
       </c>
-      <c r="E1524" s="4">
+      <c r="E1524" s="47">
         <v>1450</v>
       </c>
-      <c r="F1524" s="15">
+      <c r="F1524" s="49">
         <f t="shared" si="24"/>
         <v>21750</v>
       </c>
-      <c r="G1524" s="8" t="s">
+      <c r="G1524" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1524" s="5" t="s">
+      <c r="H1524" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1524" s="8" t="s">
+      <c r="I1524" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1524" s="8">
+      <c r="J1524" s="46">
         <v>6455</v>
       </c>
-      <c r="K1524" s="5" t="s">
+      <c r="K1524" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1525" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1525" s="42" t="s">
+    <row r="1525" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1525" s="44" t="s">
         <v>2220</v>
       </c>
-      <c r="B1525" s="25" t="s">
+      <c r="B1525" s="45" t="s">
         <v>2221</v>
       </c>
-      <c r="C1525" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1525" s="4">
+      <c r="C1525" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1525" s="47">
         <v>15</v>
       </c>
-      <c r="E1525" s="4">
+      <c r="E1525" s="47">
         <v>175</v>
       </c>
-      <c r="F1525" s="15">
+      <c r="F1525" s="49">
         <f t="shared" si="24"/>
         <v>2625</v>
       </c>
-      <c r="G1525" s="8" t="s">
+      <c r="G1525" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1525" s="5" t="s">
+      <c r="H1525" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1525" s="8" t="s">
+      <c r="I1525" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1525" s="8">
+      <c r="J1525" s="46">
         <v>6456</v>
       </c>
-      <c r="K1525" s="5" t="s">
+      <c r="K1525" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1526" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1526" s="42" t="s">
+    <row r="1526" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1526" s="44" t="s">
         <v>1214</v>
       </c>
-      <c r="B1526" s="25" t="s">
+      <c r="B1526" s="45" t="s">
         <v>1215</v>
       </c>
-      <c r="C1526" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1526" s="4">
+      <c r="C1526" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1526" s="47">
         <v>15</v>
       </c>
-      <c r="E1526" s="4">
+      <c r="E1526" s="47">
         <v>20</v>
       </c>
-      <c r="F1526" s="15">
+      <c r="F1526" s="49">
         <f t="shared" si="24"/>
         <v>300</v>
       </c>
-      <c r="G1526" s="8" t="s">
+      <c r="G1526" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1526" s="5" t="s">
+      <c r="H1526" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1526" s="8" t="s">
+      <c r="I1526" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1526" s="8">
+      <c r="J1526" s="46">
         <v>6456</v>
       </c>
-      <c r="K1526" s="5" t="s">
+      <c r="K1526" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1527" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1527" s="42" t="s">
+    <row r="1527" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1527" s="44" t="s">
         <v>1168</v>
       </c>
-      <c r="B1527" s="25" t="s">
+      <c r="B1527" s="45" t="s">
         <v>1169</v>
       </c>
-      <c r="C1527" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1527" s="4">
+      <c r="C1527" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1527" s="47">
         <v>90</v>
       </c>
-      <c r="E1527" s="4">
+      <c r="E1527" s="47">
         <v>15</v>
       </c>
-      <c r="F1527" s="15">
+      <c r="F1527" s="49">
         <f t="shared" si="24"/>
         <v>1350</v>
       </c>
-      <c r="G1527" s="8" t="s">
+      <c r="G1527" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1527" s="5" t="s">
+      <c r="H1527" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1527" s="8" t="s">
+      <c r="I1527" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1527" s="8">
+      <c r="J1527" s="46">
         <v>6456</v>
       </c>
-      <c r="K1527" s="5" t="s">
+      <c r="K1527" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1528" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1528" s="42" t="s">
+    <row r="1528" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1528" s="44" t="s">
         <v>1216</v>
       </c>
-      <c r="B1528" s="25" t="s">
+      <c r="B1528" s="45" t="s">
         <v>1914</v>
       </c>
-      <c r="C1528" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1528" s="4">
+      <c r="C1528" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1528" s="47">
         <v>5</v>
       </c>
-      <c r="E1528" s="4">
+      <c r="E1528" s="47">
         <v>45</v>
       </c>
-      <c r="F1528" s="15">
+      <c r="F1528" s="49">
         <f t="shared" si="24"/>
         <v>225</v>
       </c>
-      <c r="G1528" s="8" t="s">
+      <c r="G1528" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1528" s="5" t="s">
+      <c r="H1528" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1528" s="8" t="s">
+      <c r="I1528" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1528" s="8">
+      <c r="J1528" s="46">
         <v>6456</v>
       </c>
-      <c r="K1528" s="5" t="s">
+      <c r="K1528" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1529" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1529" s="42" t="s">
+    <row r="1529" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1529" s="44" t="s">
         <v>1407</v>
       </c>
-      <c r="B1529" s="25" t="s">
+      <c r="B1529" s="45" t="s">
         <v>2222</v>
       </c>
-      <c r="C1529" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1529" s="4">
+      <c r="C1529" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1529" s="47">
         <v>8</v>
       </c>
-      <c r="E1529" s="4">
+      <c r="E1529" s="47">
         <v>150</v>
       </c>
-      <c r="F1529" s="15">
+      <c r="F1529" s="49">
         <f t="shared" si="24"/>
         <v>1200</v>
       </c>
-      <c r="G1529" s="8" t="s">
+      <c r="G1529" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1529" s="5" t="s">
+      <c r="H1529" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1529" s="8" t="s">
+      <c r="I1529" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1529" s="8">
+      <c r="J1529" s="46">
         <v>6456</v>
       </c>
-      <c r="K1529" s="5" t="s">
+      <c r="K1529" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1530" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1530" s="42" t="s">
+    <row r="1530" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1530" s="44" t="s">
         <v>1405</v>
       </c>
-      <c r="B1530" s="25" t="s">
+      <c r="B1530" s="45" t="s">
         <v>2223</v>
       </c>
-      <c r="C1530" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1530" s="4">
+      <c r="C1530" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1530" s="47">
         <v>75</v>
       </c>
-      <c r="E1530" s="4">
+      <c r="E1530" s="47">
         <v>15</v>
       </c>
-      <c r="F1530" s="15">
+      <c r="F1530" s="49">
         <f t="shared" si="24"/>
         <v>1125</v>
       </c>
-      <c r="G1530" s="8" t="s">
+      <c r="G1530" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1530" s="5" t="s">
+      <c r="H1530" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1530" s="8" t="s">
+      <c r="I1530" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1530" s="8">
+      <c r="J1530" s="46">
         <v>6456</v>
       </c>
-      <c r="K1530" s="5" t="s">
+      <c r="K1530" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1531" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1531" s="42" t="s">
+    <row r="1531" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1531" s="44" t="s">
         <v>1239</v>
       </c>
-      <c r="B1531" s="25" t="s">
+      <c r="B1531" s="45" t="s">
         <v>2224</v>
       </c>
-      <c r="C1531" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1531" s="4">
+      <c r="C1531" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1531" s="47">
         <v>2</v>
       </c>
-      <c r="E1531" s="4">
+      <c r="E1531" s="47">
         <v>7900</v>
       </c>
-      <c r="F1531" s="15">
+      <c r="F1531" s="49">
         <f t="shared" si="24"/>
         <v>15800</v>
       </c>
-      <c r="G1531" s="8" t="s">
+      <c r="G1531" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1531" s="5" t="s">
+      <c r="H1531" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1531" s="8" t="s">
+      <c r="I1531" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1531" s="8">
+      <c r="J1531" s="46">
         <v>6456</v>
       </c>
-      <c r="K1531" s="5" t="s">
+      <c r="K1531" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1532" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1532" s="42" t="s">
+    <row r="1532" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1532" s="44" t="s">
         <v>2225</v>
       </c>
-      <c r="B1532" s="25" t="s">
+      <c r="B1532" s="45" t="s">
         <v>2226</v>
       </c>
-      <c r="C1532" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1532" s="4">
+      <c r="C1532" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1532" s="47">
         <v>2</v>
       </c>
-      <c r="E1532" s="4">
+      <c r="E1532" s="47">
         <v>5800</v>
       </c>
-      <c r="F1532" s="15">
+      <c r="F1532" s="49">
         <f t="shared" si="24"/>
         <v>11600</v>
       </c>
-      <c r="G1532" s="8" t="s">
+      <c r="G1532" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1532" s="5" t="s">
+      <c r="H1532" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1532" s="8" t="s">
+      <c r="I1532" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1532" s="8">
+      <c r="J1532" s="46">
         <v>6456</v>
       </c>
-      <c r="K1532" s="5" t="s">
+      <c r="K1532" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1533" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1533" s="42" t="s">
+    <row r="1533" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1533" s="44" t="s">
         <v>1241</v>
       </c>
-      <c r="B1533" s="25" t="s">
+      <c r="B1533" s="45" t="s">
         <v>2227</v>
       </c>
-      <c r="C1533" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1533" s="4">
+      <c r="C1533" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1533" s="47">
         <v>2</v>
       </c>
-      <c r="E1533" s="4">
+      <c r="E1533" s="47">
         <v>3200</v>
       </c>
-      <c r="F1533" s="15">
+      <c r="F1533" s="49">
         <f t="shared" si="24"/>
         <v>6400</v>
       </c>
-      <c r="G1533" s="8" t="s">
+      <c r="G1533" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1533" s="5" t="s">
+      <c r="H1533" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1533" s="8" t="s">
+      <c r="I1533" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1533" s="8">
+      <c r="J1533" s="46">
         <v>6456</v>
       </c>
-      <c r="K1533" s="5" t="s">
+      <c r="K1533" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1534" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1534" s="42" t="s">
+    <row r="1534" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1534" s="44" t="s">
         <v>1904</v>
       </c>
-      <c r="B1534" s="25" t="s">
+      <c r="B1534" s="45" t="s">
         <v>2228</v>
       </c>
-      <c r="C1534" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1534" s="4">
+      <c r="C1534" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1534" s="47">
         <v>2</v>
       </c>
-      <c r="E1534" s="4">
+      <c r="E1534" s="47">
         <v>11150</v>
       </c>
-      <c r="F1534" s="15">
+      <c r="F1534" s="49">
         <f t="shared" si="24"/>
         <v>22300</v>
       </c>
-      <c r="G1534" s="8" t="s">
+      <c r="G1534" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1534" s="5" t="s">
+      <c r="H1534" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1534" s="8" t="s">
+      <c r="I1534" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1534" s="8">
+      <c r="J1534" s="46">
         <v>6456</v>
       </c>
-      <c r="K1534" s="5" t="s">
+      <c r="K1534" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1535" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1535" s="42"/>
-      <c r="B1535" s="25" t="s">
+    <row r="1535" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1535" s="44"/>
+      <c r="B1535" s="45" t="s">
         <v>2229</v>
       </c>
-      <c r="C1535" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1535" s="4">
+      <c r="C1535" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1535" s="47">
         <v>60</v>
       </c>
-      <c r="E1535" s="4">
+      <c r="E1535" s="47">
         <v>250</v>
       </c>
-      <c r="F1535" s="15">
+      <c r="F1535" s="49">
         <f t="shared" si="24"/>
         <v>15000</v>
       </c>
-      <c r="G1535" s="8" t="s">
+      <c r="G1535" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1535" s="5" t="s">
+      <c r="H1535" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1535" s="8" t="s">
+      <c r="I1535" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1535" s="8">
+      <c r="J1535" s="46">
         <v>6457</v>
       </c>
-      <c r="K1535" s="5" t="s">
+      <c r="K1535" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1536" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1536" s="42" t="s">
+    <row r="1536" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1536" s="44" t="s">
         <v>1230</v>
       </c>
-      <c r="B1536" s="25" t="s">
+      <c r="B1536" s="45" t="s">
         <v>2230</v>
       </c>
-      <c r="C1536" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1536" s="4">
+      <c r="C1536" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1536" s="47">
         <v>2</v>
       </c>
-      <c r="E1536" s="4">
+      <c r="E1536" s="47">
         <v>250</v>
       </c>
-      <c r="F1536" s="15">
+      <c r="F1536" s="49">
         <f t="shared" si="24"/>
         <v>500</v>
       </c>
-      <c r="G1536" s="8" t="s">
+      <c r="G1536" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1536" s="5" t="s">
+      <c r="H1536" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1536" s="8" t="s">
+      <c r="I1536" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1536" s="8">
+      <c r="J1536" s="46">
         <v>6457</v>
       </c>
-      <c r="K1536" s="5" t="s">
+      <c r="K1536" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1537" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1537" s="42" t="s">
+    <row r="1537" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1537" s="44" t="s">
         <v>1184</v>
       </c>
-      <c r="B1537" s="25" t="s">
+      <c r="B1537" s="45" t="s">
         <v>2231</v>
       </c>
-      <c r="C1537" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1537" s="4">
+      <c r="C1537" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1537" s="47">
         <v>15</v>
       </c>
-      <c r="E1537" s="4">
+      <c r="E1537" s="47">
         <v>1000</v>
       </c>
-      <c r="F1537" s="15">
+      <c r="F1537" s="49">
         <f t="shared" si="24"/>
         <v>15000</v>
       </c>
-      <c r="G1537" s="8" t="s">
+      <c r="G1537" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1537" s="5" t="s">
+      <c r="H1537" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1537" s="8" t="s">
+      <c r="I1537" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1537" s="8">
+      <c r="J1537" s="46">
         <v>6457</v>
       </c>
-      <c r="K1537" s="5" t="s">
+      <c r="K1537" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1538" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1538" s="42" t="s">
+    <row r="1538" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1538" s="44" t="s">
         <v>2232</v>
       </c>
-      <c r="B1538" s="25" t="s">
+      <c r="B1538" s="45" t="s">
         <v>2233</v>
       </c>
-      <c r="C1538" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1538" s="4">
+      <c r="C1538" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1538" s="47">
         <v>60</v>
       </c>
-      <c r="E1538" s="4">
+      <c r="E1538" s="47">
         <v>501</v>
       </c>
-      <c r="F1538" s="15">
+      <c r="F1538" s="49">
         <f t="shared" si="24"/>
         <v>30060</v>
       </c>
-      <c r="G1538" s="8" t="s">
+      <c r="G1538" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1538" s="5" t="s">
+      <c r="H1538" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1538" s="8" t="s">
+      <c r="I1538" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1538" s="8">
+      <c r="J1538" s="46">
         <v>6457</v>
       </c>
-      <c r="K1538" s="5" t="s">
+      <c r="K1538" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1539" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1539" s="42" t="s">
+    <row r="1539" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1539" s="44" t="s">
         <v>1205</v>
       </c>
-      <c r="B1539" s="25" t="s">
+      <c r="B1539" s="45" t="s">
         <v>2234</v>
       </c>
-      <c r="C1539" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1539" s="4">
+      <c r="C1539" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1539" s="47">
         <v>45</v>
       </c>
-      <c r="E1539" s="4">
+      <c r="E1539" s="47">
         <v>75</v>
       </c>
-      <c r="F1539" s="15">
+      <c r="F1539" s="49">
         <f t="shared" si="24"/>
         <v>3375</v>
       </c>
-      <c r="G1539" s="8" t="s">
+      <c r="G1539" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1539" s="5" t="s">
+      <c r="H1539" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1539" s="8" t="s">
+      <c r="I1539" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1539" s="8">
+      <c r="J1539" s="46">
         <v>6457</v>
       </c>
-      <c r="K1539" s="5" t="s">
+      <c r="K1539" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1540" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1540" s="42" t="s">
+    <row r="1540" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1540" s="44" t="s">
         <v>2235</v>
       </c>
-      <c r="B1540" s="25" t="s">
+      <c r="B1540" s="45" t="s">
         <v>2236</v>
       </c>
-      <c r="C1540" s="8" t="s">
+      <c r="C1540" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="D1540" s="4">
+      <c r="D1540" s="47">
         <v>150</v>
       </c>
-      <c r="E1540" s="4">
+      <c r="E1540" s="47">
         <v>70</v>
       </c>
-      <c r="F1540" s="15">
+      <c r="F1540" s="49">
         <f t="shared" si="24"/>
         <v>10500</v>
       </c>
-      <c r="G1540" s="8" t="s">
+      <c r="G1540" s="46" t="s">
         <v>2309</v>
       </c>
-      <c r="H1540" s="5" t="s">
+      <c r="H1540" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1540" s="8" t="s">
+      <c r="I1540" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1540" s="8">
+      <c r="J1540" s="46">
         <v>6457</v>
       </c>
-      <c r="K1540" s="5" t="s">
+      <c r="K1540" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1541" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1541" s="42" t="s">
+    <row r="1541" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1541" s="44" t="s">
         <v>2237</v>
       </c>
-      <c r="B1541" s="25" t="s">
+      <c r="B1541" s="45" t="s">
         <v>2238</v>
       </c>
-      <c r="C1541" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1541" s="4">
+      <c r="C1541" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1541" s="47">
         <v>1</v>
       </c>
-      <c r="E1541" s="4">
+      <c r="E1541" s="47">
         <v>50</v>
       </c>
-      <c r="F1541" s="15">
+      <c r="F1541" s="49">
         <f t="shared" si="24"/>
         <v>50</v>
       </c>
-      <c r="G1541" s="8" t="s">
+      <c r="G1541" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1541" s="5" t="s">
+      <c r="H1541" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1541" s="8" t="s">
+      <c r="I1541" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1541" s="8">
+      <c r="J1541" s="46">
         <v>6458</v>
       </c>
-      <c r="K1541" s="5" t="s">
+      <c r="K1541" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1542" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1542" s="42" t="s">
+    <row r="1542" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1542" s="44" t="s">
         <v>2215</v>
       </c>
-      <c r="B1542" s="39" t="s">
+      <c r="B1542" s="60" t="s">
         <v>2239</v>
       </c>
-      <c r="C1542" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1542" s="4">
+      <c r="C1542" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1542" s="47">
         <v>1</v>
       </c>
-      <c r="E1542" s="4">
+      <c r="E1542" s="47">
         <v>100</v>
       </c>
-      <c r="F1542" s="15">
+      <c r="F1542" s="49">
         <f t="shared" si="24"/>
         <v>100</v>
       </c>
-      <c r="G1542" s="8" t="s">
+      <c r="G1542" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1542" s="5" t="s">
+      <c r="H1542" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1542" s="8" t="s">
+      <c r="I1542" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1542" s="8">
+      <c r="J1542" s="46">
         <v>6458</v>
       </c>
-      <c r="K1542" s="5" t="s">
+      <c r="K1542" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1543" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1543" s="42" t="s">
+    <row r="1543" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1543" s="44" t="s">
         <v>1254</v>
       </c>
-      <c r="B1543" s="25" t="s">
+      <c r="B1543" s="45" t="s">
         <v>2240</v>
       </c>
-      <c r="C1543" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1543" s="4">
+      <c r="C1543" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1543" s="47">
         <v>1</v>
       </c>
-      <c r="E1543" s="4">
+      <c r="E1543" s="47">
         <v>1600</v>
       </c>
-      <c r="F1543" s="15">
+      <c r="F1543" s="49">
         <f t="shared" ref="F1543:F1578" si="25">E1543*D1543</f>
         <v>1600</v>
       </c>
-      <c r="G1543" s="8" t="s">
+      <c r="G1543" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1543" s="5" t="s">
+      <c r="H1543" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1543" s="8" t="s">
+      <c r="I1543" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1543" s="8">
+      <c r="J1543" s="46">
         <v>6458</v>
       </c>
-      <c r="K1543" s="5" t="s">
+      <c r="K1543" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1544" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1544" s="42" t="s">
+    <row r="1544" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1544" s="44" t="s">
         <v>1258</v>
       </c>
-      <c r="B1544" s="25" t="s">
+      <c r="B1544" s="45" t="s">
         <v>2241</v>
       </c>
-      <c r="C1544" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1544" s="4">
+      <c r="C1544" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1544" s="47">
         <v>1</v>
       </c>
-      <c r="E1544" s="4">
+      <c r="E1544" s="47">
         <v>2800</v>
       </c>
-      <c r="F1544" s="15">
+      <c r="F1544" s="49">
         <f t="shared" si="25"/>
         <v>2800</v>
       </c>
-      <c r="G1544" s="8" t="s">
+      <c r="G1544" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1544" s="5" t="s">
+      <c r="H1544" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1544" s="8" t="s">
+      <c r="I1544" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1544" s="8">
+      <c r="J1544" s="46">
         <v>6458</v>
       </c>
-      <c r="K1544" s="5" t="s">
+      <c r="K1544" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1545" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1545" s="42" t="s">
+    <row r="1545" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1545" s="44" t="s">
         <v>1622</v>
       </c>
-      <c r="B1545" s="25" t="s">
+      <c r="B1545" s="45" t="s">
         <v>2213</v>
       </c>
-      <c r="C1545" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1545" s="4">
+      <c r="C1545" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1545" s="47">
         <v>1</v>
       </c>
-      <c r="E1545" s="4">
+      <c r="E1545" s="47">
         <v>1750</v>
       </c>
-      <c r="F1545" s="15">
+      <c r="F1545" s="49">
         <f t="shared" si="25"/>
         <v>1750</v>
       </c>
-      <c r="G1545" s="8" t="s">
+      <c r="G1545" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1545" s="5" t="s">
+      <c r="H1545" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1545" s="8" t="s">
+      <c r="I1545" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1545" s="8">
+      <c r="J1545" s="46">
         <v>6458</v>
       </c>
-      <c r="K1545" s="5" t="s">
+      <c r="K1545" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1546" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1546" s="42"/>
-      <c r="B1546" s="25" t="s">
+    <row r="1546" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1546" s="44"/>
+      <c r="B1546" s="45" t="s">
         <v>2242</v>
       </c>
-      <c r="C1546" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1546" s="4">
+      <c r="C1546" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1546" s="47">
         <v>1</v>
       </c>
-      <c r="E1546" s="4">
+      <c r="E1546" s="47">
         <v>2250</v>
       </c>
-      <c r="F1546" s="15">
+      <c r="F1546" s="49">
         <f t="shared" si="25"/>
         <v>2250</v>
       </c>
-      <c r="G1546" s="8" t="s">
+      <c r="G1546" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1546" s="5" t="s">
+      <c r="H1546" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1546" s="8" t="s">
+      <c r="I1546" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1546" s="8">
+      <c r="J1546" s="46">
         <v>6458</v>
       </c>
-      <c r="K1546" s="5" t="s">
+      <c r="K1546" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1547" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1547" s="42" t="s">
+    <row r="1547" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1547" s="44" t="s">
         <v>2218</v>
       </c>
-      <c r="B1547" s="25" t="s">
+      <c r="B1547" s="45" t="s">
         <v>2243</v>
       </c>
-      <c r="C1547" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1547" s="4">
+      <c r="C1547" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1547" s="47">
         <v>1</v>
       </c>
-      <c r="E1547" s="4">
+      <c r="E1547" s="47">
         <v>1450</v>
       </c>
-      <c r="F1547" s="15">
+      <c r="F1547" s="49">
         <f t="shared" si="25"/>
         <v>1450</v>
       </c>
-      <c r="G1547" s="8" t="s">
+      <c r="G1547" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1547" s="5" t="s">
+      <c r="H1547" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1547" s="8" t="s">
+      <c r="I1547" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1547" s="8">
+      <c r="J1547" s="46">
         <v>6458</v>
       </c>
-      <c r="K1547" s="5" t="s">
+      <c r="K1547" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1548" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1548" s="42" t="s">
+    <row r="1548" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1548" s="44" t="s">
         <v>2220</v>
       </c>
-      <c r="B1548" s="25" t="s">
+      <c r="B1548" s="45" t="s">
         <v>2244</v>
       </c>
-      <c r="C1548" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1548" s="4">
+      <c r="C1548" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1548" s="47">
         <v>1</v>
       </c>
-      <c r="E1548" s="4">
+      <c r="E1548" s="47">
         <v>175</v>
       </c>
-      <c r="F1548" s="15">
+      <c r="F1548" s="49">
         <f t="shared" si="25"/>
         <v>175</v>
       </c>
-      <c r="G1548" s="8" t="s">
+      <c r="G1548" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1548" s="5" t="s">
+      <c r="H1548" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1548" s="8" t="s">
+      <c r="I1548" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1548" s="8">
+      <c r="J1548" s="46">
         <v>6458</v>
       </c>
-      <c r="K1548" s="5" t="s">
+      <c r="K1548" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1549" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1549" s="42" t="s">
+    <row r="1549" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1549" s="44" t="s">
         <v>1168</v>
       </c>
-      <c r="B1549" s="25" t="s">
+      <c r="B1549" s="45" t="s">
         <v>1169</v>
       </c>
-      <c r="C1549" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1549" s="4">
+      <c r="C1549" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1549" s="47">
         <v>6</v>
       </c>
-      <c r="E1549" s="4">
+      <c r="E1549" s="47">
         <v>15</v>
       </c>
-      <c r="F1549" s="15">
+      <c r="F1549" s="49">
         <f t="shared" si="25"/>
         <v>90</v>
       </c>
-      <c r="G1549" s="8" t="s">
+      <c r="G1549" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1549" s="5" t="s">
+      <c r="H1549" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1549" s="8" t="s">
+      <c r="I1549" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1549" s="8">
+      <c r="J1549" s="46">
         <v>6458</v>
       </c>
-      <c r="K1549" s="5" t="s">
+      <c r="K1549" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1550" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1550" s="42" t="s">
+    <row r="1550" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1550" s="44" t="s">
         <v>1205</v>
       </c>
-      <c r="B1550" s="25" t="s">
+      <c r="B1550" s="45" t="s">
         <v>2245</v>
       </c>
-      <c r="C1550" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1550" s="4">
+      <c r="C1550" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1550" s="47">
         <v>3</v>
       </c>
-      <c r="E1550" s="4">
+      <c r="E1550" s="47">
         <v>75</v>
       </c>
-      <c r="F1550" s="15">
+      <c r="F1550" s="49">
         <f t="shared" si="25"/>
         <v>225</v>
       </c>
-      <c r="G1550" s="8" t="s">
+      <c r="G1550" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1550" s="5" t="s">
+      <c r="H1550" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1550" s="8" t="s">
+      <c r="I1550" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1550" s="8">
+      <c r="J1550" s="46">
         <v>6458</v>
       </c>
-      <c r="K1550" s="5" t="s">
+      <c r="K1550" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1551" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1551" s="42" t="s">
+    <row r="1551" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1551" s="44" t="s">
         <v>1214</v>
       </c>
-      <c r="B1551" s="25" t="s">
+      <c r="B1551" s="45" t="s">
         <v>1215</v>
       </c>
-      <c r="C1551" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1551" s="4">
+      <c r="C1551" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1551" s="47">
         <v>1</v>
       </c>
-      <c r="E1551" s="4">
+      <c r="E1551" s="47">
         <v>20</v>
       </c>
-      <c r="F1551" s="15">
+      <c r="F1551" s="49">
         <f t="shared" si="25"/>
         <v>20</v>
       </c>
-      <c r="G1551" s="8" t="s">
+      <c r="G1551" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1551" s="5" t="s">
+      <c r="H1551" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1551" s="8" t="s">
+      <c r="I1551" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1551" s="8">
+      <c r="J1551" s="46">
         <v>6458</v>
       </c>
-      <c r="K1551" s="5" t="s">
+      <c r="K1551" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1552" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1552" s="42" t="s">
+    <row r="1552" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1552" s="44" t="s">
         <v>1184</v>
       </c>
-      <c r="B1552" s="25" t="s">
+      <c r="B1552" s="45" t="s">
         <v>2231</v>
       </c>
-      <c r="C1552" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1552" s="4">
+      <c r="C1552" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1552" s="47">
         <v>1</v>
       </c>
-      <c r="E1552" s="4">
+      <c r="E1552" s="47">
         <v>1000</v>
       </c>
-      <c r="F1552" s="15">
+      <c r="F1552" s="49">
         <f t="shared" si="25"/>
         <v>1000</v>
       </c>
-      <c r="G1552" s="8" t="s">
+      <c r="G1552" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1552" s="5" t="s">
+      <c r="H1552" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1552" s="8" t="s">
+      <c r="I1552" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1552" s="8">
+      <c r="J1552" s="46">
         <v>6458</v>
       </c>
-      <c r="K1552" s="5" t="s">
+      <c r="K1552" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1553" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1553" s="42" t="s">
+    <row r="1553" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1553" s="44" t="s">
         <v>1132</v>
       </c>
-      <c r="B1553" s="25" t="s">
+      <c r="B1553" s="45" t="s">
         <v>2246</v>
       </c>
-      <c r="C1553" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1553" s="4">
+      <c r="C1553" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1553" s="47">
         <v>32</v>
       </c>
-      <c r="E1553" s="4">
+      <c r="E1553" s="47">
         <v>75</v>
       </c>
-      <c r="F1553" s="15">
+      <c r="F1553" s="49">
         <f t="shared" si="25"/>
         <v>2400</v>
       </c>
-      <c r="G1553" s="8" t="s">
+      <c r="G1553" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1553" s="5" t="s">
+      <c r="H1553" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1553" s="8" t="s">
+      <c r="I1553" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1553" s="8">
+      <c r="J1553" s="46">
         <v>6459</v>
       </c>
-      <c r="K1553" s="5" t="s">
+      <c r="K1553" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1554" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1554" s="42" t="s">
+    <row r="1554" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1554" s="44" t="s">
         <v>1210</v>
       </c>
-      <c r="B1554" s="25" t="s">
+      <c r="B1554" s="45" t="s">
         <v>2233</v>
       </c>
-      <c r="C1554" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1554" s="4">
+      <c r="C1554" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1554" s="47">
         <v>4</v>
       </c>
-      <c r="E1554" s="4">
+      <c r="E1554" s="47">
         <v>50</v>
       </c>
-      <c r="F1554" s="15">
+      <c r="F1554" s="49">
         <f t="shared" si="25"/>
         <v>200</v>
       </c>
-      <c r="G1554" s="8" t="s">
+      <c r="G1554" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1554" s="5" t="s">
+      <c r="H1554" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1554" s="8" t="s">
+      <c r="I1554" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1554" s="8">
+      <c r="J1554" s="46">
         <v>6459</v>
       </c>
-      <c r="K1554" s="5" t="s">
+      <c r="K1554" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1555" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1555" s="42" t="s">
+    <row r="1555" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1555" s="44" t="s">
         <v>1405</v>
       </c>
-      <c r="B1555" s="25" t="s">
+      <c r="B1555" s="45" t="s">
         <v>2223</v>
       </c>
-      <c r="C1555" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1555" s="4">
+      <c r="C1555" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1555" s="47">
         <v>6</v>
       </c>
-      <c r="E1555" s="4">
+      <c r="E1555" s="47">
         <v>15</v>
       </c>
-      <c r="F1555" s="15">
+      <c r="F1555" s="49">
         <f t="shared" si="25"/>
         <v>90</v>
       </c>
-      <c r="G1555" s="8" t="s">
+      <c r="G1555" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1555" s="5" t="s">
+      <c r="H1555" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1555" s="8" t="s">
+      <c r="I1555" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1555" s="8">
+      <c r="J1555" s="46">
         <v>6459</v>
       </c>
-      <c r="K1555" s="5" t="s">
+      <c r="K1555" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1556" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1556" s="42" t="s">
+    <row r="1556" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1556" s="44" t="s">
         <v>1628</v>
       </c>
-      <c r="B1556" s="25" t="s">
+      <c r="B1556" s="45" t="s">
         <v>1629</v>
       </c>
-      <c r="C1556" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1556" s="4">
+      <c r="C1556" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1556" s="47">
         <v>4</v>
       </c>
-      <c r="E1556" s="4">
+      <c r="E1556" s="47">
         <v>250</v>
       </c>
-      <c r="F1556" s="15">
+      <c r="F1556" s="49">
         <f t="shared" si="25"/>
         <v>1000</v>
       </c>
-      <c r="G1556" s="8" t="s">
+      <c r="G1556" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1556" s="5" t="s">
+      <c r="H1556" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1556" s="8" t="s">
+      <c r="I1556" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1556" s="8">
+      <c r="J1556" s="46">
         <v>6459</v>
       </c>
-      <c r="K1556" s="5" t="s">
+      <c r="K1556" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1557" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1557" s="42" t="s">
+    <row r="1557" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1557" s="44" t="s">
         <v>1250</v>
       </c>
-      <c r="B1557" s="25" t="s">
+      <c r="B1557" s="45" t="s">
         <v>2247</v>
       </c>
-      <c r="C1557" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1557" s="4">
+      <c r="C1557" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1557" s="47">
         <v>1</v>
       </c>
-      <c r="E1557" s="4">
+      <c r="E1557" s="47">
         <v>4500</v>
       </c>
-      <c r="F1557" s="15">
+      <c r="F1557" s="49">
         <f t="shared" si="25"/>
         <v>4500</v>
       </c>
-      <c r="G1557" s="8" t="s">
+      <c r="G1557" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1557" s="5" t="s">
+      <c r="H1557" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1557" s="8" t="s">
+      <c r="I1557" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1557" s="8">
+      <c r="J1557" s="46">
         <v>6459</v>
       </c>
-      <c r="K1557" s="5" t="s">
+      <c r="K1557" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1558" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1558" s="42" t="s">
+    <row r="1558" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1558" s="44" t="s">
         <v>2248</v>
       </c>
-      <c r="B1558" s="25" t="s">
+      <c r="B1558" s="45" t="s">
         <v>2249</v>
       </c>
-      <c r="C1558" s="8" t="s">
+      <c r="C1558" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="D1558" s="4">
+      <c r="D1558" s="47">
         <v>5</v>
       </c>
-      <c r="E1558" s="4">
+      <c r="E1558" s="47">
         <v>1200</v>
       </c>
-      <c r="F1558" s="15">
+      <c r="F1558" s="49">
         <f t="shared" si="25"/>
         <v>6000</v>
       </c>
-      <c r="G1558" s="8" t="s">
+      <c r="G1558" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1558" s="5" t="s">
+      <c r="H1558" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1558" s="8" t="s">
+      <c r="I1558" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1558" s="8">
+      <c r="J1558" s="46">
         <v>6459</v>
       </c>
-      <c r="K1558" s="5" t="s">
+      <c r="K1558" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1559" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1559" s="42" t="s">
+    <row r="1559" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1559" s="44" t="s">
         <v>1622</v>
       </c>
-      <c r="B1559" s="25" t="s">
+      <c r="B1559" s="45" t="s">
         <v>1623</v>
       </c>
-      <c r="C1559" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1559" s="4">
+      <c r="C1559" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1559" s="47">
         <v>2</v>
       </c>
-      <c r="E1559" s="4">
+      <c r="E1559" s="47">
         <v>1750</v>
       </c>
-      <c r="F1559" s="15">
+      <c r="F1559" s="49">
         <f t="shared" si="25"/>
         <v>3500</v>
       </c>
-      <c r="G1559" s="8" t="s">
+      <c r="G1559" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1559" s="5" t="s">
+      <c r="H1559" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1559" s="8" t="s">
+      <c r="I1559" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1559" s="8">
+      <c r="J1559" s="46">
         <v>6459</v>
       </c>
-      <c r="K1559" s="5" t="s">
+      <c r="K1559" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1560" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1560" s="42" t="s">
+    <row r="1560" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1560" s="44" t="s">
         <v>2250</v>
       </c>
-      <c r="B1560" s="25" t="s">
+      <c r="B1560" s="45" t="s">
         <v>2251</v>
       </c>
-      <c r="C1560" s="8" t="s">
+      <c r="C1560" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="D1560" s="4">
+      <c r="D1560" s="47">
         <v>5</v>
       </c>
-      <c r="E1560" s="4">
+      <c r="E1560" s="47">
         <v>180</v>
       </c>
-      <c r="F1560" s="15">
+      <c r="F1560" s="49">
         <f t="shared" si="25"/>
         <v>900</v>
       </c>
-      <c r="G1560" s="8" t="s">
+      <c r="G1560" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1560" s="5" t="s">
+      <c r="H1560" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1560" s="8" t="s">
+      <c r="I1560" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1560" s="8">
+      <c r="J1560" s="46">
         <v>6459</v>
       </c>
-      <c r="K1560" s="5" t="s">
+      <c r="K1560" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1561" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1561" s="42" t="s">
+    <row r="1561" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1561" s="44" t="s">
         <v>1172</v>
       </c>
-      <c r="B1561" s="25" t="s">
+      <c r="B1561" s="45" t="s">
         <v>1173</v>
       </c>
-      <c r="C1561" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1561" s="4">
+      <c r="C1561" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1561" s="47">
         <v>1</v>
       </c>
-      <c r="E1561" s="4">
+      <c r="E1561" s="47">
         <v>1000</v>
       </c>
-      <c r="F1561" s="15">
+      <c r="F1561" s="49">
         <f t="shared" si="25"/>
         <v>1000</v>
       </c>
-      <c r="G1561" s="8" t="s">
+      <c r="G1561" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1561" s="5" t="s">
+      <c r="H1561" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1561" s="8" t="s">
+      <c r="I1561" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1561" s="8">
+      <c r="J1561" s="46">
         <v>6459</v>
       </c>
-      <c r="K1561" s="5" t="s">
+      <c r="K1561" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1562" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1562" s="42" t="s">
+    <row r="1562" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1562" s="44" t="s">
         <v>337</v>
       </c>
-      <c r="B1562" s="25" t="s">
+      <c r="B1562" s="45" t="s">
         <v>2252</v>
       </c>
-      <c r="C1562" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1562" s="4">
+      <c r="C1562" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1562" s="47">
         <v>25</v>
       </c>
-      <c r="E1562" s="4">
+      <c r="E1562" s="47">
         <v>50</v>
       </c>
-      <c r="F1562" s="15">
+      <c r="F1562" s="49">
         <f t="shared" si="25"/>
         <v>1250</v>
       </c>
-      <c r="G1562" s="8" t="s">
+      <c r="G1562" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1562" s="5" t="s">
+      <c r="H1562" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1562" s="8" t="s">
+      <c r="I1562" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1562" s="8">
+      <c r="J1562" s="46">
         <v>6459</v>
       </c>
-      <c r="K1562" s="5" t="s">
+      <c r="K1562" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
-    <row r="1563" spans="1:11" s="19" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1563" s="42" t="s">
+    <row r="1563" spans="1:11" s="51" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1563" s="44" t="s">
         <v>2253</v>
       </c>
-      <c r="B1563" s="25" t="s">
+      <c r="B1563" s="45" t="s">
         <v>2254</v>
       </c>
-      <c r="C1563" s="8" t="s">
+      <c r="C1563" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="D1563" s="4">
+      <c r="D1563" s="47">
         <v>15</v>
       </c>
-      <c r="E1563" s="4">
+      <c r="E1563" s="47">
         <v>350</v>
       </c>
-      <c r="F1563" s="15">
+      <c r="F1563" s="49">
         <f t="shared" si="25"/>
         <v>5250</v>
       </c>
-      <c r="G1563" s="8" t="s">
+      <c r="G1563" s="46" t="s">
         <v>2310</v>
       </c>
-      <c r="H1563" s="5" t="s">
+      <c r="H1563" s="50" t="s">
         <v>2204</v>
       </c>
-      <c r="I1563" s="8" t="s">
+      <c r="I1563" s="46" t="s">
         <v>2336</v>
       </c>
-      <c r="J1563" s="8">
+      <c r="J1563" s="46">
         <v>6459</v>
       </c>
-      <c r="K1563" s="5" t="s">
+      <c r="K1563" s="50" t="s">
         <v>2134</v>
       </c>
     </row>
@@ -64621,7 +64674,7 @@
     <row r="1579" spans="1:11" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="F1579" s="17">
         <f>SUM(F2:F1578)</f>
-        <v>25910916.216196019</v>
+        <v>25847684.01619602</v>
       </c>
     </row>
   </sheetData>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416924DF-F880-4F53-89A7-1D98A0CC954C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8A7D73-0C59-498C-AF53-91F53B0BB08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,11 +14,22 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A1:$K1578</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8586" uniqueCount="2400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8586" uniqueCount="2399">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -7104,9 +7115,6 @@
   </si>
   <si>
     <t xml:space="preserve">فاصل زيت </t>
-  </si>
-  <si>
-    <t>19-4-2027</t>
   </si>
   <si>
     <t>6337</t>
@@ -8207,7 +8215,7 @@
     <row r="4" spans="1:15" s="12" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>21</v>
@@ -22786,7 +22794,7 @@
     <row r="409" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A409" s="13"/>
       <c r="B409" s="14" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="C409" s="15" t="s">
         <v>21</v>
@@ -25196,7 +25204,7 @@
     <row r="476" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A476" s="13"/>
       <c r="B476" s="14" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="C476" s="15" t="s">
         <v>21</v>
@@ -25338,7 +25346,7 @@
     <row r="480" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A480" s="13"/>
       <c r="B480" s="14" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="C480" s="15" t="s">
         <v>21</v>
@@ -25408,7 +25416,7 @@
     <row r="482" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A482" s="13"/>
       <c r="B482" s="14" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="C482" s="15" t="s">
         <v>21</v>
@@ -25624,7 +25632,7 @@
         <v>2080</v>
       </c>
       <c r="B488" s="14" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="C488" s="15" t="s">
         <v>21</v>
@@ -28102,7 +28110,7 @@
     <row r="557" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A557" s="13"/>
       <c r="B557" s="14" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="C557" s="15" t="s">
         <v>21</v>
@@ -33245,10 +33253,10 @@
     </row>
     <row r="700" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A700" s="59" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="B700" s="14" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="C700" s="15" t="s">
         <v>21</v>
@@ -33533,10 +33541,10 @@
     </row>
     <row r="708" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A708" s="59" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="B708" s="14" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="C708" s="15" t="s">
         <v>21</v>
@@ -34179,10 +34187,10 @@
     </row>
     <row r="726" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A726" s="59" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="B726" s="14" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="C726" s="15" t="s">
         <v>21</v>
@@ -34215,10 +34223,10 @@
     </row>
     <row r="727" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A727" s="59" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="B727" s="14" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="C727" s="15" t="s">
         <v>21</v>
@@ -35406,7 +35414,7 @@
         <v>1245</v>
       </c>
       <c r="B760" s="14" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="C760" s="15" t="s">
         <v>21</v>
@@ -37380,7 +37388,7 @@
     <row r="815" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A815" s="13"/>
       <c r="B815" s="14" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="C815" s="15" t="s">
         <v>21</v>
@@ -38924,7 +38932,7 @@
     <row r="858" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A858" s="13"/>
       <c r="B858" s="14" t="s">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="C858" s="15" t="s">
         <v>21</v>
@@ -39390,7 +39398,7 @@
     <row r="871" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A871" s="13"/>
       <c r="B871" s="14" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="C871" s="15" t="s">
         <v>21</v>
@@ -41334,7 +41342,7 @@
         <v>2277</v>
       </c>
       <c r="B925" s="14" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="C925" s="15" t="s">
         <v>21</v>
@@ -42296,7 +42304,7 @@
     <row r="952" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A952" s="13"/>
       <c r="B952" s="14" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="C952" s="15" t="s">
         <v>21</v>
@@ -43266,7 +43274,7 @@
     <row r="979" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A979" s="13"/>
       <c r="B979" s="14" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="C979" s="15" t="s">
         <v>21</v>
@@ -45672,7 +45680,7 @@
     <row r="1046" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1046" s="13"/>
       <c r="B1046" s="14" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="C1046" s="15" t="s">
         <v>21</v>
@@ -45706,7 +45714,7 @@
     <row r="1047" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1047" s="13"/>
       <c r="B1047" s="14" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
       <c r="C1047" s="15" t="s">
         <v>21</v>
@@ -47285,7 +47293,7 @@
     </row>
     <row r="1091" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1091" s="60" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="B1091" s="14" t="s">
         <v>2361</v>
@@ -47307,13 +47315,13 @@
         <v>1708</v>
       </c>
       <c r="H1091" s="18" t="s">
-        <v>2362</v>
+        <v>1666</v>
       </c>
       <c r="I1091" s="15" t="s">
         <v>1709</v>
       </c>
       <c r="J1091" s="15" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="K1091" s="18">
         <v>46117</v>
@@ -50700,10 +50708,10 @@
     </row>
     <row r="1186" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1186" s="60" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="B1186" s="14" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="C1186" s="15" t="s">
         <v>21</v>
@@ -54691,7 +54699,7 @@
     <row r="1297" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1297" s="13"/>
       <c r="B1297" s="14" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
       <c r="C1297" s="15" t="s">
         <v>21</v>
@@ -56237,7 +56245,7 @@
     <row r="1340" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1340" s="13"/>
       <c r="B1340" s="62" t="s">
-        <v>2391</v>
+        <v>2390</v>
       </c>
       <c r="C1340" s="15" t="s">
         <v>21</v>
@@ -57566,10 +57574,10 @@
     </row>
     <row r="1377" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1377" s="60" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="B1377" s="14" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="C1377" s="15" t="s">
         <v>21</v>
@@ -57602,10 +57610,10 @@
     </row>
     <row r="1378" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1378" s="60" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="B1378" s="14" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="C1378" s="15" t="s">
         <v>21</v>
@@ -57674,10 +57682,10 @@
     </row>
     <row r="1380" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1380" s="60" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="B1380" s="14" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="C1380" s="15" t="s">
         <v>21</v>
@@ -57746,10 +57754,10 @@
     </row>
     <row r="1382" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1382" s="60" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="B1382" s="14" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="C1382" s="15" t="s">
         <v>21</v>
@@ -58538,7 +58546,7 @@
     </row>
     <row r="1404" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1404" s="60" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="B1404" s="14" t="s">
         <v>2103</v>
@@ -59079,7 +59087,7 @@
     <row r="1419" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1419" s="13"/>
       <c r="B1419" s="14" t="s">
-        <v>2392</v>
+        <v>2391</v>
       </c>
       <c r="C1419" s="15" t="s">
         <v>21</v>
@@ -62365,7 +62373,7 @@
         <v>96</v>
       </c>
       <c r="B1511" s="14" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
       <c r="C1511" s="15" t="s">
         <v>21</v>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8A7D73-0C59-498C-AF53-91F53B0BB08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CEA2FD-42BA-416C-8F58-88BA7E874C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7087,24 +7087,12 @@
     <t>فلتر لحام 5/8</t>
   </si>
   <si>
-    <t>بروفيل باب تلاجة PVC موديل A141</t>
-  </si>
-  <si>
     <t>19/4/2026</t>
   </si>
   <si>
     <t>سماريل</t>
   </si>
   <si>
-    <t>بروفيل باب تلاجة PVC موديل A142</t>
-  </si>
-  <si>
-    <t>بروفيل باب تلاجة PVC موديل A143</t>
-  </si>
-  <si>
-    <t>بروفيل باب تلاجة PVC موديل A144</t>
-  </si>
-  <si>
     <t>افرلود 5/8 5</t>
   </si>
   <si>
@@ -7226,6 +7214,18 @@
   </si>
   <si>
     <t>بنطه كبايه 19</t>
+  </si>
+  <si>
+    <t>بروفيل باب ثلاجة PVC موديل A141</t>
+  </si>
+  <si>
+    <t>بروفيل باب ثلاجة PVC موديل A142</t>
+  </si>
+  <si>
+    <t>بروفيل باب ثلاجة PVC موديل A143</t>
+  </si>
+  <si>
+    <t>بروفيل باب ثلاجة PVC موديل A144</t>
   </si>
 </sst>
 </file>
@@ -8215,7 +8215,7 @@
     <row r="4" spans="1:15" s="12" customFormat="1" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A4" s="13"/>
       <c r="B4" s="14" t="s">
-        <v>2395</v>
+        <v>2391</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>21</v>
@@ -22794,7 +22794,7 @@
     <row r="409" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A409" s="13"/>
       <c r="B409" s="14" t="s">
-        <v>2396</v>
+        <v>2392</v>
       </c>
       <c r="C409" s="15" t="s">
         <v>21</v>
@@ -25204,7 +25204,7 @@
     <row r="476" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A476" s="13"/>
       <c r="B476" s="14" t="s">
-        <v>2380</v>
+        <v>2376</v>
       </c>
       <c r="C476" s="15" t="s">
         <v>21</v>
@@ -25346,7 +25346,7 @@
     <row r="480" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A480" s="13"/>
       <c r="B480" s="14" t="s">
-        <v>2379</v>
+        <v>2375</v>
       </c>
       <c r="C480" s="15" t="s">
         <v>21</v>
@@ -25416,7 +25416,7 @@
     <row r="482" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A482" s="13"/>
       <c r="B482" s="14" t="s">
-        <v>2378</v>
+        <v>2374</v>
       </c>
       <c r="C482" s="15" t="s">
         <v>21</v>
@@ -25632,7 +25632,7 @@
         <v>2080</v>
       </c>
       <c r="B488" s="14" t="s">
-        <v>2377</v>
+        <v>2373</v>
       </c>
       <c r="C488" s="15" t="s">
         <v>21</v>
@@ -28110,7 +28110,7 @@
     <row r="557" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A557" s="13"/>
       <c r="B557" s="14" t="s">
-        <v>2393</v>
+        <v>2389</v>
       </c>
       <c r="C557" s="15" t="s">
         <v>21</v>
@@ -33253,10 +33253,10 @@
     </row>
     <row r="700" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A700" s="59" t="s">
-        <v>2383</v>
+        <v>2379</v>
       </c>
       <c r="B700" s="14" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
       <c r="C700" s="15" t="s">
         <v>21</v>
@@ -33541,10 +33541,10 @@
     </row>
     <row r="708" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A708" s="59" t="s">
-        <v>2385</v>
+        <v>2381</v>
       </c>
       <c r="B708" s="14" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
       <c r="C708" s="15" t="s">
         <v>21</v>
@@ -34187,10 +34187,10 @@
     </row>
     <row r="726" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A726" s="59" t="s">
-        <v>2385</v>
+        <v>2381</v>
       </c>
       <c r="B726" s="14" t="s">
-        <v>2384</v>
+        <v>2380</v>
       </c>
       <c r="C726" s="15" t="s">
         <v>21</v>
@@ -34223,10 +34223,10 @@
     </row>
     <row r="727" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A727" s="59" t="s">
-        <v>2383</v>
+        <v>2379</v>
       </c>
       <c r="B727" s="14" t="s">
-        <v>2382</v>
+        <v>2378</v>
       </c>
       <c r="C727" s="15" t="s">
         <v>21</v>
@@ -35414,7 +35414,7 @@
         <v>1245</v>
       </c>
       <c r="B760" s="14" t="s">
-        <v>2386</v>
+        <v>2382</v>
       </c>
       <c r="C760" s="15" t="s">
         <v>21</v>
@@ -37388,7 +37388,7 @@
     <row r="815" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A815" s="13"/>
       <c r="B815" s="14" t="s">
-        <v>2387</v>
+        <v>2383</v>
       </c>
       <c r="C815" s="15" t="s">
         <v>21</v>
@@ -38932,7 +38932,7 @@
     <row r="858" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A858" s="13"/>
       <c r="B858" s="14" t="s">
-        <v>2388</v>
+        <v>2384</v>
       </c>
       <c r="C858" s="15" t="s">
         <v>21</v>
@@ -39398,7 +39398,7 @@
     <row r="871" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A871" s="13"/>
       <c r="B871" s="14" t="s">
-        <v>2394</v>
+        <v>2390</v>
       </c>
       <c r="C871" s="15" t="s">
         <v>21</v>
@@ -41342,7 +41342,7 @@
         <v>2277</v>
       </c>
       <c r="B925" s="14" t="s">
-        <v>2376</v>
+        <v>2372</v>
       </c>
       <c r="C925" s="15" t="s">
         <v>21</v>
@@ -42304,7 +42304,7 @@
     <row r="952" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A952" s="13"/>
       <c r="B952" s="14" t="s">
-        <v>2381</v>
+        <v>2377</v>
       </c>
       <c r="C952" s="15" t="s">
         <v>21</v>
@@ -43274,7 +43274,7 @@
     <row r="979" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A979" s="13"/>
       <c r="B979" s="14" t="s">
-        <v>2389</v>
+        <v>2385</v>
       </c>
       <c r="C979" s="15" t="s">
         <v>21</v>
@@ -45680,7 +45680,7 @@
     <row r="1046" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1046" s="13"/>
       <c r="B1046" s="14" t="s">
-        <v>2397</v>
+        <v>2393</v>
       </c>
       <c r="C1046" s="15" t="s">
         <v>21</v>
@@ -45714,7 +45714,7 @@
     <row r="1047" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1047" s="13"/>
       <c r="B1047" s="14" t="s">
-        <v>2398</v>
+        <v>2394</v>
       </c>
       <c r="C1047" s="15" t="s">
         <v>21</v>
@@ -47152,7 +47152,7 @@
     <row r="1087" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1087" s="13"/>
       <c r="B1087" s="14" t="s">
-        <v>2360</v>
+        <v>2356</v>
       </c>
       <c r="C1087" s="15" t="s">
         <v>21</v>
@@ -47293,10 +47293,10 @@
     </row>
     <row r="1091" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1091" s="60" t="s">
-        <v>2363</v>
+        <v>2359</v>
       </c>
       <c r="B1091" s="14" t="s">
-        <v>2361</v>
+        <v>2357</v>
       </c>
       <c r="C1091" s="15" t="s">
         <v>21</v>
@@ -47321,7 +47321,7 @@
         <v>1709</v>
       </c>
       <c r="J1091" s="15" t="s">
-        <v>2362</v>
+        <v>2358</v>
       </c>
       <c r="K1091" s="18">
         <v>46117</v>
@@ -50708,10 +50708,10 @@
     </row>
     <row r="1186" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1186" s="60" t="s">
-        <v>2375</v>
+        <v>2371</v>
       </c>
       <c r="B1186" s="14" t="s">
-        <v>2374</v>
+        <v>2370</v>
       </c>
       <c r="C1186" s="15" t="s">
         <v>21</v>
@@ -54699,7 +54699,7 @@
     <row r="1297" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1297" s="13"/>
       <c r="B1297" s="14" t="s">
-        <v>2392</v>
+        <v>2388</v>
       </c>
       <c r="C1297" s="15" t="s">
         <v>21</v>
@@ -56245,7 +56245,7 @@
     <row r="1340" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1340" s="13"/>
       <c r="B1340" s="62" t="s">
-        <v>2390</v>
+        <v>2386</v>
       </c>
       <c r="C1340" s="15" t="s">
         <v>21</v>
@@ -57574,10 +57574,10 @@
     </row>
     <row r="1377" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1377" s="60" t="s">
-        <v>2367</v>
+        <v>2363</v>
       </c>
       <c r="B1377" s="14" t="s">
-        <v>2365</v>
+        <v>2361</v>
       </c>
       <c r="C1377" s="15" t="s">
         <v>21</v>
@@ -57610,10 +57610,10 @@
     </row>
     <row r="1378" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1378" s="60" t="s">
-        <v>2368</v>
+        <v>2364</v>
       </c>
       <c r="B1378" s="14" t="s">
-        <v>2366</v>
+        <v>2362</v>
       </c>
       <c r="C1378" s="15" t="s">
         <v>21</v>
@@ -57682,10 +57682,10 @@
     </row>
     <row r="1380" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1380" s="60" t="s">
-        <v>2370</v>
+        <v>2366</v>
       </c>
       <c r="B1380" s="14" t="s">
-        <v>2369</v>
+        <v>2365</v>
       </c>
       <c r="C1380" s="15" t="s">
         <v>21</v>
@@ -57754,10 +57754,10 @@
     </row>
     <row r="1382" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1382" s="60" t="s">
-        <v>2372</v>
+        <v>2368</v>
       </c>
       <c r="B1382" s="14" t="s">
-        <v>2371</v>
+        <v>2367</v>
       </c>
       <c r="C1382" s="15" t="s">
         <v>21</v>
@@ -58546,7 +58546,7 @@
     </row>
     <row r="1404" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1404" s="60" t="s">
-        <v>2373</v>
+        <v>2369</v>
       </c>
       <c r="B1404" s="14" t="s">
         <v>2103</v>
@@ -59087,7 +59087,7 @@
     <row r="1419" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1419" s="13"/>
       <c r="B1419" s="14" t="s">
-        <v>2391</v>
+        <v>2387</v>
       </c>
       <c r="C1419" s="15" t="s">
         <v>21</v>
@@ -62373,7 +62373,7 @@
         <v>96</v>
       </c>
       <c r="B1511" s="14" t="s">
-        <v>2364</v>
+        <v>2360</v>
       </c>
       <c r="C1511" s="15" t="s">
         <v>21</v>
@@ -64170,10 +64170,10 @@
     </row>
     <row r="1561" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1561" s="59" t="s">
-        <v>2359</v>
+        <v>2355</v>
       </c>
       <c r="B1561" s="14" t="s">
-        <v>2358</v>
+        <v>2354</v>
       </c>
       <c r="C1561" s="15" t="s">
         <v>21</v>
@@ -65895,7 +65895,7 @@
     <row r="1609" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1609" s="19"/>
       <c r="B1609" s="20" t="s">
-        <v>2352</v>
+        <v>2395</v>
       </c>
       <c r="C1609" s="21" t="s">
         <v>46</v>
@@ -65914,10 +65914,10 @@
         <v>38</v>
       </c>
       <c r="H1609" s="24" t="s">
+        <v>2352</v>
+      </c>
+      <c r="I1609" s="21" t="s">
         <v>2353</v>
-      </c>
-      <c r="I1609" s="21" t="s">
-        <v>2354</v>
       </c>
       <c r="J1609" s="21">
         <v>6454</v>
@@ -65929,7 +65929,7 @@
     <row r="1610" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1610" s="19"/>
       <c r="B1610" s="20" t="s">
-        <v>2355</v>
+        <v>2396</v>
       </c>
       <c r="C1610" s="21" t="s">
         <v>46</v>
@@ -65948,10 +65948,10 @@
         <v>38</v>
       </c>
       <c r="H1610" s="24" t="s">
+        <v>2352</v>
+      </c>
+      <c r="I1610" s="21" t="s">
         <v>2353</v>
-      </c>
-      <c r="I1610" s="21" t="s">
-        <v>2354</v>
       </c>
       <c r="J1610" s="21">
         <v>6454</v>
@@ -65963,7 +65963,7 @@
     <row r="1611" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1611" s="19"/>
       <c r="B1611" s="20" t="s">
-        <v>2356</v>
+        <v>2397</v>
       </c>
       <c r="C1611" s="21" t="s">
         <v>46</v>
@@ -65982,10 +65982,10 @@
         <v>38</v>
       </c>
       <c r="H1611" s="24" t="s">
+        <v>2352</v>
+      </c>
+      <c r="I1611" s="21" t="s">
         <v>2353</v>
-      </c>
-      <c r="I1611" s="21" t="s">
-        <v>2354</v>
       </c>
       <c r="J1611" s="21">
         <v>6454</v>
@@ -65997,7 +65997,7 @@
     <row r="1612" spans="1:11" ht="24.95" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1612" s="19"/>
       <c r="B1612" s="20" t="s">
-        <v>2357</v>
+        <v>2398</v>
       </c>
       <c r="C1612" s="21" t="s">
         <v>46</v>
@@ -66016,10 +66016,10 @@
         <v>38</v>
       </c>
       <c r="H1612" s="24" t="s">
+        <v>2352</v>
+      </c>
+      <c r="I1612" s="21" t="s">
         <v>2353</v>
-      </c>
-      <c r="I1612" s="21" t="s">
-        <v>2354</v>
       </c>
       <c r="J1612" s="21">
         <v>6454</v>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0240706-55E0-443F-BA93-F7241DF4FDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2D943C-3A61-4F88-9454-38EF4E332D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8586" uniqueCount="2399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8586" uniqueCount="2400">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -7226,6 +7226,9 @@
   </si>
   <si>
     <t>بروفيل باب ثلاجة PVC موديل A144</t>
+  </si>
+  <si>
+    <t>10106023</t>
   </si>
 </sst>
 </file>
@@ -57210,7 +57213,7 @@
     </row>
     <row r="1367" spans="1:11" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1367" s="19" t="s">
-        <v>162</v>
+        <v>2399</v>
       </c>
       <c r="B1367" s="20" t="s">
         <v>2054</v>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2D943C-3A61-4F88-9454-38EF4E332D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51B67B4-97C1-4057-910D-73BAFDAEA52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50354,7 +50354,7 @@
         <v>1829</v>
       </c>
       <c r="C1176" s="21" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D1176" s="22">
         <v>1</v>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEC0CB7-DC11-43CC-A8E4-5220CA38E0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3D222C-AE0A-4659-98F5-8DE72A8D831C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9259" uniqueCount="2581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9258" uniqueCount="2581">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -7781,7 +7781,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7852,12 +7852,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -7994,7 +7988,7 @@
     <xf numFmtId="12" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8012,7 +8006,7 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8024,8 +8018,8 @@
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -8037,11 +8031,11 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8327,7 +8321,7 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="23" customWidth="1"/>
-    <col min="2" max="2" width="52.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" style="34" customWidth="1"/>
     <col min="3" max="3" width="7.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" style="2" customWidth="1"/>
@@ -66556,7 +66550,7 @@
       <c r="A1621" s="30" t="s">
         <v>2418</v>
       </c>
-      <c r="B1621" s="33" t="s">
+      <c r="B1621" s="8" t="s">
         <v>2419</v>
       </c>
       <c r="C1621" s="7" t="s">
@@ -66589,9 +66583,7 @@
       </c>
     </row>
     <row r="1622" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1622" s="30" t="s">
-        <v>2377</v>
-      </c>
+      <c r="A1622" s="30"/>
       <c r="B1622" s="7" t="s">
         <v>1534</v>
       </c>
@@ -68102,7 +68094,7 @@
         <v>834</v>
       </c>
       <c r="C1664" s="7" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D1664" s="8">
         <v>2</v>
@@ -69387,11 +69379,10 @@
       </c>
     </row>
     <row r="1700" spans="1:11" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B1700" s="20"/>
       <c r="C1700" s="20"/>
       <c r="D1700" s="21"/>
       <c r="E1700" s="21"/>
-      <c r="F1700" s="34">
+      <c r="F1700" s="33">
         <f>SUM(F2:F1699)</f>
         <v>27668891.124196012</v>
       </c>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3D222C-AE0A-4659-98F5-8DE72A8D831C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6069646E-B212-4C28-BD86-905E2D0152C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6069646E-B212-4C28-BD86-905E2D0152C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB866F8F-3AC0-47F0-B6CA-86F5AB4C425A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9258" uniqueCount="2581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9258" uniqueCount="2580">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -7235,9 +7235,6 @@
   </si>
   <si>
     <t>11-2-2026</t>
-  </si>
-  <si>
-    <t>الورشه الفنيه</t>
   </si>
   <si>
     <t>6224</t>
@@ -9200,7 +9197,7 @@
         <v>72</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>62</v>
@@ -13843,7 +13840,7 @@
         <v>72</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="C154" s="7" t="s">
         <v>21</v>
@@ -38316,7 +38313,7 @@
         <v>11576</v>
       </c>
       <c r="G834" s="7" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="H834" s="10" t="s">
         <v>1391</v>
@@ -42270,7 +42267,7 @@
         <v>7800</v>
       </c>
       <c r="G944" s="7" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="H944" s="10">
         <v>46057</v>
@@ -66285,21 +66282,21 @@
         <v>2401</v>
       </c>
       <c r="I1613" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J1613" s="7" t="s">
         <v>2402</v>
       </c>
-      <c r="J1613" s="7" t="s">
+      <c r="K1613" s="10" t="s">
         <v>2403</v>
-      </c>
-      <c r="K1613" s="10" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="1614" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1614" s="30" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B1614" s="7" t="s">
         <v>2405</v>
-      </c>
-      <c r="B1614" s="7" t="s">
-        <v>2406</v>
       </c>
       <c r="C1614" s="7" t="s">
         <v>21</v>
@@ -66321,21 +66318,21 @@
         <v>2401</v>
       </c>
       <c r="I1614" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J1614" s="7" t="s">
         <v>2402</v>
       </c>
-      <c r="J1614" s="7" t="s">
+      <c r="K1614" s="10" t="s">
         <v>2403</v>
-      </c>
-      <c r="K1614" s="10" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="1615" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1615" s="30" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B1615" s="7" t="s">
         <v>2407</v>
-      </c>
-      <c r="B1615" s="7" t="s">
-        <v>2408</v>
       </c>
       <c r="C1615" s="7" t="s">
         <v>21</v>
@@ -66357,13 +66354,13 @@
         <v>2401</v>
       </c>
       <c r="I1615" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J1615" s="7" t="s">
         <v>2402</v>
       </c>
-      <c r="J1615" s="7" t="s">
+      <c r="K1615" s="10" t="s">
         <v>2403</v>
-      </c>
-      <c r="K1615" s="10" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="1616" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -66371,7 +66368,7 @@
         <v>1559</v>
       </c>
       <c r="B1616" s="7" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="C1616" s="7" t="s">
         <v>21</v>
@@ -66393,21 +66390,21 @@
         <v>2401</v>
       </c>
       <c r="I1616" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J1616" s="7" t="s">
         <v>2402</v>
       </c>
-      <c r="J1616" s="7" t="s">
+      <c r="K1616" s="10" t="s">
         <v>2403</v>
-      </c>
-      <c r="K1616" s="10" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="1617" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1617" s="30" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B1617" s="7" t="s">
         <v>2410</v>
-      </c>
-      <c r="B1617" s="7" t="s">
-        <v>2411</v>
       </c>
       <c r="C1617" s="7" t="s">
         <v>21</v>
@@ -66429,21 +66426,21 @@
         <v>2401</v>
       </c>
       <c r="I1617" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J1617" s="7" t="s">
         <v>2402</v>
       </c>
-      <c r="J1617" s="7" t="s">
+      <c r="K1617" s="10" t="s">
         <v>2403</v>
-      </c>
-      <c r="K1617" s="10" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="1618" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1618" s="30" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B1618" s="7" t="s">
         <v>2412</v>
-      </c>
-      <c r="B1618" s="7" t="s">
-        <v>2413</v>
       </c>
       <c r="C1618" s="7" t="s">
         <v>21</v>
@@ -66465,21 +66462,21 @@
         <v>2401</v>
       </c>
       <c r="I1618" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J1618" s="7" t="s">
         <v>2402</v>
       </c>
-      <c r="J1618" s="7" t="s">
+      <c r="K1618" s="10" t="s">
         <v>2403</v>
-      </c>
-      <c r="K1618" s="10" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="1619" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1619" s="30" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B1619" s="7" t="s">
         <v>2414</v>
-      </c>
-      <c r="B1619" s="7" t="s">
-        <v>2415</v>
       </c>
       <c r="C1619" s="7" t="s">
         <v>21</v>
@@ -66501,13 +66498,13 @@
         <v>2401</v>
       </c>
       <c r="I1619" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J1619" s="7" t="s">
         <v>2402</v>
       </c>
-      <c r="J1619" s="7" t="s">
+      <c r="K1619" s="10" t="s">
         <v>2403</v>
-      </c>
-      <c r="K1619" s="10" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="1620" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -66515,7 +66512,7 @@
         <v>1549</v>
       </c>
       <c r="B1620" s="7" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="C1620" s="7" t="s">
         <v>21</v>
@@ -66537,21 +66534,21 @@
         <v>2401</v>
       </c>
       <c r="I1620" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="J1620" s="7" t="s">
         <v>2402</v>
       </c>
-      <c r="J1620" s="7" t="s">
+      <c r="K1620" s="10" t="s">
         <v>2403</v>
-      </c>
-      <c r="K1620" s="10" t="s">
-        <v>2404</v>
       </c>
     </row>
     <row r="1621" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1621" s="30" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B1621" s="8" t="s">
         <v>2418</v>
-      </c>
-      <c r="B1621" s="8" t="s">
-        <v>2419</v>
       </c>
       <c r="C1621" s="7" t="s">
         <v>21</v>
@@ -66567,16 +66564,16 @@
         <v>4914</v>
       </c>
       <c r="G1621" s="7" t="s">
+        <v>2419</v>
+      </c>
+      <c r="H1621" s="10" t="s">
         <v>2420</v>
       </c>
-      <c r="H1621" s="10" t="s">
+      <c r="I1621" s="7" t="s">
+        <v>2416</v>
+      </c>
+      <c r="J1621" s="7" t="s">
         <v>2421</v>
-      </c>
-      <c r="I1621" s="7" t="s">
-        <v>2417</v>
-      </c>
-      <c r="J1621" s="7" t="s">
-        <v>2422</v>
       </c>
       <c r="K1621" s="10" t="s">
         <v>1153</v>
@@ -66618,7 +66615,7 @@
     </row>
     <row r="1623" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1623" s="30" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="B1623" s="7" t="s">
         <v>1535</v>
@@ -66654,10 +66651,10 @@
     </row>
     <row r="1624" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1624" s="30" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B1624" s="7" t="s">
         <v>2424</v>
-      </c>
-      <c r="B1624" s="7" t="s">
-        <v>2425</v>
       </c>
       <c r="C1624" s="7" t="s">
         <v>21</v>
@@ -66673,27 +66670,27 @@
         <v>4030</v>
       </c>
       <c r="G1624" s="7" t="s">
+        <v>2425</v>
+      </c>
+      <c r="H1624" s="10" t="s">
         <v>2426</v>
       </c>
-      <c r="H1624" s="10" t="s">
+      <c r="I1624" s="7" t="s">
         <v>2427</v>
       </c>
-      <c r="I1624" s="7" t="s">
+      <c r="J1624" s="7" t="s">
         <v>2428</v>
       </c>
-      <c r="J1624" s="7" t="s">
+      <c r="K1624" s="10" t="s">
         <v>2429</v>
-      </c>
-      <c r="K1624" s="10" t="s">
-        <v>2430</v>
       </c>
     </row>
     <row r="1625" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1625" s="30" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B1625" s="7" t="s">
         <v>2431</v>
-      </c>
-      <c r="B1625" s="7" t="s">
-        <v>2432</v>
       </c>
       <c r="C1625" s="7" t="s">
         <v>46</v>
@@ -66709,19 +66706,19 @@
         <v>7000</v>
       </c>
       <c r="G1625" s="7" t="s">
+        <v>2425</v>
+      </c>
+      <c r="H1625" s="10" t="s">
         <v>2426</v>
       </c>
-      <c r="H1625" s="10" t="s">
+      <c r="I1625" s="7" t="s">
         <v>2427</v>
       </c>
-      <c r="I1625" s="7" t="s">
+      <c r="J1625" s="7" t="s">
         <v>2428</v>
       </c>
-      <c r="J1625" s="7" t="s">
+      <c r="K1625" s="10" t="s">
         <v>2429</v>
-      </c>
-      <c r="K1625" s="10" t="s">
-        <v>2430</v>
       </c>
     </row>
     <row r="1626" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -66729,7 +66726,7 @@
         <v>609</v>
       </c>
       <c r="B1626" s="7" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="C1626" s="7" t="s">
         <v>21</v>
@@ -66745,19 +66742,19 @@
         <v>606315</v>
       </c>
       <c r="G1626" s="7" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="H1626" s="10" t="s">
         <v>1783</v>
       </c>
       <c r="I1626" s="7" t="s">
+        <v>2434</v>
+      </c>
+      <c r="J1626" s="7" t="s">
         <v>2435</v>
       </c>
-      <c r="J1626" s="7" t="s">
+      <c r="K1626" s="10" t="s">
         <v>2436</v>
-      </c>
-      <c r="K1626" s="10" t="s">
-        <v>2437</v>
       </c>
     </row>
     <row r="1627" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -66765,7 +66762,7 @@
         <v>1737</v>
       </c>
       <c r="B1627" s="7" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="C1627" s="7" t="s">
         <v>21</v>
@@ -66781,19 +66778,19 @@
         <v>227368.08</v>
       </c>
       <c r="G1627" s="7" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="H1627" s="10" t="s">
         <v>1783</v>
       </c>
       <c r="I1627" s="7" t="s">
+        <v>2434</v>
+      </c>
+      <c r="J1627" s="7" t="s">
         <v>2435</v>
       </c>
-      <c r="J1627" s="7" t="s">
+      <c r="K1627" s="10" t="s">
         <v>2436</v>
-      </c>
-      <c r="K1627" s="10" t="s">
-        <v>2437</v>
       </c>
     </row>
     <row r="1628" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -66801,7 +66798,7 @@
         <v>577</v>
       </c>
       <c r="B1628" s="7" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="C1628" s="7" t="s">
         <v>21</v>
@@ -66817,27 +66814,27 @@
         <v>137369.81</v>
       </c>
       <c r="G1628" s="7" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="H1628" s="10" t="s">
         <v>1783</v>
       </c>
       <c r="I1628" s="7" t="s">
+        <v>2434</v>
+      </c>
+      <c r="J1628" s="7" t="s">
         <v>2435</v>
       </c>
-      <c r="J1628" s="7" t="s">
+      <c r="K1628" s="10" t="s">
         <v>2436</v>
-      </c>
-      <c r="K1628" s="10" t="s">
-        <v>2437</v>
       </c>
     </row>
     <row r="1629" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1629" s="30" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B1629" s="7" t="s">
         <v>2440</v>
-      </c>
-      <c r="B1629" s="7" t="s">
-        <v>2441</v>
       </c>
       <c r="C1629" s="7" t="s">
         <v>21</v>
@@ -66853,7 +66850,7 @@
         <v>3750</v>
       </c>
       <c r="G1629" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1629" s="10" t="s">
         <v>1789</v>
@@ -66862,7 +66859,7 @@
         <v>534</v>
       </c>
       <c r="J1629" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1629" s="10" t="s">
         <v>1793</v>
@@ -66870,10 +66867,10 @@
     </row>
     <row r="1630" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1630" s="30" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B1630" s="7" t="s">
         <v>2444</v>
-      </c>
-      <c r="B1630" s="7" t="s">
-        <v>2445</v>
       </c>
       <c r="C1630" s="7" t="s">
         <v>21</v>
@@ -66889,7 +66886,7 @@
         <v>18750</v>
       </c>
       <c r="G1630" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1630" s="10" t="s">
         <v>1789</v>
@@ -66898,7 +66895,7 @@
         <v>534</v>
       </c>
       <c r="J1630" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1630" s="10" t="s">
         <v>1793</v>
@@ -66925,7 +66922,7 @@
         <v>18750</v>
       </c>
       <c r="G1631" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1631" s="10" t="s">
         <v>1789</v>
@@ -66934,7 +66931,7 @@
         <v>534</v>
       </c>
       <c r="J1631" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1631" s="10" t="s">
         <v>1793</v>
@@ -66942,10 +66939,10 @@
     </row>
     <row r="1632" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1632" s="30" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B1632" s="7" t="s">
         <v>2446</v>
-      </c>
-      <c r="B1632" s="7" t="s">
-        <v>2447</v>
       </c>
       <c r="C1632" s="7" t="s">
         <v>21</v>
@@ -66961,7 +66958,7 @@
         <v>300</v>
       </c>
       <c r="G1632" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1632" s="10" t="s">
         <v>1789</v>
@@ -66970,7 +66967,7 @@
         <v>534</v>
       </c>
       <c r="J1632" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1632" s="10" t="s">
         <v>1793</v>
@@ -66978,10 +66975,10 @@
     </row>
     <row r="1633" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1633" s="30" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B1633" s="7" t="s">
         <v>2448</v>
-      </c>
-      <c r="B1633" s="7" t="s">
-        <v>2449</v>
       </c>
       <c r="C1633" s="7" t="s">
         <v>21</v>
@@ -66997,7 +66994,7 @@
         <v>200</v>
       </c>
       <c r="G1633" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1633" s="10" t="s">
         <v>1789</v>
@@ -67006,7 +67003,7 @@
         <v>534</v>
       </c>
       <c r="J1633" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1633" s="10" t="s">
         <v>1793</v>
@@ -67014,10 +67011,10 @@
     </row>
     <row r="1634" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1634" s="30" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B1634" s="7" t="s">
         <v>2450</v>
-      </c>
-      <c r="B1634" s="7" t="s">
-        <v>2451</v>
       </c>
       <c r="C1634" s="7" t="s">
         <v>21</v>
@@ -67033,7 +67030,7 @@
         <v>3375</v>
       </c>
       <c r="G1634" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1634" s="10" t="s">
         <v>1789</v>
@@ -67042,7 +67039,7 @@
         <v>534</v>
       </c>
       <c r="J1634" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1634" s="10" t="s">
         <v>1793</v>
@@ -67053,7 +67050,7 @@
         <v>537</v>
       </c>
       <c r="B1635" s="7" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="C1635" s="7" t="s">
         <v>21</v>
@@ -67069,7 +67066,7 @@
         <v>750</v>
       </c>
       <c r="G1635" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1635" s="10" t="s">
         <v>1789</v>
@@ -67078,7 +67075,7 @@
         <v>534</v>
       </c>
       <c r="J1635" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1635" s="10" t="s">
         <v>1793</v>
@@ -67086,10 +67083,10 @@
     </row>
     <row r="1636" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1636" s="30" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B1636" s="7" t="s">
         <v>2453</v>
-      </c>
-      <c r="B1636" s="7" t="s">
-        <v>2454</v>
       </c>
       <c r="C1636" s="7" t="s">
         <v>21</v>
@@ -67105,7 +67102,7 @@
         <v>1500</v>
       </c>
       <c r="G1636" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1636" s="10" t="s">
         <v>1789</v>
@@ -67114,7 +67111,7 @@
         <v>534</v>
       </c>
       <c r="J1636" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1636" s="10" t="s">
         <v>1793</v>
@@ -67122,10 +67119,10 @@
     </row>
     <row r="1637" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1637" s="30" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B1637" s="7" t="s">
         <v>2455</v>
-      </c>
-      <c r="B1637" s="7" t="s">
-        <v>2456</v>
       </c>
       <c r="C1637" s="7" t="s">
         <v>21</v>
@@ -67141,7 +67138,7 @@
         <v>4800</v>
       </c>
       <c r="G1637" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1637" s="10" t="s">
         <v>1789</v>
@@ -67150,7 +67147,7 @@
         <v>534</v>
       </c>
       <c r="J1637" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1637" s="10" t="s">
         <v>1793</v>
@@ -67177,7 +67174,7 @@
         <v>1250</v>
       </c>
       <c r="G1638" s="7" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="H1638" s="10" t="s">
         <v>1789</v>
@@ -67186,7 +67183,7 @@
         <v>534</v>
       </c>
       <c r="J1638" s="7" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="K1638" s="10" t="s">
         <v>1793</v>
@@ -67197,7 +67194,7 @@
         <v>847</v>
       </c>
       <c r="B1639" s="7" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="C1639" s="7" t="s">
         <v>21</v>
@@ -67213,7 +67210,7 @@
         <v>5625</v>
       </c>
       <c r="G1639" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1639" s="10" t="s">
         <v>1789</v>
@@ -67222,7 +67219,7 @@
         <v>534</v>
       </c>
       <c r="J1639" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1639" s="10" t="s">
         <v>1793</v>
@@ -67230,10 +67227,10 @@
     </row>
     <row r="1640" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1640" s="30" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B1640" s="7" t="s">
         <v>2460</v>
-      </c>
-      <c r="B1640" s="7" t="s">
-        <v>2461</v>
       </c>
       <c r="C1640" s="7" t="s">
         <v>46</v>
@@ -67249,7 +67246,7 @@
         <v>2250</v>
       </c>
       <c r="G1640" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1640" s="10" t="s">
         <v>1789</v>
@@ -67258,7 +67255,7 @@
         <v>534</v>
       </c>
       <c r="J1640" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1640" s="10" t="s">
         <v>1793</v>
@@ -67266,10 +67263,10 @@
     </row>
     <row r="1641" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1641" s="30" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B1641" s="7" t="s">
         <v>2462</v>
-      </c>
-      <c r="B1641" s="7" t="s">
-        <v>2463</v>
       </c>
       <c r="C1641" s="7" t="s">
         <v>21</v>
@@ -67285,7 +67282,7 @@
         <v>2250</v>
       </c>
       <c r="G1641" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1641" s="10" t="s">
         <v>1789</v>
@@ -67294,7 +67291,7 @@
         <v>534</v>
       </c>
       <c r="J1641" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1641" s="10" t="s">
         <v>1793</v>
@@ -67302,10 +67299,10 @@
     </row>
     <row r="1642" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1642" s="30" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B1642" s="7" t="s">
         <v>2464</v>
-      </c>
-      <c r="B1642" s="7" t="s">
-        <v>2465</v>
       </c>
       <c r="C1642" s="7" t="s">
         <v>21</v>
@@ -67321,7 +67318,7 @@
         <v>575</v>
       </c>
       <c r="G1642" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1642" s="10" t="s">
         <v>1789</v>
@@ -67330,7 +67327,7 @@
         <v>534</v>
       </c>
       <c r="J1642" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1642" s="10" t="s">
         <v>1793</v>
@@ -67338,7 +67335,7 @@
     </row>
     <row r="1643" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1643" s="30" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="B1643" s="7" t="s">
         <v>2065</v>
@@ -67357,7 +67354,7 @@
         <v>500</v>
       </c>
       <c r="G1643" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1643" s="10" t="s">
         <v>1789</v>
@@ -67366,7 +67363,7 @@
         <v>534</v>
       </c>
       <c r="J1643" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1643" s="10" t="s">
         <v>1793</v>
@@ -67374,10 +67371,10 @@
     </row>
     <row r="1644" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1644" s="30" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B1644" s="7" t="s">
         <v>2453</v>
-      </c>
-      <c r="B1644" s="7" t="s">
-        <v>2454</v>
       </c>
       <c r="C1644" s="7" t="s">
         <v>21</v>
@@ -67393,7 +67390,7 @@
         <v>90</v>
       </c>
       <c r="G1644" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1644" s="10" t="s">
         <v>1789</v>
@@ -67402,7 +67399,7 @@
         <v>534</v>
       </c>
       <c r="J1644" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1644" s="10" t="s">
         <v>1793</v>
@@ -67410,10 +67407,10 @@
     </row>
     <row r="1645" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1645" s="30" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B1645" s="7" t="s">
         <v>2467</v>
-      </c>
-      <c r="B1645" s="7" t="s">
-        <v>2468</v>
       </c>
       <c r="C1645" s="7" t="s">
         <v>21</v>
@@ -67429,7 +67426,7 @@
         <v>675</v>
       </c>
       <c r="G1645" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1645" s="10" t="s">
         <v>1789</v>
@@ -67438,7 +67435,7 @@
         <v>534</v>
       </c>
       <c r="J1645" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1645" s="10" t="s">
         <v>1793</v>
@@ -67446,10 +67443,10 @@
     </row>
     <row r="1646" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1646" s="30" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B1646" s="7" t="s">
         <v>2469</v>
-      </c>
-      <c r="B1646" s="7" t="s">
-        <v>2470</v>
       </c>
       <c r="C1646" s="7" t="s">
         <v>21</v>
@@ -67465,7 +67462,7 @@
         <v>11000</v>
       </c>
       <c r="G1646" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1646" s="10" t="s">
         <v>1789</v>
@@ -67474,7 +67471,7 @@
         <v>534</v>
       </c>
       <c r="J1646" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1646" s="10" t="s">
         <v>1793</v>
@@ -67485,7 +67482,7 @@
         <v>535</v>
       </c>
       <c r="B1647" s="7" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="C1647" s="7" t="s">
         <v>21</v>
@@ -67501,7 +67498,7 @@
         <v>300</v>
       </c>
       <c r="G1647" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1647" s="10" t="s">
         <v>1789</v>
@@ -67510,7 +67507,7 @@
         <v>534</v>
       </c>
       <c r="J1647" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1647" s="10" t="s">
         <v>1793</v>
@@ -67518,10 +67515,10 @@
     </row>
     <row r="1648" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1648" s="30" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B1648" s="7" t="s">
         <v>2472</v>
-      </c>
-      <c r="B1648" s="7" t="s">
-        <v>2473</v>
       </c>
       <c r="C1648" s="7" t="s">
         <v>21</v>
@@ -67537,7 +67534,7 @@
         <v>300</v>
       </c>
       <c r="G1648" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1648" s="10" t="s">
         <v>1789</v>
@@ -67546,7 +67543,7 @@
         <v>534</v>
       </c>
       <c r="J1648" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1648" s="10" t="s">
         <v>1793</v>
@@ -67554,10 +67551,10 @@
     </row>
     <row r="1649" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1649" s="30" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B1649" s="7" t="s">
         <v>2474</v>
-      </c>
-      <c r="B1649" s="7" t="s">
-        <v>2475</v>
       </c>
       <c r="C1649" s="7" t="s">
         <v>21</v>
@@ -67573,7 +67570,7 @@
         <v>150</v>
       </c>
       <c r="G1649" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1649" s="10" t="s">
         <v>1789</v>
@@ -67582,7 +67579,7 @@
         <v>534</v>
       </c>
       <c r="J1649" s="7" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="K1649" s="10" t="s">
         <v>1793</v>
@@ -67590,10 +67587,10 @@
     </row>
     <row r="1650" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1650" s="30" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B1650" s="7" t="s">
         <v>2476</v>
-      </c>
-      <c r="B1650" s="7" t="s">
-        <v>2477</v>
       </c>
       <c r="C1650" s="7" t="s">
         <v>21</v>
@@ -67609,7 +67606,7 @@
         <v>275</v>
       </c>
       <c r="G1650" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1650" s="10" t="s">
         <v>1789</v>
@@ -67618,7 +67615,7 @@
         <v>534</v>
       </c>
       <c r="J1650" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1650" s="10" t="s">
         <v>1793</v>
@@ -67626,10 +67623,10 @@
     </row>
     <row r="1651" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1651" s="30" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B1651" s="7" t="s">
         <v>2479</v>
-      </c>
-      <c r="B1651" s="7" t="s">
-        <v>2480</v>
       </c>
       <c r="C1651" s="7" t="s">
         <v>21</v>
@@ -67645,7 +67642,7 @@
         <v>3000</v>
       </c>
       <c r="G1651" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1651" s="10" t="s">
         <v>1789</v>
@@ -67654,7 +67651,7 @@
         <v>534</v>
       </c>
       <c r="J1651" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1651" s="10" t="s">
         <v>1793</v>
@@ -67662,10 +67659,10 @@
     </row>
     <row r="1652" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1652" s="30" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="B1652" s="7" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="C1652" s="7" t="s">
         <v>21</v>
@@ -67681,7 +67678,7 @@
         <v>1500</v>
       </c>
       <c r="G1652" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1652" s="10" t="s">
         <v>1789</v>
@@ -67690,7 +67687,7 @@
         <v>534</v>
       </c>
       <c r="J1652" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1652" s="10" t="s">
         <v>1793</v>
@@ -67698,10 +67695,10 @@
     </row>
     <row r="1653" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1653" s="30" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B1653" s="7" t="s">
         <v>2483</v>
-      </c>
-      <c r="B1653" s="7" t="s">
-        <v>2484</v>
       </c>
       <c r="C1653" s="7" t="s">
         <v>21</v>
@@ -67717,7 +67714,7 @@
         <v>100</v>
       </c>
       <c r="G1653" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1653" s="10" t="s">
         <v>1789</v>
@@ -67726,7 +67723,7 @@
         <v>534</v>
       </c>
       <c r="J1653" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1653" s="10" t="s">
         <v>1793</v>
@@ -67734,10 +67731,10 @@
     </row>
     <row r="1654" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1654" s="30" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B1654" s="7" t="s">
         <v>2485</v>
-      </c>
-      <c r="B1654" s="7" t="s">
-        <v>2486</v>
       </c>
       <c r="C1654" s="7" t="s">
         <v>21</v>
@@ -67753,7 +67750,7 @@
         <v>75</v>
       </c>
       <c r="G1654" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1654" s="10" t="s">
         <v>1789</v>
@@ -67762,7 +67759,7 @@
         <v>534</v>
       </c>
       <c r="J1654" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1654" s="10" t="s">
         <v>1793</v>
@@ -67770,10 +67767,10 @@
     </row>
     <row r="1655" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1655" s="30" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B1655" s="7" t="s">
         <v>2487</v>
-      </c>
-      <c r="B1655" s="7" t="s">
-        <v>2488</v>
       </c>
       <c r="C1655" s="7" t="s">
         <v>21</v>
@@ -67789,7 +67786,7 @@
         <v>925</v>
       </c>
       <c r="G1655" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1655" s="10" t="s">
         <v>1789</v>
@@ -67798,7 +67795,7 @@
         <v>534</v>
       </c>
       <c r="J1655" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1655" s="10" t="s">
         <v>1793</v>
@@ -67806,10 +67803,10 @@
     </row>
     <row r="1656" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1656" s="30" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B1656" s="7" t="s">
         <v>2489</v>
-      </c>
-      <c r="B1656" s="7" t="s">
-        <v>2490</v>
       </c>
       <c r="C1656" s="7" t="s">
         <v>21</v>
@@ -67825,7 +67822,7 @@
         <v>17250</v>
       </c>
       <c r="G1656" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1656" s="10" t="s">
         <v>1789</v>
@@ -67834,7 +67831,7 @@
         <v>534</v>
       </c>
       <c r="J1656" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1656" s="10" t="s">
         <v>1793</v>
@@ -67842,10 +67839,10 @@
     </row>
     <row r="1657" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1657" s="30" t="s">
+        <v>2490</v>
+      </c>
+      <c r="B1657" s="7" t="s">
         <v>2491</v>
-      </c>
-      <c r="B1657" s="7" t="s">
-        <v>2492</v>
       </c>
       <c r="C1657" s="7" t="s">
         <v>21</v>
@@ -67861,7 +67858,7 @@
         <v>2250</v>
       </c>
       <c r="G1657" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1657" s="10" t="s">
         <v>1789</v>
@@ -67870,7 +67867,7 @@
         <v>534</v>
       </c>
       <c r="J1657" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1657" s="10" t="s">
         <v>1793</v>
@@ -67881,7 +67878,7 @@
         <v>841</v>
       </c>
       <c r="B1658" s="7" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="C1658" s="7" t="s">
         <v>21</v>
@@ -67897,7 +67894,7 @@
         <v>70</v>
       </c>
       <c r="G1658" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1658" s="10" t="s">
         <v>1789</v>
@@ -67906,7 +67903,7 @@
         <v>534</v>
       </c>
       <c r="J1658" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1658" s="10" t="s">
         <v>1793</v>
@@ -67917,7 +67914,7 @@
         <v>2067</v>
       </c>
       <c r="B1659" s="7" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="C1659" s="7" t="s">
         <v>21</v>
@@ -67933,7 +67930,7 @@
         <v>1225</v>
       </c>
       <c r="G1659" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1659" s="10" t="s">
         <v>1789</v>
@@ -67942,7 +67939,7 @@
         <v>534</v>
       </c>
       <c r="J1659" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1659" s="10" t="s">
         <v>1793</v>
@@ -67950,10 +67947,10 @@
     </row>
     <row r="1660" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1660" s="30" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="B1660" s="7" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="C1660" s="7" t="s">
         <v>21</v>
@@ -67969,7 +67966,7 @@
         <v>1750</v>
       </c>
       <c r="G1660" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1660" s="10" t="s">
         <v>1789</v>
@@ -67978,7 +67975,7 @@
         <v>534</v>
       </c>
       <c r="J1660" s="7" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="K1660" s="10" t="s">
         <v>1793</v>
@@ -67987,7 +67984,7 @@
     <row r="1661" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1661" s="6"/>
       <c r="B1661" s="7" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="C1661" s="7" t="s">
         <v>21</v>
@@ -68003,7 +68000,7 @@
         <v>1540</v>
       </c>
       <c r="G1661" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1661" s="10" t="s">
         <v>1789</v>
@@ -68012,7 +68009,7 @@
         <v>534</v>
       </c>
       <c r="J1661" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1661" s="10" t="s">
         <v>1793</v>
@@ -68021,7 +68018,7 @@
     <row r="1662" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1662" s="6"/>
       <c r="B1662" s="7" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="C1662" s="7" t="s">
         <v>21</v>
@@ -68037,7 +68034,7 @@
         <v>6125</v>
       </c>
       <c r="G1662" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1662" s="10" t="s">
         <v>1789</v>
@@ -68046,7 +68043,7 @@
         <v>534</v>
       </c>
       <c r="J1662" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1662" s="10" t="s">
         <v>1793</v>
@@ -68055,7 +68052,7 @@
     <row r="1663" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1663" s="6"/>
       <c r="B1663" s="7" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="C1663" s="7" t="s">
         <v>21</v>
@@ -68071,7 +68068,7 @@
         <v>570</v>
       </c>
       <c r="G1663" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1663" s="10" t="s">
         <v>1789</v>
@@ -68080,7 +68077,7 @@
         <v>534</v>
       </c>
       <c r="J1663" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1663" s="10" t="s">
         <v>1793</v>
@@ -68107,7 +68104,7 @@
         <v>250</v>
       </c>
       <c r="G1664" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1664" s="10" t="s">
         <v>1789</v>
@@ -68116,7 +68113,7 @@
         <v>534</v>
       </c>
       <c r="J1664" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1664" s="10" t="s">
         <v>1793</v>
@@ -68124,10 +68121,10 @@
     </row>
     <row r="1665" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1665" s="30" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="B1665" s="7" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="C1665" s="7" t="s">
         <v>713</v>
@@ -68143,7 +68140,7 @@
         <v>5800</v>
       </c>
       <c r="G1665" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1665" s="10" t="s">
         <v>1789</v>
@@ -68152,7 +68149,7 @@
         <v>534</v>
       </c>
       <c r="J1665" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1665" s="10" t="s">
         <v>1793</v>
@@ -68160,10 +68157,10 @@
     </row>
     <row r="1666" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1666" s="30" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="B1666" s="7" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C1666" s="7" t="s">
         <v>21</v>
@@ -68179,7 +68176,7 @@
         <v>150</v>
       </c>
       <c r="G1666" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1666" s="10" t="s">
         <v>1789</v>
@@ -68188,7 +68185,7 @@
         <v>534</v>
       </c>
       <c r="J1666" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1666" s="10" t="s">
         <v>1793</v>
@@ -68196,7 +68193,7 @@
     </row>
     <row r="1667" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1667" s="30" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B1667" s="7" t="s">
         <v>840</v>
@@ -68215,7 +68212,7 @@
         <v>1140</v>
       </c>
       <c r="G1667" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1667" s="10" t="s">
         <v>1789</v>
@@ -68224,7 +68221,7 @@
         <v>534</v>
       </c>
       <c r="J1667" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1667" s="10" t="s">
         <v>1793</v>
@@ -68232,10 +68229,10 @@
     </row>
     <row r="1668" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1668" s="30" t="s">
+        <v>2503</v>
+      </c>
+      <c r="B1668" s="7" t="s">
         <v>2504</v>
-      </c>
-      <c r="B1668" s="7" t="s">
-        <v>2505</v>
       </c>
       <c r="C1668" s="7" t="s">
         <v>21</v>
@@ -68251,7 +68248,7 @@
         <v>660</v>
       </c>
       <c r="G1668" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1668" s="10" t="s">
         <v>1789</v>
@@ -68260,7 +68257,7 @@
         <v>534</v>
       </c>
       <c r="J1668" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1668" s="10" t="s">
         <v>1793</v>
@@ -68268,7 +68265,7 @@
     </row>
     <row r="1669" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1669" s="30" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B1669" s="7" t="s">
         <v>2083</v>
@@ -68287,7 +68284,7 @@
         <v>768</v>
       </c>
       <c r="G1669" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1669" s="10" t="s">
         <v>1789</v>
@@ -68296,7 +68293,7 @@
         <v>534</v>
       </c>
       <c r="J1669" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1669" s="10" t="s">
         <v>1793</v>
@@ -68304,10 +68301,10 @@
     </row>
     <row r="1670" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1670" s="30" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B1670" s="7" t="s">
         <v>2507</v>
-      </c>
-      <c r="B1670" s="7" t="s">
-        <v>2508</v>
       </c>
       <c r="C1670" s="7" t="s">
         <v>21</v>
@@ -68323,7 +68320,7 @@
         <v>330</v>
       </c>
       <c r="G1670" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1670" s="10" t="s">
         <v>1789</v>
@@ -68332,7 +68329,7 @@
         <v>534</v>
       </c>
       <c r="J1670" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1670" s="10" t="s">
         <v>1793</v>
@@ -68340,10 +68337,10 @@
     </row>
     <row r="1671" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1671" s="30" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B1671" s="7" t="s">
         <v>2509</v>
-      </c>
-      <c r="B1671" s="7" t="s">
-        <v>2510</v>
       </c>
       <c r="C1671" s="7" t="s">
         <v>21</v>
@@ -68359,7 +68356,7 @@
         <v>1500</v>
       </c>
       <c r="G1671" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1671" s="10" t="s">
         <v>1789</v>
@@ -68368,7 +68365,7 @@
         <v>534</v>
       </c>
       <c r="J1671" s="7" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="K1671" s="10" t="s">
         <v>1793</v>
@@ -68376,10 +68373,10 @@
     </row>
     <row r="1672" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1672" s="30" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B1672" s="7" t="s">
         <v>2511</v>
-      </c>
-      <c r="B1672" s="7" t="s">
-        <v>2512</v>
       </c>
       <c r="C1672" s="7" t="s">
         <v>21</v>
@@ -68395,7 +68392,7 @@
         <v>1200</v>
       </c>
       <c r="G1672" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1672" s="10" t="s">
         <v>1789</v>
@@ -68404,7 +68401,7 @@
         <v>534</v>
       </c>
       <c r="J1672" s="7" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="K1672" s="10" t="s">
         <v>1793</v>
@@ -68412,10 +68409,10 @@
     </row>
     <row r="1673" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1673" s="30" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B1673" s="7" t="s">
         <v>2514</v>
-      </c>
-      <c r="B1673" s="7" t="s">
-        <v>2515</v>
       </c>
       <c r="C1673" s="7" t="s">
         <v>21</v>
@@ -68431,7 +68428,7 @@
         <v>500</v>
       </c>
       <c r="G1673" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1673" s="10" t="s">
         <v>1789</v>
@@ -68440,7 +68437,7 @@
         <v>534</v>
       </c>
       <c r="J1673" s="7" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="K1673" s="10" t="s">
         <v>1793</v>
@@ -68448,10 +68445,10 @@
     </row>
     <row r="1674" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1674" s="30" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B1674" s="7" t="s">
         <v>2516</v>
-      </c>
-      <c r="B1674" s="7" t="s">
-        <v>2517</v>
       </c>
       <c r="C1674" s="7" t="s">
         <v>21</v>
@@ -68467,7 +68464,7 @@
         <v>75</v>
       </c>
       <c r="G1674" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1674" s="10" t="s">
         <v>1789</v>
@@ -68476,7 +68473,7 @@
         <v>534</v>
       </c>
       <c r="J1674" s="7" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="K1674" s="10" t="s">
         <v>1793</v>
@@ -68484,10 +68481,10 @@
     </row>
     <row r="1675" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1675" s="30" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B1675" s="7" t="s">
         <v>2518</v>
-      </c>
-      <c r="B1675" s="7" t="s">
-        <v>2519</v>
       </c>
       <c r="C1675" s="7" t="s">
         <v>21</v>
@@ -68503,7 +68500,7 @@
         <v>35</v>
       </c>
       <c r="G1675" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1675" s="10" t="s">
         <v>1789</v>
@@ -68512,7 +68509,7 @@
         <v>534</v>
       </c>
       <c r="J1675" s="7" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="K1675" s="10" t="s">
         <v>1793</v>
@@ -68520,10 +68517,10 @@
     </row>
     <row r="1676" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1676" s="30" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B1676" s="7" t="s">
         <v>2520</v>
-      </c>
-      <c r="B1676" s="7" t="s">
-        <v>2521</v>
       </c>
       <c r="C1676" s="7" t="s">
         <v>21</v>
@@ -68539,7 +68536,7 @@
         <v>300</v>
       </c>
       <c r="G1676" s="7" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="H1676" s="10" t="s">
         <v>1789</v>
@@ -68548,7 +68545,7 @@
         <v>534</v>
       </c>
       <c r="J1676" s="7" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="K1676" s="10" t="s">
         <v>1793</v>
@@ -68559,7 +68556,7 @@
         <v>216</v>
       </c>
       <c r="B1677" s="7" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C1677" s="7" t="s">
         <v>21</v>
@@ -68575,19 +68572,19 @@
         <v>400</v>
       </c>
       <c r="G1677" s="7" t="s">
+        <v>2522</v>
+      </c>
+      <c r="H1677" s="10" t="s">
         <v>2523</v>
-      </c>
-      <c r="H1677" s="10" t="s">
-        <v>2524</v>
       </c>
       <c r="I1677" s="7" t="s">
         <v>129</v>
       </c>
       <c r="J1677" s="7" t="s">
+        <v>2524</v>
+      </c>
+      <c r="K1677" s="10" t="s">
         <v>2525</v>
-      </c>
-      <c r="K1677" s="10" t="s">
-        <v>2526</v>
       </c>
     </row>
     <row r="1678" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -68595,7 +68592,7 @@
         <v>806</v>
       </c>
       <c r="B1678" s="7" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="C1678" s="7" t="s">
         <v>62</v>
@@ -68611,27 +68608,27 @@
         <v>22610</v>
       </c>
       <c r="G1678" s="7" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="H1678" s="10" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="I1678" s="7" t="s">
         <v>77</v>
       </c>
       <c r="J1678" s="7" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="K1678" s="10" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="1679" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1679" s="30" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B1679" s="7" t="s">
         <v>2530</v>
-      </c>
-      <c r="B1679" s="7" t="s">
-        <v>2531</v>
       </c>
       <c r="C1679" s="7" t="s">
         <v>62</v>
@@ -68647,27 +68644,27 @@
         <v>14200</v>
       </c>
       <c r="G1679" s="7" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="H1679" s="10" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="I1679" s="7" t="s">
         <v>77</v>
       </c>
       <c r="J1679" s="7" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="K1679" s="10" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="1680" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1680" s="30" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B1680" s="7" t="s">
         <v>2532</v>
-      </c>
-      <c r="B1680" s="7" t="s">
-        <v>2533</v>
       </c>
       <c r="C1680" s="7" t="s">
         <v>21</v>
@@ -68683,19 +68680,19 @@
         <v>20000</v>
       </c>
       <c r="G1680" s="7" t="s">
+        <v>2533</v>
+      </c>
+      <c r="H1680" s="10" t="s">
         <v>2534</v>
-      </c>
-      <c r="H1680" s="10" t="s">
-        <v>2535</v>
       </c>
       <c r="I1680" s="7" t="s">
         <v>57</v>
       </c>
       <c r="J1680" s="7" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="K1680" s="10" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="1681" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -68703,7 +68700,7 @@
         <v>577</v>
       </c>
       <c r="B1681" s="7" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="C1681" s="7" t="s">
         <v>62</v>
@@ -68719,19 +68716,19 @@
         <v>8420.7999999999993</v>
       </c>
       <c r="G1681" s="7" t="s">
+        <v>2533</v>
+      </c>
+      <c r="H1681" s="10" t="s">
         <v>2534</v>
-      </c>
-      <c r="H1681" s="10" t="s">
-        <v>2535</v>
       </c>
       <c r="I1681" s="7" t="s">
         <v>57</v>
       </c>
       <c r="J1681" s="7" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="K1681" s="10" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="1682" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -68739,7 +68736,7 @@
         <v>699</v>
       </c>
       <c r="B1682" s="7" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="C1682" s="7" t="s">
         <v>62</v>
@@ -68755,19 +68752,19 @@
         <v>15788.999999999998</v>
       </c>
       <c r="G1682" s="7" t="s">
+        <v>2533</v>
+      </c>
+      <c r="H1682" s="10" t="s">
         <v>2534</v>
-      </c>
-      <c r="H1682" s="10" t="s">
-        <v>2535</v>
       </c>
       <c r="I1682" s="7" t="s">
         <v>57</v>
       </c>
       <c r="J1682" s="7" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="K1682" s="10" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="1683" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -68775,7 +68772,7 @@
         <v>157</v>
       </c>
       <c r="B1683" s="10" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="C1683" s="7" t="s">
         <v>21</v>
@@ -68791,7 +68788,7 @@
         <v>5557.5</v>
       </c>
       <c r="G1683" s="7" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="H1683" s="10" t="s">
         <v>2332</v>
@@ -68800,7 +68797,7 @@
         <v>144</v>
       </c>
       <c r="J1683" s="7" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="K1683" s="10">
         <v>46363</v>
@@ -68808,10 +68805,10 @@
     </row>
     <row r="1684" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1684" s="30" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B1684" s="10" t="s">
         <v>2542</v>
-      </c>
-      <c r="B1684" s="10" t="s">
-        <v>2543</v>
       </c>
       <c r="C1684" s="7" t="s">
         <v>21</v>
@@ -68827,7 +68824,7 @@
         <v>1054</v>
       </c>
       <c r="G1684" s="7" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="H1684" s="10" t="s">
         <v>2332</v>
@@ -68836,7 +68833,7 @@
         <v>144</v>
       </c>
       <c r="J1684" s="7" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="K1684" s="10">
         <v>46363</v>
@@ -68844,10 +68841,10 @@
     </row>
     <row r="1685" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1685" s="30" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B1685" s="10" t="s">
         <v>2544</v>
-      </c>
-      <c r="B1685" s="10" t="s">
-        <v>2545</v>
       </c>
       <c r="C1685" s="7" t="s">
         <v>21</v>
@@ -68863,7 +68860,7 @@
         <v>1266.99</v>
       </c>
       <c r="G1685" s="7" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="H1685" s="10" t="s">
         <v>2332</v>
@@ -68872,7 +68869,7 @@
         <v>144</v>
       </c>
       <c r="J1685" s="7" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="K1685" s="10">
         <v>46363</v>
@@ -68880,10 +68877,10 @@
     </row>
     <row r="1686" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1686" s="30" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B1686" s="10" t="s">
         <v>2546</v>
-      </c>
-      <c r="B1686" s="10" t="s">
-        <v>2547</v>
       </c>
       <c r="C1686" s="7" t="s">
         <v>21</v>
@@ -68899,7 +68896,7 @@
         <v>9284</v>
       </c>
       <c r="G1686" s="7" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="H1686" s="10" t="s">
         <v>2332</v>
@@ -68908,7 +68905,7 @@
         <v>144</v>
       </c>
       <c r="J1686" s="7" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="K1686" s="10">
         <v>46363</v>
@@ -68916,10 +68913,10 @@
     </row>
     <row r="1687" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1687" s="30" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B1687" s="10" t="s">
         <v>2548</v>
-      </c>
-      <c r="B1687" s="10" t="s">
-        <v>2549</v>
       </c>
       <c r="C1687" s="7" t="s">
         <v>21</v>
@@ -68935,7 +68932,7 @@
         <v>292.5</v>
       </c>
       <c r="G1687" s="7" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="H1687" s="10" t="s">
         <v>2332</v>
@@ -68944,7 +68941,7 @@
         <v>144</v>
       </c>
       <c r="J1687" s="7" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="K1687" s="10">
         <v>46363</v>
@@ -68952,10 +68949,10 @@
     </row>
     <row r="1688" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1688" s="30" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B1688" s="10" t="s">
         <v>2550</v>
-      </c>
-      <c r="B1688" s="10" t="s">
-        <v>2551</v>
       </c>
       <c r="C1688" s="7" t="s">
         <v>21</v>
@@ -68971,7 +68968,7 @@
         <v>1930.5</v>
       </c>
       <c r="G1688" s="7" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="H1688" s="10" t="s">
         <v>2332</v>
@@ -68980,7 +68977,7 @@
         <v>144</v>
       </c>
       <c r="J1688" s="7" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="K1688" s="10">
         <v>46363</v>
@@ -68991,7 +68988,7 @@
         <v>904</v>
       </c>
       <c r="B1689" s="10" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C1689" s="7" t="s">
         <v>21</v>
@@ -69007,7 +69004,7 @@
         <v>3071.25</v>
       </c>
       <c r="G1689" s="7" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="H1689" s="10" t="s">
         <v>2332</v>
@@ -69016,7 +69013,7 @@
         <v>144</v>
       </c>
       <c r="J1689" s="7" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="K1689" s="10">
         <v>46363</v>
@@ -69024,10 +69021,10 @@
     </row>
     <row r="1690" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1690" s="30" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B1690" s="10" t="s">
         <v>2553</v>
-      </c>
-      <c r="B1690" s="10" t="s">
-        <v>2554</v>
       </c>
       <c r="C1690" s="7" t="s">
         <v>21</v>
@@ -69043,7 +69040,7 @@
         <v>175.5</v>
       </c>
       <c r="G1690" s="7" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="H1690" s="10" t="s">
         <v>2332</v>
@@ -69052,7 +69049,7 @@
         <v>144</v>
       </c>
       <c r="J1690" s="7" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="K1690" s="10">
         <v>46363</v>
@@ -69063,7 +69060,7 @@
         <v>201</v>
       </c>
       <c r="B1691" s="10" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="C1691" s="10" t="s">
         <v>21</v>
@@ -69079,16 +69076,16 @@
         <v>2750</v>
       </c>
       <c r="G1691" s="7" t="s">
+        <v>2555</v>
+      </c>
+      <c r="H1691" s="10" t="s">
         <v>2556</v>
-      </c>
-      <c r="H1691" s="10" t="s">
-        <v>2557</v>
       </c>
       <c r="I1691" s="7" t="s">
         <v>203</v>
       </c>
       <c r="J1691" s="10" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="K1691" s="10">
         <v>46363</v>
@@ -69099,7 +69096,7 @@
         <v>205</v>
       </c>
       <c r="B1692" s="10" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="C1692" s="10" t="s">
         <v>21</v>
@@ -69115,16 +69112,16 @@
         <v>750</v>
       </c>
       <c r="G1692" s="7" t="s">
+        <v>2555</v>
+      </c>
+      <c r="H1692" s="10" t="s">
         <v>2556</v>
-      </c>
-      <c r="H1692" s="10" t="s">
-        <v>2557</v>
       </c>
       <c r="I1692" s="7" t="s">
         <v>203</v>
       </c>
       <c r="J1692" s="10" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="K1692" s="10">
         <v>46363</v>
@@ -69135,7 +69132,7 @@
         <v>297</v>
       </c>
       <c r="B1693" s="10" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="C1693" s="10" t="s">
         <v>21</v>
@@ -69151,16 +69148,16 @@
         <v>3200</v>
       </c>
       <c r="G1693" s="7" t="s">
+        <v>2555</v>
+      </c>
+      <c r="H1693" s="10" t="s">
         <v>2556</v>
-      </c>
-      <c r="H1693" s="10" t="s">
-        <v>2557</v>
       </c>
       <c r="I1693" s="7" t="s">
         <v>203</v>
       </c>
       <c r="J1693" s="10" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="K1693" s="10">
         <v>46363</v>
@@ -69171,7 +69168,7 @@
         <v>1528</v>
       </c>
       <c r="B1694" s="7" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="C1694" s="10" t="s">
         <v>21</v>
@@ -69187,27 +69184,27 @@
         <v>131614</v>
       </c>
       <c r="G1694" s="7" t="s">
+        <v>2561</v>
+      </c>
+      <c r="H1694" s="10" t="s">
+        <v>2556</v>
+      </c>
+      <c r="I1694" s="7" t="s">
         <v>2562</v>
       </c>
-      <c r="H1694" s="10" t="s">
-        <v>2557</v>
-      </c>
-      <c r="I1694" s="7" t="s">
+      <c r="J1694" s="7" t="s">
         <v>2563</v>
       </c>
-      <c r="J1694" s="7" t="s">
+      <c r="K1694" s="10" t="s">
         <v>2564</v>
-      </c>
-      <c r="K1694" s="10" t="s">
-        <v>2565</v>
       </c>
     </row>
     <row r="1695" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1695" s="30" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B1695" s="7" t="s">
         <v>2566</v>
-      </c>
-      <c r="B1695" s="7" t="s">
-        <v>2567</v>
       </c>
       <c r="C1695" s="10" t="s">
         <v>21</v>
@@ -69223,27 +69220,27 @@
         <v>222882</v>
       </c>
       <c r="G1695" s="7" t="s">
+        <v>2561</v>
+      </c>
+      <c r="H1695" s="10" t="s">
+        <v>2556</v>
+      </c>
+      <c r="I1695" s="7" t="s">
         <v>2562</v>
       </c>
-      <c r="H1695" s="10" t="s">
-        <v>2557</v>
-      </c>
-      <c r="I1695" s="7" t="s">
+      <c r="J1695" s="7" t="s">
         <v>2563</v>
       </c>
-      <c r="J1695" s="7" t="s">
+      <c r="K1695" s="10" t="s">
         <v>2564</v>
-      </c>
-      <c r="K1695" s="10" t="s">
-        <v>2565</v>
       </c>
     </row>
     <row r="1696" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1696" s="6" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B1696" s="7" t="s">
         <v>2568</v>
-      </c>
-      <c r="B1696" s="7" t="s">
-        <v>2569</v>
       </c>
       <c r="C1696" s="10" t="s">
         <v>21</v>
@@ -69259,7 +69256,7 @@
         <v>15684.300000000001</v>
       </c>
       <c r="G1696" s="7" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="H1696" s="10">
         <v>46327</v>
@@ -69268,7 +69265,7 @@
         <v>804</v>
       </c>
       <c r="J1696" s="7" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="K1696" s="10" t="s">
         <v>71</v>
@@ -69276,10 +69273,10 @@
     </row>
     <row r="1697" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1697" s="6" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B1697" s="7" t="s">
         <v>2572</v>
-      </c>
-      <c r="B1697" s="7" t="s">
-        <v>2573</v>
       </c>
       <c r="C1697" s="10" t="s">
         <v>21</v>
@@ -69295,7 +69292,7 @@
         <v>4966.7900000000009</v>
       </c>
       <c r="G1697" s="7" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="H1697" s="10">
         <v>46327</v>
@@ -69304,7 +69301,7 @@
         <v>804</v>
       </c>
       <c r="J1697" s="7" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="K1697" s="10" t="s">
         <v>71</v>
@@ -69313,7 +69310,7 @@
     <row r="1698" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1698" s="6"/>
       <c r="B1698" s="7" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="C1698" s="10" t="s">
         <v>21</v>
@@ -69329,7 +69326,7 @@
         <v>10054.800000000001</v>
       </c>
       <c r="G1698" s="7" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="H1698" s="10">
         <v>46327</v>
@@ -69338,7 +69335,7 @@
         <v>804</v>
       </c>
       <c r="J1698" s="7" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="K1698" s="10" t="s">
         <v>71</v>
@@ -69347,7 +69344,7 @@
     <row r="1699" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1699" s="6"/>
       <c r="B1699" s="7" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="C1699" s="10" t="s">
         <v>21</v>
@@ -69363,7 +69360,7 @@
         <v>2280</v>
       </c>
       <c r="G1699" s="7" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="H1699" s="10">
         <v>46327</v>
@@ -69372,7 +69369,7 @@
         <v>804</v>
       </c>
       <c r="J1699" s="7" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="K1699" s="10" t="s">
         <v>71</v>

--- a/data/transactions/all.xlsx
+++ b/data/transactions/all.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB866F8F-3AC0-47F0-B6CA-86F5AB4C425A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21E2912-FC40-4F9D-B3F2-51BA1939BFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9258" uniqueCount="2580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9254" uniqueCount="2580">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -8314,7 +8314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1700"/>
+  <dimension ref="A1:P1699"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="23" customWidth="1"/>
@@ -66134,7 +66134,7 @@
         <v>90.957490000000007</v>
       </c>
       <c r="F1609" s="9">
-        <f t="shared" ref="F1609:F1699" si="26">E1609*D1609</f>
+        <f t="shared" ref="F1609:F1698" si="26">E1609*D1609</f>
         <v>90957.49</v>
       </c>
       <c r="G1609" s="7">
@@ -66580,25 +66580,27 @@
       </c>
     </row>
     <row r="1622" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1622" s="30"/>
+      <c r="A1622" s="30" t="s">
+        <v>2422</v>
+      </c>
       <c r="B1622" s="7" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="C1622" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1622" s="8">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E1622" s="8">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="F1622" s="9">
         <f t="shared" si="26"/>
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="G1622" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H1622" s="10">
         <v>46146</v>
@@ -66607,7 +66609,7 @@
         <v>54</v>
       </c>
       <c r="J1622" s="7">
-        <v>6303</v>
+        <v>6304</v>
       </c>
       <c r="K1622" s="10" t="s">
         <v>1501</v>
@@ -66615,59 +66617,59 @@
     </row>
     <row r="1623" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1623" s="30" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="B1623" s="7" t="s">
-        <v>1535</v>
+        <v>2424</v>
       </c>
       <c r="C1623" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1623" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E1623" s="8">
-        <v>190</v>
+        <v>2015</v>
       </c>
       <c r="F1623" s="9">
         <f t="shared" si="26"/>
-        <v>950</v>
-      </c>
-      <c r="G1623" s="7">
-        <v>136</v>
-      </c>
-      <c r="H1623" s="10">
-        <v>46146</v>
+        <v>4030</v>
+      </c>
+      <c r="G1623" s="7" t="s">
+        <v>2425</v>
+      </c>
+      <c r="H1623" s="10" t="s">
+        <v>2426</v>
       </c>
       <c r="I1623" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J1623" s="7">
-        <v>6304</v>
+        <v>2427</v>
+      </c>
+      <c r="J1623" s="7" t="s">
+        <v>2428</v>
       </c>
       <c r="K1623" s="10" t="s">
-        <v>1501</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="1624" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1624" s="30" t="s">
-        <v>2423</v>
+        <v>2430</v>
       </c>
       <c r="B1624" s="7" t="s">
-        <v>2424</v>
+        <v>2431</v>
       </c>
       <c r="C1624" s="7" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D1624" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E1624" s="8">
-        <v>2015</v>
+        <v>1400</v>
       </c>
       <c r="F1624" s="9">
         <f t="shared" si="26"/>
-        <v>4030</v>
+        <v>7000</v>
       </c>
       <c r="G1624" s="7" t="s">
         <v>2425</v>
@@ -66687,59 +66689,59 @@
     </row>
     <row r="1625" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1625" s="30" t="s">
-        <v>2430</v>
+        <v>609</v>
       </c>
       <c r="B1625" s="7" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="C1625" s="7" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D1625" s="8">
-        <v>5</v>
+        <v>300</v>
       </c>
       <c r="E1625" s="8">
-        <v>1400</v>
+        <v>2021.05</v>
       </c>
       <c r="F1625" s="9">
         <f t="shared" si="26"/>
-        <v>7000</v>
+        <v>606315</v>
       </c>
       <c r="G1625" s="7" t="s">
-        <v>2425</v>
+        <v>2433</v>
       </c>
       <c r="H1625" s="10" t="s">
-        <v>2426</v>
+        <v>1783</v>
       </c>
       <c r="I1625" s="7" t="s">
-        <v>2427</v>
+        <v>2434</v>
       </c>
       <c r="J1625" s="7" t="s">
-        <v>2428</v>
+        <v>2435</v>
       </c>
       <c r="K1625" s="10" t="s">
-        <v>2429</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="1626" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1626" s="30" t="s">
-        <v>609</v>
+        <v>1737</v>
       </c>
       <c r="B1626" s="7" t="s">
-        <v>2432</v>
+        <v>2437</v>
       </c>
       <c r="C1626" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1626" s="8">
-        <v>300</v>
+        <v>72</v>
       </c>
       <c r="E1626" s="8">
-        <v>2021.05</v>
+        <v>3157.89</v>
       </c>
       <c r="F1626" s="9">
         <f t="shared" si="26"/>
-        <v>606315</v>
+        <v>227368.08</v>
       </c>
       <c r="G1626" s="7" t="s">
         <v>2433</v>
@@ -66759,23 +66761,23 @@
     </row>
     <row r="1627" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1627" s="30" t="s">
-        <v>1737</v>
+        <v>577</v>
       </c>
       <c r="B1627" s="7" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="C1627" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1627" s="8">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="E1627" s="8">
-        <v>3157.89</v>
+        <v>4736.8900000000003</v>
       </c>
       <c r="F1627" s="9">
         <f t="shared" si="26"/>
-        <v>227368.08</v>
+        <v>137369.81</v>
       </c>
       <c r="G1627" s="7" t="s">
         <v>2433</v>
@@ -66795,46 +66797,46 @@
     </row>
     <row r="1628" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1628" s="30" t="s">
-        <v>577</v>
+        <v>2439</v>
       </c>
       <c r="B1628" s="7" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="C1628" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1628" s="8">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E1628" s="8">
-        <v>4736.8900000000003</v>
+        <v>75</v>
       </c>
       <c r="F1628" s="9">
         <f t="shared" si="26"/>
-        <v>137369.81</v>
+        <v>3750</v>
       </c>
       <c r="G1628" s="7" t="s">
-        <v>2433</v>
+        <v>2441</v>
       </c>
       <c r="H1628" s="10" t="s">
-        <v>1783</v>
+        <v>1789</v>
       </c>
       <c r="I1628" s="7" t="s">
-        <v>2434</v>
+        <v>534</v>
       </c>
       <c r="J1628" s="7" t="s">
-        <v>2435</v>
+        <v>2442</v>
       </c>
       <c r="K1628" s="10" t="s">
-        <v>2436</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1629" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1629" s="30" t="s">
-        <v>2439</v>
+        <v>2443</v>
       </c>
       <c r="B1629" s="7" t="s">
-        <v>2440</v>
+        <v>2444</v>
       </c>
       <c r="C1629" s="7" t="s">
         <v>21</v>
@@ -66843,11 +66845,11 @@
         <v>50</v>
       </c>
       <c r="E1629" s="8">
-        <v>75</v>
+        <v>375</v>
       </c>
       <c r="F1629" s="9">
         <f t="shared" si="26"/>
-        <v>3750</v>
+        <v>18750</v>
       </c>
       <c r="G1629" s="7" t="s">
         <v>2441</v>
@@ -66867,19 +66869,19 @@
     </row>
     <row r="1630" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1630" s="30" t="s">
-        <v>2443</v>
+        <v>892</v>
       </c>
       <c r="B1630" s="7" t="s">
-        <v>2444</v>
+        <v>893</v>
       </c>
       <c r="C1630" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1630" s="8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E1630" s="8">
-        <v>375</v>
+        <v>750</v>
       </c>
       <c r="F1630" s="9">
         <f t="shared" si="26"/>
@@ -66903,23 +66905,23 @@
     </row>
     <row r="1631" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1631" s="30" t="s">
-        <v>892</v>
+        <v>2445</v>
       </c>
       <c r="B1631" s="7" t="s">
-        <v>893</v>
+        <v>2446</v>
       </c>
       <c r="C1631" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1631" s="8">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E1631" s="8">
-        <v>750</v>
+        <v>15</v>
       </c>
       <c r="F1631" s="9">
         <f t="shared" si="26"/>
-        <v>18750</v>
+        <v>300</v>
       </c>
       <c r="G1631" s="7" t="s">
         <v>2441</v>
@@ -66939,23 +66941,23 @@
     </row>
     <row r="1632" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1632" s="30" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="B1632" s="7" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="C1632" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1632" s="8">
+        <v>10</v>
+      </c>
+      <c r="E1632" s="8">
         <v>20</v>
-      </c>
-      <c r="E1632" s="8">
-        <v>15</v>
       </c>
       <c r="F1632" s="9">
         <f t="shared" si="26"/>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G1632" s="7" t="s">
         <v>2441</v>
@@ -66975,23 +66977,23 @@
     </row>
     <row r="1633" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1633" s="30" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="B1633" s="7" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="C1633" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1633" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E1633" s="8">
-        <v>20</v>
+        <v>675</v>
       </c>
       <c r="F1633" s="9">
         <f t="shared" si="26"/>
-        <v>200</v>
+        <v>3375</v>
       </c>
       <c r="G1633" s="7" t="s">
         <v>2441</v>
@@ -67011,23 +67013,23 @@
     </row>
     <row r="1634" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1634" s="30" t="s">
-        <v>2449</v>
+        <v>537</v>
       </c>
       <c r="B1634" s="7" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="C1634" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1634" s="8">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E1634" s="8">
-        <v>675</v>
+        <v>15</v>
       </c>
       <c r="F1634" s="9">
         <f t="shared" si="26"/>
-        <v>3375</v>
+        <v>750</v>
       </c>
       <c r="G1634" s="7" t="s">
         <v>2441</v>
@@ -67047,23 +67049,23 @@
     </row>
     <row r="1635" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1635" s="30" t="s">
-        <v>537</v>
+        <v>2452</v>
       </c>
       <c r="B1635" s="7" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="C1635" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1635" s="8">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E1635" s="8">
         <v>15</v>
       </c>
       <c r="F1635" s="9">
         <f t="shared" si="26"/>
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="G1635" s="7" t="s">
         <v>2441</v>
@@ -67083,10 +67085,10 @@
     </row>
     <row r="1636" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1636" s="30" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="B1636" s="7" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="C1636" s="7" t="s">
         <v>21</v>
@@ -67095,11 +67097,11 @@
         <v>100</v>
       </c>
       <c r="E1636" s="8">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="F1636" s="9">
         <f t="shared" si="26"/>
-        <v>1500</v>
+        <v>4800</v>
       </c>
       <c r="G1636" s="7" t="s">
         <v>2441</v>
@@ -67119,23 +67121,23 @@
     </row>
     <row r="1637" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1637" s="30" t="s">
-        <v>2454</v>
+        <v>539</v>
       </c>
       <c r="B1637" s="7" t="s">
-        <v>2455</v>
+        <v>540</v>
       </c>
       <c r="C1637" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1637" s="8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E1637" s="8">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F1637" s="9">
         <f t="shared" si="26"/>
-        <v>4800</v>
+        <v>1250</v>
       </c>
       <c r="G1637" s="7" t="s">
         <v>2441</v>
@@ -67155,26 +67157,26 @@
     </row>
     <row r="1638" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1638" s="30" t="s">
-        <v>539</v>
+        <v>847</v>
       </c>
       <c r="B1638" s="7" t="s">
-        <v>540</v>
+        <v>2456</v>
       </c>
       <c r="C1638" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1638" s="8">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E1638" s="8">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="F1638" s="9">
         <f t="shared" si="26"/>
-        <v>1250</v>
+        <v>5625</v>
       </c>
       <c r="G1638" s="7" t="s">
-        <v>2441</v>
+        <v>2457</v>
       </c>
       <c r="H1638" s="10" t="s">
         <v>1789</v>
@@ -67183,7 +67185,7 @@
         <v>534</v>
       </c>
       <c r="J1638" s="7" t="s">
-        <v>2442</v>
+        <v>2458</v>
       </c>
       <c r="K1638" s="10" t="s">
         <v>1793</v>
@@ -67191,23 +67193,23 @@
     </row>
     <row r="1639" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1639" s="30" t="s">
-        <v>847</v>
+        <v>2459</v>
       </c>
       <c r="B1639" s="7" t="s">
-        <v>2456</v>
+        <v>2460</v>
       </c>
       <c r="C1639" s="7" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D1639" s="8">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E1639" s="8">
-        <v>125</v>
+        <v>450</v>
       </c>
       <c r="F1639" s="9">
         <f t="shared" si="26"/>
-        <v>5625</v>
+        <v>2250</v>
       </c>
       <c r="G1639" s="7" t="s">
         <v>2457</v>
@@ -67227,19 +67229,19 @@
     </row>
     <row r="1640" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1640" s="30" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="B1640" s="7" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="C1640" s="7" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D1640" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E1640" s="8">
-        <v>450</v>
+        <v>2250</v>
       </c>
       <c r="F1640" s="9">
         <f t="shared" si="26"/>
@@ -67263,10 +67265,10 @@
     </row>
     <row r="1641" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1641" s="30" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="B1641" s="7" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="C1641" s="7" t="s">
         <v>21</v>
@@ -67275,11 +67277,11 @@
         <v>1</v>
       </c>
       <c r="E1641" s="8">
-        <v>2250</v>
+        <v>575</v>
       </c>
       <c r="F1641" s="9">
         <f t="shared" si="26"/>
-        <v>2250</v>
+        <v>575</v>
       </c>
       <c r="G1641" s="7" t="s">
         <v>2457</v>
@@ -67299,23 +67301,23 @@
     </row>
     <row r="1642" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1642" s="30" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="B1642" s="7" t="s">
-        <v>2464</v>
+        <v>2065</v>
       </c>
       <c r="C1642" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1642" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1642" s="8">
-        <v>575</v>
+        <v>125</v>
       </c>
       <c r="F1642" s="9">
         <f t="shared" si="26"/>
-        <v>575</v>
+        <v>500</v>
       </c>
       <c r="G1642" s="7" t="s">
         <v>2457</v>
@@ -67335,23 +67337,23 @@
     </row>
     <row r="1643" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1643" s="30" t="s">
-        <v>2465</v>
+        <v>2452</v>
       </c>
       <c r="B1643" s="7" t="s">
-        <v>2065</v>
+        <v>2453</v>
       </c>
       <c r="C1643" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1643" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1643" s="8">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="F1643" s="9">
         <f t="shared" si="26"/>
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="G1643" s="7" t="s">
         <v>2457</v>
@@ -67371,23 +67373,23 @@
     </row>
     <row r="1644" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1644" s="30" t="s">
-        <v>2452</v>
+        <v>2466</v>
       </c>
       <c r="B1644" s="7" t="s">
-        <v>2453</v>
+        <v>2467</v>
       </c>
       <c r="C1644" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1644" s="8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1644" s="8">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F1644" s="9">
         <f t="shared" si="26"/>
-        <v>90</v>
+        <v>675</v>
       </c>
       <c r="G1644" s="7" t="s">
         <v>2457</v>
@@ -67407,23 +67409,23 @@
     </row>
     <row r="1645" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1645" s="30" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="B1645" s="7" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="C1645" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1645" s="8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E1645" s="8">
-        <v>75</v>
+        <v>2750</v>
       </c>
       <c r="F1645" s="9">
         <f t="shared" si="26"/>
-        <v>675</v>
+        <v>11000</v>
       </c>
       <c r="G1645" s="7" t="s">
         <v>2457</v>
@@ -67443,10 +67445,10 @@
     </row>
     <row r="1646" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1646" s="30" t="s">
-        <v>2468</v>
+        <v>535</v>
       </c>
       <c r="B1646" s="7" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="C1646" s="7" t="s">
         <v>21</v>
@@ -67455,11 +67457,11 @@
         <v>4</v>
       </c>
       <c r="E1646" s="8">
-        <v>2750</v>
+        <v>75</v>
       </c>
       <c r="F1646" s="9">
         <f t="shared" si="26"/>
-        <v>11000</v>
+        <v>300</v>
       </c>
       <c r="G1646" s="7" t="s">
         <v>2457</v>
@@ -67479,10 +67481,10 @@
     </row>
     <row r="1647" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1647" s="30" t="s">
-        <v>535</v>
+        <v>2471</v>
       </c>
       <c r="B1647" s="7" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="C1647" s="7" t="s">
         <v>21</v>
@@ -67515,23 +67517,23 @@
     </row>
     <row r="1648" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1648" s="30" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="B1648" s="7" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="C1648" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1648" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E1648" s="8">
         <v>75</v>
       </c>
       <c r="F1648" s="9">
         <f t="shared" si="26"/>
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="G1648" s="7" t="s">
         <v>2457</v>
@@ -67551,23 +67553,23 @@
     </row>
     <row r="1649" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1649" s="30" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="B1649" s="7" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
       <c r="C1649" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1649" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1649" s="8">
-        <v>75</v>
+        <v>275</v>
       </c>
       <c r="F1649" s="9">
         <f t="shared" si="26"/>
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="G1649" s="7" t="s">
         <v>2457</v>
@@ -67579,7 +67581,7 @@
         <v>534</v>
       </c>
       <c r="J1649" s="7" t="s">
-        <v>2458</v>
+        <v>2477</v>
       </c>
       <c r="K1649" s="10" t="s">
         <v>1793</v>
@@ -67587,10 +67589,10 @@
     </row>
     <row r="1650" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1650" s="30" t="s">
-        <v>2475</v>
+        <v>2478</v>
       </c>
       <c r="B1650" s="7" t="s">
-        <v>2476</v>
+        <v>2479</v>
       </c>
       <c r="C1650" s="7" t="s">
         <v>21</v>
@@ -67599,11 +67601,11 @@
         <v>1</v>
       </c>
       <c r="E1650" s="8">
-        <v>275</v>
+        <v>3000</v>
       </c>
       <c r="F1650" s="9">
         <f t="shared" si="26"/>
-        <v>275</v>
+        <v>3000</v>
       </c>
       <c r="G1650" s="7" t="s">
         <v>2457</v>
@@ -67623,23 +67625,23 @@
     </row>
     <row r="1651" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1651" s="30" t="s">
-        <v>2478</v>
+        <v>2577</v>
       </c>
       <c r="B1651" s="7" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="C1651" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1651" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1651" s="8">
-        <v>3000</v>
+        <v>750</v>
       </c>
       <c r="F1651" s="9">
         <f t="shared" si="26"/>
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="G1651" s="7" t="s">
         <v>2457</v>
@@ -67659,23 +67661,23 @@
     </row>
     <row r="1652" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1652" s="30" t="s">
-        <v>2577</v>
+        <v>2482</v>
       </c>
       <c r="B1652" s="7" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="C1652" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1652" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E1652" s="8">
-        <v>750</v>
+        <v>25</v>
       </c>
       <c r="F1652" s="9">
         <f t="shared" si="26"/>
-        <v>1500</v>
+        <v>100</v>
       </c>
       <c r="G1652" s="7" t="s">
         <v>2457</v>
@@ -67695,23 +67697,23 @@
     </row>
     <row r="1653" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1653" s="30" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="B1653" s="7" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="C1653" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1653" s="8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E1653" s="8">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F1653" s="9">
         <f t="shared" si="26"/>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G1653" s="7" t="s">
         <v>2457</v>
@@ -67731,23 +67733,23 @@
     </row>
     <row r="1654" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1654" s="30" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="B1654" s="7" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="C1654" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1654" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1654" s="8">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="F1654" s="9">
         <f t="shared" si="26"/>
-        <v>75</v>
+        <v>925</v>
       </c>
       <c r="G1654" s="7" t="s">
         <v>2457</v>
@@ -67767,10 +67769,10 @@
     </row>
     <row r="1655" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1655" s="30" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="B1655" s="7" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="C1655" s="7" t="s">
         <v>21</v>
@@ -67779,11 +67781,11 @@
         <v>5</v>
       </c>
       <c r="E1655" s="8">
-        <v>185</v>
+        <v>3450</v>
       </c>
       <c r="F1655" s="9">
         <f t="shared" si="26"/>
-        <v>925</v>
+        <v>17250</v>
       </c>
       <c r="G1655" s="7" t="s">
         <v>2457</v>
@@ -67803,10 +67805,10 @@
     </row>
     <row r="1656" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1656" s="30" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="B1656" s="7" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="C1656" s="7" t="s">
         <v>21</v>
@@ -67815,11 +67817,11 @@
         <v>5</v>
       </c>
       <c r="E1656" s="8">
-        <v>3450</v>
+        <v>450</v>
       </c>
       <c r="F1656" s="9">
         <f t="shared" si="26"/>
-        <v>17250</v>
+        <v>2250</v>
       </c>
       <c r="G1656" s="7" t="s">
         <v>2457</v>
@@ -67839,23 +67841,23 @@
     </row>
     <row r="1657" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1657" s="30" t="s">
-        <v>2490</v>
+        <v>841</v>
       </c>
       <c r="B1657" s="7" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="C1657" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1657" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E1657" s="8">
-        <v>450</v>
+        <v>35</v>
       </c>
       <c r="F1657" s="9">
         <f t="shared" si="26"/>
-        <v>2250</v>
+        <v>70</v>
       </c>
       <c r="G1657" s="7" t="s">
         <v>2457</v>
@@ -67875,23 +67877,23 @@
     </row>
     <row r="1658" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1658" s="30" t="s">
-        <v>841</v>
+        <v>2067</v>
       </c>
       <c r="B1658" s="7" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="C1658" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1658" s="8">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E1658" s="8">
         <v>35</v>
       </c>
       <c r="F1658" s="9">
         <f t="shared" si="26"/>
-        <v>70</v>
+        <v>1225</v>
       </c>
       <c r="G1658" s="7" t="s">
         <v>2457</v>
@@ -67911,23 +67913,23 @@
     </row>
     <row r="1659" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1659" s="30" t="s">
-        <v>2067</v>
+        <v>2578</v>
       </c>
       <c r="B1659" s="7" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="C1659" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1659" s="8">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E1659" s="8">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="F1659" s="9">
         <f t="shared" si="26"/>
-        <v>1225</v>
+        <v>1750</v>
       </c>
       <c r="G1659" s="7" t="s">
         <v>2457</v>
@@ -67946,24 +67948,22 @@
       </c>
     </row>
     <row r="1660" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1660" s="30" t="s">
-        <v>2578</v>
-      </c>
+      <c r="A1660" s="6"/>
       <c r="B1660" s="7" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="C1660" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1660" s="8">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E1660" s="8">
-        <v>175</v>
+        <v>28</v>
       </c>
       <c r="F1660" s="9">
         <f t="shared" si="26"/>
-        <v>1750</v>
+        <v>1540</v>
       </c>
       <c r="G1660" s="7" t="s">
         <v>2457</v>
@@ -67975,7 +67975,7 @@
         <v>534</v>
       </c>
       <c r="J1660" s="7" t="s">
-        <v>2477</v>
+        <v>2497</v>
       </c>
       <c r="K1660" s="10" t="s">
         <v>1793</v>
@@ -67984,20 +67984,20 @@
     <row r="1661" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1661" s="6"/>
       <c r="B1661" s="7" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="C1661" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1661" s="8">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="E1661" s="8">
-        <v>28</v>
+        <v>875</v>
       </c>
       <c r="F1661" s="9">
         <f t="shared" si="26"/>
-        <v>1540</v>
+        <v>6125</v>
       </c>
       <c r="G1661" s="7" t="s">
         <v>2457</v>
@@ -68018,20 +68018,20 @@
     <row r="1662" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1662" s="6"/>
       <c r="B1662" s="7" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="C1662" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1662" s="8">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E1662" s="8">
-        <v>875</v>
+        <v>38</v>
       </c>
       <c r="F1662" s="9">
         <f t="shared" si="26"/>
-        <v>6125</v>
+        <v>570</v>
       </c>
       <c r="G1662" s="7" t="s">
         <v>2457</v>
@@ -68050,22 +68050,24 @@
       </c>
     </row>
     <row r="1663" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1663" s="6"/>
+      <c r="A1663" s="6" t="s">
+        <v>833</v>
+      </c>
       <c r="B1663" s="7" t="s">
-        <v>2499</v>
+        <v>834</v>
       </c>
       <c r="C1663" s="7" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D1663" s="8">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E1663" s="8">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="F1663" s="9">
         <f t="shared" si="26"/>
-        <v>570</v>
+        <v>250</v>
       </c>
       <c r="G1663" s="7" t="s">
         <v>2457</v>
@@ -68084,24 +68086,24 @@
       </c>
     </row>
     <row r="1664" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1664" s="6" t="s">
-        <v>833</v>
+      <c r="A1664" s="30" t="s">
+        <v>2480</v>
       </c>
       <c r="B1664" s="7" t="s">
-        <v>834</v>
+        <v>2500</v>
       </c>
       <c r="C1664" s="7" t="s">
-        <v>46</v>
+        <v>713</v>
       </c>
       <c r="D1664" s="8">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E1664" s="8">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="F1664" s="9">
         <f t="shared" si="26"/>
-        <v>250</v>
+        <v>5800</v>
       </c>
       <c r="G1664" s="7" t="s">
         <v>2457</v>
@@ -68121,23 +68123,23 @@
     </row>
     <row r="1665" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1665" s="30" t="s">
-        <v>2480</v>
+        <v>2494</v>
       </c>
       <c r="B1665" s="7" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="C1665" s="7" t="s">
-        <v>713</v>
+        <v>21</v>
       </c>
       <c r="D1665" s="8">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="E1665" s="8">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="F1665" s="9">
         <f t="shared" si="26"/>
-        <v>5800</v>
+        <v>150</v>
       </c>
       <c r="G1665" s="7" t="s">
         <v>2457</v>
@@ -68157,23 +68159,23 @@
     </row>
     <row r="1666" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1666" s="30" t="s">
-        <v>2494</v>
+        <v>2502</v>
       </c>
       <c r="B1666" s="7" t="s">
-        <v>2501</v>
+        <v>840</v>
       </c>
       <c r="C1666" s="7" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D1666" s="8">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1666" s="8">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="F1666" s="9">
         <f t="shared" si="26"/>
-        <v>150</v>
+        <v>1140</v>
       </c>
       <c r="G1666" s="7" t="s">
         <v>2457</v>
@@ -68193,23 +68195,23 @@
     </row>
     <row r="1667" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1667" s="30" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="B1667" s="7" t="s">
-        <v>840</v>
+        <v>2504</v>
       </c>
       <c r="C1667" s="7" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D1667" s="8">
         <v>12</v>
       </c>
       <c r="E1667" s="8">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="F1667" s="9">
         <f t="shared" si="26"/>
-        <v>1140</v>
+        <v>660</v>
       </c>
       <c r="G1667" s="7" t="s">
         <v>2457</v>
@@ -68229,23 +68231,23 @@
     </row>
     <row r="1668" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1668" s="30" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="B1668" s="7" t="s">
-        <v>2504</v>
+        <v>2083</v>
       </c>
       <c r="C1668" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1668" s="8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1668" s="8">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F1668" s="9">
         <f t="shared" si="26"/>
-        <v>660</v>
+        <v>768</v>
       </c>
       <c r="G1668" s="7" t="s">
         <v>2457</v>
@@ -68265,23 +68267,23 @@
     </row>
     <row r="1669" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1669" s="30" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="B1669" s="7" t="s">
-        <v>2083</v>
+        <v>2507</v>
       </c>
       <c r="C1669" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1669" s="8">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E1669" s="8">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F1669" s="9">
         <f t="shared" si="26"/>
-        <v>768</v>
+        <v>330</v>
       </c>
       <c r="G1669" s="7" t="s">
         <v>2457</v>
@@ -68301,23 +68303,23 @@
     </row>
     <row r="1670" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1670" s="30" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="B1670" s="7" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="C1670" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1670" s="8">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E1670" s="8">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F1670" s="9">
         <f t="shared" si="26"/>
-        <v>330</v>
+        <v>1500</v>
       </c>
       <c r="G1670" s="7" t="s">
         <v>2457</v>
@@ -68337,10 +68339,10 @@
     </row>
     <row r="1671" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1671" s="30" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="B1671" s="7" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="C1671" s="7" t="s">
         <v>21</v>
@@ -68349,11 +68351,11 @@
         <v>60</v>
       </c>
       <c r="E1671" s="8">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F1671" s="9">
         <f t="shared" si="26"/>
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="G1671" s="7" t="s">
         <v>2457</v>
@@ -68365,7 +68367,7 @@
         <v>534</v>
       </c>
       <c r="J1671" s="7" t="s">
-        <v>2497</v>
+        <v>2512</v>
       </c>
       <c r="K1671" s="10" t="s">
         <v>1793</v>
@@ -68373,23 +68375,23 @@
     </row>
     <row r="1672" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1672" s="30" t="s">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="B1672" s="7" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="C1672" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1672" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E1672" s="8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F1672" s="9">
         <f t="shared" si="26"/>
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="G1672" s="7" t="s">
         <v>2457</v>
@@ -68409,23 +68411,23 @@
     </row>
     <row r="1673" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1673" s="30" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="B1673" s="7" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="C1673" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1673" s="8">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E1673" s="8">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F1673" s="9">
         <f t="shared" si="26"/>
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="G1673" s="7" t="s">
         <v>2457</v>
@@ -68445,10 +68447,10 @@
     </row>
     <row r="1674" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1674" s="30" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="B1674" s="7" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="C1674" s="7" t="s">
         <v>21</v>
@@ -68457,11 +68459,11 @@
         <v>1</v>
       </c>
       <c r="E1674" s="8">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F1674" s="9">
         <f t="shared" si="26"/>
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G1674" s="7" t="s">
         <v>2457</v>
@@ -68481,23 +68483,23 @@
     </row>
     <row r="1675" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1675" s="30" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="B1675" s="7" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="C1675" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1675" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1675" s="8">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F1675" s="9">
         <f t="shared" si="26"/>
-        <v>35</v>
+        <v>300</v>
       </c>
       <c r="G1675" s="7" t="s">
         <v>2457</v>
@@ -68517,71 +68519,71 @@
     </row>
     <row r="1676" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1676" s="30" t="s">
-        <v>2519</v>
+        <v>216</v>
       </c>
       <c r="B1676" s="7" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="C1676" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1676" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E1676" s="8">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="F1676" s="9">
         <f t="shared" si="26"/>
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G1676" s="7" t="s">
-        <v>2457</v>
+        <v>2522</v>
       </c>
       <c r="H1676" s="10" t="s">
-        <v>1789</v>
+        <v>2523</v>
       </c>
       <c r="I1676" s="7" t="s">
-        <v>534</v>
+        <v>129</v>
       </c>
       <c r="J1676" s="7" t="s">
-        <v>2512</v>
+        <v>2524</v>
       </c>
       <c r="K1676" s="10" t="s">
-        <v>1793</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="1677" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1677" s="30" t="s">
-        <v>216</v>
+        <v>806</v>
       </c>
       <c r="B1677" s="7" t="s">
-        <v>2521</v>
+        <v>2526</v>
       </c>
       <c r="C1677" s="7" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D1677" s="8">
-        <v>2</v>
+        <v>266</v>
       </c>
       <c r="E1677" s="8">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="F1677" s="9">
         <f t="shared" si="26"/>
-        <v>400</v>
+        <v>22610</v>
       </c>
       <c r="G1677" s="7" t="s">
-        <v>2522</v>
+        <v>2527</v>
       </c>
       <c r="H1677" s="10" t="s">
         <v>2523</v>
       </c>
       <c r="I1677" s="7" t="s">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="J1677" s="7" t="s">
-        <v>2524</v>
+        <v>2528</v>
       </c>
       <c r="K1677" s="10" t="s">
         <v>2525</v>
@@ -68589,23 +68591,23 @@
     </row>
     <row r="1678" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1678" s="30" t="s">
-        <v>806</v>
+        <v>2529</v>
       </c>
       <c r="B1678" s="7" t="s">
-        <v>2526</v>
+        <v>2530</v>
       </c>
       <c r="C1678" s="7" t="s">
         <v>62</v>
       </c>
       <c r="D1678" s="8">
-        <v>266</v>
+        <v>568</v>
       </c>
       <c r="E1678" s="8">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="F1678" s="9">
         <f t="shared" si="26"/>
-        <v>22610</v>
+        <v>14200</v>
       </c>
       <c r="G1678" s="7" t="s">
         <v>2527</v>
@@ -68625,35 +68627,35 @@
     </row>
     <row r="1679" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1679" s="30" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="B1679" s="7" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="C1679" s="7" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D1679" s="8">
-        <v>568</v>
+        <v>5</v>
       </c>
       <c r="E1679" s="8">
-        <v>25</v>
+        <v>4000</v>
       </c>
       <c r="F1679" s="9">
         <f t="shared" si="26"/>
-        <v>14200</v>
+        <v>20000</v>
       </c>
       <c r="G1679" s="7" t="s">
-        <v>2527</v>
+        <v>2533</v>
       </c>
       <c r="H1679" s="10" t="s">
-        <v>2523</v>
+        <v>2534</v>
       </c>
       <c r="I1679" s="7" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="J1679" s="7" t="s">
-        <v>2528</v>
+        <v>2535</v>
       </c>
       <c r="K1679" s="10" t="s">
         <v>2525</v>
@@ -68661,23 +68663,23 @@
     </row>
     <row r="1680" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1680" s="30" t="s">
-        <v>2531</v>
+        <v>577</v>
       </c>
       <c r="B1680" s="7" t="s">
-        <v>2532</v>
+        <v>2536</v>
       </c>
       <c r="C1680" s="7" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D1680" s="8">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E1680" s="8">
-        <v>4000</v>
+        <v>263.14999999999998</v>
       </c>
       <c r="F1680" s="9">
         <f t="shared" si="26"/>
-        <v>20000</v>
+        <v>8420.7999999999993</v>
       </c>
       <c r="G1680" s="7" t="s">
         <v>2533</v>
@@ -68697,23 +68699,23 @@
     </row>
     <row r="1681" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1681" s="30" t="s">
-        <v>577</v>
+        <v>699</v>
       </c>
       <c r="B1681" s="7" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="C1681" s="7" t="s">
         <v>62</v>
       </c>
       <c r="D1681" s="8">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E1681" s="8">
         <v>263.14999999999998</v>
       </c>
       <c r="F1681" s="9">
         <f t="shared" si="26"/>
-        <v>8420.7999999999993</v>
+        <v>15788.999999999998</v>
       </c>
       <c r="G1681" s="7" t="s">
         <v>2533</v>
@@ -68733,59 +68735,59 @@
     </row>
     <row r="1682" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1682" s="30" t="s">
-        <v>699</v>
-      </c>
-      <c r="B1682" s="7" t="s">
-        <v>2537</v>
+        <v>157</v>
+      </c>
+      <c r="B1682" s="10" t="s">
+        <v>2538</v>
       </c>
       <c r="C1682" s="7" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D1682" s="8">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E1682" s="8">
-        <v>263.14999999999998</v>
+        <v>555.75</v>
       </c>
       <c r="F1682" s="9">
-        <f t="shared" si="26"/>
-        <v>15788.999999999998</v>
+        <f>E1682*D1682</f>
+        <v>5557.5</v>
       </c>
       <c r="G1682" s="7" t="s">
-        <v>2533</v>
+        <v>2539</v>
       </c>
       <c r="H1682" s="10" t="s">
-        <v>2534</v>
+        <v>2332</v>
       </c>
       <c r="I1682" s="7" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="J1682" s="7" t="s">
-        <v>2535</v>
-      </c>
-      <c r="K1682" s="10" t="s">
-        <v>2525</v>
+        <v>2540</v>
+      </c>
+      <c r="K1682" s="10">
+        <v>46363</v>
       </c>
     </row>
     <row r="1683" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1683" s="30" t="s">
-        <v>157</v>
+        <v>2541</v>
       </c>
       <c r="B1683" s="10" t="s">
-        <v>2538</v>
+        <v>2542</v>
       </c>
       <c r="C1683" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1683" s="8">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E1683" s="8">
-        <v>555.75</v>
+        <v>1054</v>
       </c>
       <c r="F1683" s="9">
-        <f>E1683*D1683</f>
-        <v>5557.5</v>
+        <f t="shared" ref="F1683:F1692" si="27">E1683*D1683</f>
+        <v>1054</v>
       </c>
       <c r="G1683" s="7" t="s">
         <v>2539</v>
@@ -68805,10 +68807,10 @@
     </row>
     <row r="1684" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1684" s="30" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="B1684" s="10" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="C1684" s="7" t="s">
         <v>21</v>
@@ -68817,11 +68819,11 @@
         <v>1</v>
       </c>
       <c r="E1684" s="8">
-        <v>1054</v>
+        <v>1266.99</v>
       </c>
       <c r="F1684" s="9">
-        <f t="shared" ref="F1684:F1693" si="27">E1684*D1684</f>
-        <v>1054</v>
+        <f t="shared" si="27"/>
+        <v>1266.99</v>
       </c>
       <c r="G1684" s="7" t="s">
         <v>2539</v>
@@ -68841,23 +68843,23 @@
     </row>
     <row r="1685" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1685" s="30" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="B1685" s="10" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="C1685" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1685" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E1685" s="8">
-        <v>1266.99</v>
+        <v>1160.5</v>
       </c>
       <c r="F1685" s="9">
         <f t="shared" si="27"/>
-        <v>1266.99</v>
+        <v>9284</v>
       </c>
       <c r="G1685" s="7" t="s">
         <v>2539</v>
@@ -68877,23 +68879,23 @@
     </row>
     <row r="1686" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1686" s="30" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="B1686" s="10" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="C1686" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1686" s="8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E1686" s="8">
-        <v>1160.5</v>
+        <v>292.5</v>
       </c>
       <c r="F1686" s="9">
-        <f t="shared" si="27"/>
-        <v>9284</v>
+        <f>E1686*D1686</f>
+        <v>292.5</v>
       </c>
       <c r="G1686" s="7" t="s">
         <v>2539</v>
@@ -68913,10 +68915,10 @@
     </row>
     <row r="1687" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1687" s="30" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="B1687" s="10" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
       <c r="C1687" s="7" t="s">
         <v>21</v>
@@ -68925,11 +68927,11 @@
         <v>1</v>
       </c>
       <c r="E1687" s="8">
-        <v>292.5</v>
+        <v>1930.5</v>
       </c>
       <c r="F1687" s="9">
-        <f>E1687*D1687</f>
-        <v>292.5</v>
+        <f t="shared" si="27"/>
+        <v>1930.5</v>
       </c>
       <c r="G1687" s="7" t="s">
         <v>2539</v>
@@ -68949,23 +68951,23 @@
     </row>
     <row r="1688" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1688" s="30" t="s">
-        <v>2549</v>
+        <v>904</v>
       </c>
       <c r="B1688" s="10" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="C1688" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1688" s="8">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E1688" s="8">
-        <v>1930.5</v>
+        <v>204.75</v>
       </c>
       <c r="F1688" s="9">
         <f t="shared" si="27"/>
-        <v>1930.5</v>
+        <v>3071.25</v>
       </c>
       <c r="G1688" s="7" t="s">
         <v>2539</v>
@@ -68985,23 +68987,23 @@
     </row>
     <row r="1689" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1689" s="30" t="s">
-        <v>904</v>
+        <v>2552</v>
       </c>
       <c r="B1689" s="10" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="C1689" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D1689" s="8">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E1689" s="8">
-        <v>204.75</v>
+        <v>175.5</v>
       </c>
       <c r="F1689" s="9">
         <f t="shared" si="27"/>
-        <v>3071.25</v>
+        <v>175.5</v>
       </c>
       <c r="G1689" s="7" t="s">
         <v>2539</v>
@@ -69021,35 +69023,35 @@
     </row>
     <row r="1690" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1690" s="30" t="s">
-        <v>2552</v>
+        <v>201</v>
       </c>
       <c r="B1690" s="10" t="s">
-        <v>2553</v>
-      </c>
-      <c r="C1690" s="7" t="s">
+        <v>2554</v>
+      </c>
+      <c r="C1690" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D1690" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1690" s="8">
-        <v>175.5</v>
+        <v>550</v>
       </c>
       <c r="F1690" s="9">
         <f t="shared" si="27"/>
-        <v>175.5</v>
+        <v>2750</v>
       </c>
       <c r="G1690" s="7" t="s">
-        <v>2539</v>
+        <v>2555</v>
       </c>
       <c r="H1690" s="10" t="s">
-        <v>2332</v>
+        <v>2556</v>
       </c>
       <c r="I1690" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="J1690" s="7" t="s">
-        <v>2540</v>
+        <v>203</v>
+      </c>
+      <c r="J1690" s="10" t="s">
+        <v>2557</v>
       </c>
       <c r="K1690" s="10">
         <v>46363</v>
@@ -69057,23 +69059,23 @@
     </row>
     <row r="1691" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1691" s="30" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B1691" s="10" t="s">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="C1691" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D1691" s="8">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E1691" s="8">
-        <v>550</v>
+        <v>15</v>
       </c>
       <c r="F1691" s="9">
         <f t="shared" si="27"/>
-        <v>2750</v>
+        <v>750</v>
       </c>
       <c r="G1691" s="7" t="s">
         <v>2555</v>
@@ -69093,23 +69095,23 @@
     </row>
     <row r="1692" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1692" s="30" t="s">
-        <v>205</v>
+        <v>297</v>
       </c>
       <c r="B1692" s="10" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="C1692" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D1692" s="8">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E1692" s="8">
-        <v>15</v>
+        <v>800</v>
       </c>
       <c r="F1692" s="9">
         <f t="shared" si="27"/>
-        <v>750</v>
+        <v>3200</v>
       </c>
       <c r="G1692" s="7" t="s">
         <v>2555</v>
@@ -69129,59 +69131,59 @@
     </row>
     <row r="1693" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1693" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="B1693" s="10" t="s">
-        <v>2559</v>
+        <v>1528</v>
+      </c>
+      <c r="B1693" s="7" t="s">
+        <v>2560</v>
       </c>
       <c r="C1693" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D1693" s="8">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="E1693" s="8">
-        <v>800</v>
+        <v>1666</v>
       </c>
       <c r="F1693" s="9">
-        <f t="shared" si="27"/>
-        <v>3200</v>
+        <f t="shared" si="26"/>
+        <v>131614</v>
       </c>
       <c r="G1693" s="7" t="s">
-        <v>2555</v>
+        <v>2561</v>
       </c>
       <c r="H1693" s="10" t="s">
         <v>2556</v>
       </c>
       <c r="I1693" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="J1693" s="10" t="s">
-        <v>2557</v>
-      </c>
-      <c r="K1693" s="10">
-        <v>46363</v>
+        <v>2562</v>
+      </c>
+      <c r="J1693" s="7" t="s">
+        <v>2563</v>
+      </c>
+      <c r="K1693" s="10" t="s">
+        <v>2564</v>
       </c>
     </row>
     <row r="1694" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1694" s="30" t="s">
-        <v>1528</v>
+        <v>2565</v>
       </c>
       <c r="B1694" s="7" t="s">
-        <v>2560</v>
+        <v>2566</v>
       </c>
       <c r="C1694" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D1694" s="8">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="E1694" s="8">
-        <v>1666</v>
+        <v>1842</v>
       </c>
       <c r="F1694" s="9">
         <f t="shared" si="26"/>
-        <v>131614</v>
+        <v>222882</v>
       </c>
       <c r="G1694" s="7" t="s">
         <v>2561</v>
@@ -69200,60 +69202,60 @@
       </c>
     </row>
     <row r="1695" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1695" s="30" t="s">
-        <v>2565</v>
+      <c r="A1695" s="6" t="s">
+        <v>2567</v>
       </c>
       <c r="B1695" s="7" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="C1695" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D1695" s="8">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="E1695" s="8">
-        <v>1842</v>
+        <v>871.35</v>
       </c>
       <c r="F1695" s="9">
         <f t="shared" si="26"/>
-        <v>222882</v>
+        <v>15684.300000000001</v>
       </c>
       <c r="G1695" s="7" t="s">
-        <v>2561</v>
-      </c>
-      <c r="H1695" s="10" t="s">
-        <v>2556</v>
+        <v>2569</v>
+      </c>
+      <c r="H1695" s="10">
+        <v>46327</v>
       </c>
       <c r="I1695" s="7" t="s">
-        <v>2562</v>
+        <v>804</v>
       </c>
       <c r="J1695" s="7" t="s">
-        <v>2563</v>
+        <v>2570</v>
       </c>
       <c r="K1695" s="10" t="s">
-        <v>2564</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1696" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1696" s="6" t="s">
-        <v>2567</v>
+        <v>2571</v>
       </c>
       <c r="B1696" s="7" t="s">
-        <v>2568</v>
+        <v>2572</v>
       </c>
       <c r="C1696" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D1696" s="8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1696" s="8">
-        <v>871.35</v>
+        <v>261.41000000000003</v>
       </c>
       <c r="F1696" s="9">
         <f t="shared" si="26"/>
-        <v>15684.300000000001</v>
+        <v>4966.7900000000009</v>
       </c>
       <c r="G1696" s="7" t="s">
         <v>2569</v>
@@ -69272,11 +69274,9 @@
       </c>
     </row>
     <row r="1697" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1697" s="6" t="s">
-        <v>2571</v>
-      </c>
+      <c r="A1697" s="6"/>
       <c r="B1697" s="7" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="C1697" s="10" t="s">
         <v>21</v>
@@ -69284,12 +69284,12 @@
       <c r="D1697" s="8">
         <v>19</v>
       </c>
-      <c r="E1697" s="8">
-        <v>261.41000000000003</v>
+      <c r="E1697" s="19">
+        <v>529.20000000000005</v>
       </c>
       <c r="F1697" s="9">
         <f t="shared" si="26"/>
-        <v>4966.7900000000009</v>
+        <v>10054.800000000001</v>
       </c>
       <c r="G1697" s="7" t="s">
         <v>2569</v>
@@ -69310,7 +69310,7 @@
     <row r="1698" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1698" s="6"/>
       <c r="B1698" s="7" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="C1698" s="10" t="s">
         <v>21</v>
@@ -69318,12 +69318,12 @@
       <c r="D1698" s="8">
         <v>19</v>
       </c>
-      <c r="E1698" s="19">
-        <v>529.20000000000005</v>
+      <c r="E1698" s="8">
+        <v>120</v>
       </c>
       <c r="F1698" s="9">
         <f t="shared" si="26"/>
-        <v>10054.800000000001</v>
+        <v>2280</v>
       </c>
       <c r="G1698" s="7" t="s">
         <v>2569</v>
@@ -69341,53 +69341,19 @@
         <v>71</v>
       </c>
     </row>
-    <row r="1699" spans="1:11" s="12" customFormat="1" ht="24" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1699" s="6"/>
-      <c r="B1699" s="7" t="s">
-        <v>2574</v>
-      </c>
-      <c r="C1699" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1699" s="8">
-        <v>19</v>
-      </c>
-      <c r="E1699" s="8">
-        <v>120</v>
-      </c>
-      <c r="F1699" s="9">
-        <f t="shared" si="26"/>
-        <v>2280</v>
-      </c>
-      <c r="G1699" s="7" t="s">
-        <v>2569</v>
-      </c>
-      <c r="H1699" s="10">
-        <v>46327</v>
-      </c>
-      <c r="I1699" s="7" t="s">
-        <v>804</v>
-      </c>
-      <c r="J1699" s="7" t="s">
-        <v>2570</v>
-      </c>
-      <c r="K1699" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="1700" spans="1:11" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="C1700" s="20"/>
-      <c r="D1700" s="21"/>
-      <c r="E1700" s="21"/>
-      <c r="F1700" s="33">
-        <f>SUM(F2:F1699)</f>
-        <v>27668891.124196012</v>
-      </c>
-      <c r="G1700" s="20"/>
-      <c r="H1700" s="22"/>
-      <c r="I1700" s="20"/>
-      <c r="J1700" s="20"/>
-      <c r="K1700" s="22"/>
+    <row r="1699" spans="1:11" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="C1699" s="20"/>
+      <c r="D1699" s="21"/>
+      <c r="E1699" s="21"/>
+      <c r="F1699" s="33">
+        <f>SUM(F2:F1698)</f>
+        <v>27668441.124196012</v>
+      </c>
+      <c r="G1699" s="20"/>
+      <c r="H1699" s="22"/>
+      <c r="I1699" s="20"/>
+      <c r="J1699" s="20"/>
+      <c r="K1699" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
